--- a/docs/requirements-v0.1.xlsx
+++ b/docs/requirements-v0.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Workspace\02_開発\workbench\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B98EE4-9476-473E-8F0D-BFF753DF94F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1170B8F5-1DA0-438D-907A-BA333C5E9D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="163">
   <si>
     <t>チーム名:</t>
   </si>
@@ -52,9 +52,6 @@
     <t>ver.0.1</t>
   </si>
   <si>
-    <t>2026年10月14日</t>
-  </si>
-  <si>
     <t>利用者承認</t>
   </si>
   <si>
@@ -100,9 +97,6 @@
     <t>新規作成(下書き)</t>
   </si>
   <si>
-    <t>2026/10/14</t>
-  </si>
-  <si>
     <t>要件定義書(製品名・コンセプト)</t>
   </si>
   <si>
@@ -158,14 +152,6 @@
   </si>
   <si>
     <t>作業台(workbench)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>開けば、次にやることがわかる</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>トップ画面を開いた瞬間に、大学と開発のやることが締切順に並び、次に手をつけるものが決まる。機能を足すか迷ったら「開いた瞬間に次がわかるようになるか」で判断する。</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -243,21 +229,12 @@
     <t>トップ画面の表示</t>
   </si>
   <si>
-    <t>開いてから2秒以内に、今日・今週のやることが出る</t>
-  </si>
-  <si>
-    <t>タスク100件を入れた状態で測る</t>
-  </si>
-  <si>
     <t>使いやすさ</t>
   </si>
   <si>
     <t>作業の切り替え</t>
   </si>
   <si>
-    <t>記録中の作業を別のものに切り替えるのが2クリック以内</t>
-  </si>
-  <si>
     <t>実際に操作して数える</t>
   </si>
   <si>
@@ -307,41 +284,11 @@
   </si>
   <si>
     <t>対象外</t>
-  </si>
-  <si>
-    <t>X3 スマホ・サーバー公開</t>
-  </si>
-  <si>
-    <t>スマホからの利用と、ネット上のサーバーでの公開はしない</t>
-  </si>
-  <si>
-    <t>X4 チーム・ゼミでの共有</t>
-  </si>
-  <si>
-    <t>ほかの人とデータを共有する機能は作らない</t>
-  </si>
-  <si>
-    <t>X5 販売・課金</t>
-  </si>
-  <si>
-    <t>販売や課金はしない</t>
-  </si>
-  <si>
-    <t>X6 学習サイトの読み取り</t>
-  </si>
-  <si>
-    <t>大学の学習サイトに自分のパスワードを持たせて、中身を読み取ることはしない(大学の利用規約に触れるおそれがあるため)</t>
   </si>
   <si>
     <t>自分1人(情報系の大学生。PC 操作と git に慣れている)。
 対象外の利用者:ほかの学生、先生・大学職員、チームやゼミでの共有。</t>
     <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>X2 ほかの学生の利用</t>
-  </si>
-  <si>
-    <t>ほかの学生のユーザー登録・ログインは作らない。将来も広げない</t>
   </si>
   <si>
     <t>F9 大学からの連絡の取り込み</t>
@@ -546,6 +493,131 @@
     <t>済:「手つかず」の決め方と日数 → 締切ありは締切の3日前に記録なし、締切なしは登録から3日間記録なし
 済:「長い」の時間 → 2時間
 済:アプリを閉じているときの通知 → 画面を閉じていても通知する(PC 起動時に自動で立ち上がる)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:どのメールを「大学からの連絡」とみなすか → 差出人が大学のアドレスのもの。授業・奨学金・試合のチケットを分けて見せる
+済:3種類に当てはまらない大学のメールをどうするか → 「その他」としてたたんで出す
+済:「学内連絡:」の一斉配信をどこまで拾うか → 3種類以外は全部「その他」に入る
+済:奨学金・試合のチケットの連絡をどこに出すか → それぞれ大学の入れ物にする
+済:授業への振り分け方 → 科目名で自動、外れたら選び直し、選び直しを覚える
+済:タスクの候補を、確認なしで登録するか → 自動で登録し、印をつけ、1回で消せる
+済:いつ読むか、Outlook が起動していないときの扱い → 起動時と10分ごと。閉じていれば裏で立ち上げる</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>大学の Outlook メールから、授業・奨学金・試合のチケット・その他の連絡を取り込む</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・モーニングブリーフの時間割(timetable.md)を直接読む。時間割を直すのはこのファイル1か所だけ。公開リポジトリには入れない
+・時間割の科目を、大学の入れ物として登録する
+・トップ画面に今日の授業を出す
+・読めなかったときは、画面に「時間割を読めませんでした」と出す
+・学期の入れ替えは自動にしない。学期が終わったら、自分が Claude に新しい時間割を説明し、Claude が時間割の書き換えと、終わった授業の入れ物の終了を行う。そのとき Claude は、何をどう変えたか(変更の仕方)を説明する
+・頼み忘れを防ぐため、学期の終わりが近づいたら、トップ画面に「※学期が終わります。時間割の入れ替えを Claude に頼む」と米印つきで出す(案:学期の終わりの1週間前から)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:時間割ファイルを直接読むか、写して持つか → モーニングブリーフの timetable.md を直接読む
+済:学期が変わったときの入れ替え → 自分が Claude に説明し、Claude が変更して、変更の仕方を説明する
+・学期の終わりの日をどこに持つか、米印をいつから出すか(案:1週間前)
+→ 基本設計で決める</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>見れば、次にやることがわかる</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>画面に目をやった瞬間に、大学と開発のやることが締切順に並び、次に手をつけるものが決まる。ずっと開いておく使い方に合わせ、「開いたとき」に限らず、見ればいつでもわかることを大事にする。機能を足すか迷ったら「見た瞬間に次がわかるようになるか」で判断する。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>目的の達成</t>
+  </si>
+  <si>
+    <t>締切の見落としがない</t>
+  </si>
+  <si>
+    <t>2週間使って、締切を過ぎてから気づいた課題が0件</t>
+  </si>
+  <si>
+    <t>2週間のあいだに「期限切れ」に入ったタスクを数え、気づくのが締切より後だったものが0件か確かめる</t>
+  </si>
+  <si>
+    <t>迷う時間がない</t>
+  </si>
+  <si>
+    <t>画面を見てから次の作業を選ぶまで10秒以内</t>
+  </si>
+  <si>
+    <t>5回測り、5回とも10秒以内か確かめる</t>
+  </si>
+  <si>
+    <t>開いてから2秒以内に、今日・今週のやることが出る(Claude の案)。git とメールの読み込みは含めない。画面を先に出し、読み込みは裏で続け、読み込み中は「大学のメールを読み込み中…」と小さく出す</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク100件(Claude の案)を入れた状態で、画面が出てやることが並ぶまでを測る</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>記録中の作業を別のものに切り替えるのが2クリック以内(Claude の案)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>X1 大学からの連絡の取り込み</t>
+  </si>
+  <si>
+    <t>対象外から外し、機能 F9 として作る(要件定義 問8で「X1 だけは実現させたい」と決めた)</t>
+  </si>
+  <si>
+    <t>対象外</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>X2 ほかの学生の利用</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ほかの学生のユーザー登録・ログインは作らない。将来も広げない</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>―</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>X3 スマホ・サーバー公開</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>スマホからの利用と、ネット上のサーバーでの公開はしない</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>X4 チーム・ゼミでの共有</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ほかの人とデータを共有する機能は作らない</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>X5 販売・課金</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>販売や課金はしない</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>X6 学習サイトの読み取り</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>大学の学習サイトに自分のパスワードを持たせて、中身を読み取ることはしない(大学の利用規約に触れるおそれがあるため)。ただし、学習サイトから大学のアドレスで届く通知メールは F9 で読む。メール本文のリンクは画面に出すだけで、サイトを開いてログインするのは自分</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -558,34 +630,12 @@
 ・授業の連絡は、件名や本文に時間割の科目名が入っているかで、その授業の入れ物に振り分ける
 ・振り分けを間違えたものや「その他」に入ったものは、自分で入れ物を選び直せる。選び直した結果を覚え、次から同じ差出人・同じ件名なら、その入れ物に入れる
 ・「奨学金」「試合のチケット」は大学の入れ物として自動で作り、授業と同じように扱う
-・締切が書いてあるメールは、確認なしで自動でタスクにし、「メールから自動で入った」印をつける。間違っていたら1回の操作で消せ、消したものは次に読んだときに復活しない</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>済:どのメールを「大学からの連絡」とみなすか → 差出人が大学のアドレスのもの。授業・奨学金・試合のチケットを分けて見せる
-済:3種類に当てはまらない大学のメールをどうするか → 「その他」としてたたんで出す
-済:「学内連絡:」の一斉配信をどこまで拾うか → 3種類以外は全部「その他」に入る
-済:奨学金・試合のチケットの連絡をどこに出すか → それぞれ大学の入れ物にする
-済:授業への振り分け方 → 科目名で自動、外れたら選び直し、選び直しを覚える
-済:タスクの候補を、確認なしで登録するか → 自動で登録し、印をつけ、1回で消せる
-済:いつ読むか、Outlook が起動していないときの扱い → 起動時と10分ごと。閉じていれば裏で立ち上げる</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>大学の Outlook メールから、授業・奨学金・試合のチケット・その他の連絡を取り込む</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・モーニングブリーフの時間割(timetable.md)を直接読む。時間割を直すのはこのファイル1か所だけ。公開リポジトリには入れない
-・時間割の科目を、大学の入れ物として登録する
-・トップ画面に今日の授業を出す
-・読めなかったときは、画面に「時間割を読めませんでした」と出す
-・学期の入れ替えは自動にしない。学期が終わったら、自分が Claude に新しい時間割を説明し、Claude が時間割の書き換えと、終わった授業の入れ物の終了を行う。そのとき Claude は、何をどう変えたか(変更の仕方)を説明する</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>済:時間割ファイルを直接読むか、写して持つか → モーニングブリーフの timetable.md を直接読む
-済:学期が変わったときの入れ替え → 自分が Claude に説明し、Claude が変更して、変更の仕方を説明する</t>
+・締切が書いてあるメールは、確認なしで自動でタスクにし、「メールから自動で入った」印をつける。間違っていたら1回の操作で消せ、消したものは次に読んだときに復活しない
+・学習サイトから大学のアドレスで届く通知メールも読む。本文にあるサイトへのリンクを画面に出し、自分でクリックして開ける。アプリがサイトを開くことはしない(X6)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>2026年10月15日</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -757,7 +807,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -799,6 +849,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1160,44 +1222,44 @@
       <c r="I10" s="14"/>
       <c r="J10" s="14"/>
     </row>
-    <row r="13" spans="1:10" ht="18.75">
+    <row r="13" spans="1:10" ht="37.5">
       <c r="F13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>8</v>
+      <c r="G13" s="22" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="16.5">
       <c r="E15" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="12"/>
       <c r="H15" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I15" s="12"/>
       <c r="J15" s="12"/>
     </row>
     <row r="16" spans="1:10" ht="16.5">
       <c r="E16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="H16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="17" spans="5:10" ht="45.95" customHeight="1">
@@ -1243,39 +1305,39 @@
   <sheetData>
     <row r="1" spans="1:9" ht="24">
       <c r="A1" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="16.5">
       <c r="A2" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="16.5">
       <c r="A3" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="C5" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="D5" s="16" t="s">
         <v>19</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>20</v>
       </c>
       <c r="E5" s="18"/>
       <c r="F5" s="16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5" s="18"/>
       <c r="H5" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I5" s="18"/>
     </row>
@@ -1284,22 +1346,22 @@
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
       <c r="D6" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="16.5">
@@ -1307,14 +1369,14 @@
         <v>1</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>23</v>
-      </c>
       <c r="D7" s="4"/>
-      <c r="E7" s="4" t="s">
-        <v>24</v>
+      <c r="E7" s="23">
+        <v>46310</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
@@ -1559,61 +1621,61 @@
   <sheetData>
     <row r="1" spans="1:3" ht="24">
       <c r="A1" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16.5">
       <c r="A2" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="16.5">
       <c r="A3" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="36" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C5" s="8"/>
     </row>
     <row r="6" spans="1:3" ht="36" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>45</v>
+        <v>25</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="54">
       <c r="A7" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="54">
       <c r="A8" s="11" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="81">
       <c r="A9" s="11" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1642,252 +1704,252 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24">
       <c r="A1" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="16.5">
       <c r="A2" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="16.5">
       <c r="A3" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="16.5">
       <c r="A5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>33</v>
-      </c>
       <c r="G5" s="7" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="99">
       <c r="A6" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="C6" s="8" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="115.5">
       <c r="A7" s="8"/>
       <c r="B7" s="8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="148.5">
       <c r="A8" s="8"/>
       <c r="B8" s="8" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="115.5">
       <c r="A9" s="8"/>
       <c r="B9" s="8" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="82.5">
       <c r="A10" s="8"/>
       <c r="B10" s="8" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="132">
       <c r="A11" s="8"/>
       <c r="B11" s="8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="132">
       <c r="A12" s="8"/>
       <c r="B12" s="8" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="148.5">
       <c r="A13" s="8"/>
       <c r="B13" s="8" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="379.5">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="409.5">
       <c r="A14" s="8"/>
       <c r="B14" s="8" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="165">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="214.5">
       <c r="A15" s="8"/>
       <c r="B15" s="8" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>151</v>
+        <v>87</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>133</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>152</v>
+        <v>48</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>134</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="16.5">
@@ -1947,22 +2009,22 @@
   <sheetData>
     <row r="1" spans="1:1" ht="24">
       <c r="A1" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="16.5">
       <c r="A2" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="16.5">
       <c r="A3" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="16.5">
       <c r="A5" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1977,7 +2039,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1988,283 +2050,325 @@
   <sheetData>
     <row r="1" spans="1:4" ht="24">
       <c r="A1" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.5">
       <c r="A2" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.5">
       <c r="A3" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16.5">
       <c r="A5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="16.5">
+    </row>
+    <row r="6" spans="1:4" ht="49.5">
       <c r="A6" s="8" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>70</v>
+        <v>64</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16.5">
       <c r="A7" s="8" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>73</v>
+        <v>66</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16.5">
       <c r="A8" s="8" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="16.5">
       <c r="A9" s="8" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16.5">
       <c r="A10" s="8" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="16.5">
       <c r="A11" s="8" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C11" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="33">
+      <c r="A12" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="16.5">
+      <c r="A13" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="33">
+      <c r="A14" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="27">
+      <c r="A15" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="54">
+      <c r="A17" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="27">
+      <c r="A18" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="C18" s="11" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="33">
-      <c r="A12" s="8" t="s">
+      <c r="D18" s="11" t="s">
         <v>90</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="33">
-      <c r="A13" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="27">
-      <c r="A15" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="27">
-      <c r="A16" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="27">
-      <c r="A17" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="11" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="11" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="27">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" s="11" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="27">
       <c r="A22" s="11" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="27">
       <c r="A23" s="11" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>89</v>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="40.5">
+      <c r="A25" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/docs/requirements-v0.1.xlsx
+++ b/docs/requirements-v0.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Workspace\02_開発\workbench\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1170B8F5-1DA0-438D-907A-BA333C5E9D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B696BD9F-E58E-4074-8491-C5A922E9FD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="188">
   <si>
     <t>チーム名:</t>
   </si>
@@ -392,38 +392,14 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>・入れ物の種類は「大学」と「開発」の2つ
-・タスクと作業記録は、どれか1つの入れ物に入る
-・入れ物は消さずに「終了」にしてしまう。終了にすると一覧とトップ画面から見えなくなり、中身は残る。あとで戻せる
-・完全に消せるのは、中身が空の入れ物だけ
-・学期が終わった授業も「終了」にして片付ける</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>済:入れ物を消したとき、中のタスクと作業記録をどうするか → 消さずに終了にする
 済:学期が終わった授業をどう片付けるか → 終了にする</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・タスクは必ず1つの入れ物に入る
-・締切(日付)をつけられる。締切のないタスクも登録できる
-・締切には時刻も入れられる(入れなくてもよい)。時刻のあるタスクは、同じ日の中で時刻順に並ぶ
-・毎週の繰り返しを作れる(例:毎週火曜 9:00まで)。1つ完了すると、次の週の分が自動で出る
-・完了にできる</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>済:締切のないタスクを許すか → 許す(トップでは「締切なし」にまとめる)
 済:締切に時刻まで要るか → 締切をつけるときは日付が必須、時刻は任意
 済:毎週出る課題のような繰り返しをどうするか → 毎週の繰り返しだけ作れる</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・一番上に「期限切れ」として、締切を過ぎたタスクを色を変えてまとめる。完了にするか締切を変えるまで残る
-・その下に「今日」と「今週」に分けて、締切の近い順に並べる
-・締切のないタスクは、その下に「締切なし」としてまとめて出す
-・同じ締切の日の中は、①時刻があるものは時刻順、時刻なしはその日の最後 ②同じなら大学を開発より先 ③さらに同じなら登録が古い順。「締切なし」の中は登録が古い順
-・各タスクに入れ物の名前のラベル(例:「卒論」「fx-practice」)をつけ、ラベルの色を大学と開発の2色で分ける</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -479,14 +455,6 @@
   <si>
     <t>済:いつ読むか → 起動時と10分ごと
 済:コミットは時刻が1点しかないので、作業時間をどう出すか → 手の記録があればくっつける、なければ点として並べる</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・締切の前日に知らせる
-・手つかずのタスクを知らせる。締切のあるタスクは、締切の3日前になっても作業記録が1つもないとき。締切のないタスクは、登録してから3日間、作業記録も完了もないとき
-・同じ作業記録が2時間続いたら知らせる(切り替え忘れを防ぐため)
-・画面を閉じていても通知する。PC を起動したら裏の部分が自動で立ち上がる
-・PC の電源が切れていた間の通知は、次に画面を開いたときにまとめて見せる</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -636,6 +604,154 @@
   </si>
   <si>
     <t>2026年10月15日</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・タスクは必ず1つの入れ物に入る
+・締切(日付)をつけられる。締切のないタスクも登録できる
+・開発のタスクは、ふだんは締切を空のままにする。面接前のデモなど、必要なときだけつけられる
+・締切には時刻も入れられる(入れなくてもよい)。時刻のあるタスクは、同じ日の中で時刻順に並ぶ
+・毎週の繰り返しを作れる(例:毎週火曜 9:00まで)。1つ完了すると、次の週の分が自動で出る
+・完了にできる</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・締切の前日に知らせる
+・手つかずのタスクを知らせる。締切のあるタスクは、締切の3日前になっても作業記録が1つもないとき。締切のないタスクは、登録してから3日間、作業記録も完了もないとき(開発の締切のないタスクには出さない)
+・「手つかず」はタスクを選んだ作業記録だけで判断する。入れ物だけを選んだ記録は数えない。通知が来たら、その記録にタスクを選び直せば止まる
+・同じ作業記録が2時間続いたら知らせる(切り替え忘れを防ぐため)
+・画面を閉じていても通知する。PC を起動したら裏の部分が自動で立ち上がる
+・PC の電源が切れていた間の通知は、次に画面を開いたときにまとめて見せる</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・入れ物の種類は「大学」「開発」「就活」の3つ
+・タスクと作業記録は、どれか1つの入れ物に入る
+・入れ物は消さずに「終了」にしてしまう。終了にすると一覧とトップ画面から見えなくなり、中身は残る。あとで戻せる
+・完全に消せるのは、中身が空の入れ物だけ
+・学期が終わった授業も「終了」にして片付ける</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・一番上に「期限切れ」として、締切を過ぎたタスクを色を変えてまとめる。完了にするか締切を変えるまで残る
+・その下に「今日」と「今週」に分けて、締切の近い順に並べる
+・締切のないタスクは、その下に「締切なし」としてまとめて出す
+・同じ締切の日の中は、①時刻があるものは時刻順、時刻なしはその日の最後 ②同じなら大学・就活を開発より先 ③さらに同じなら登録が古い順。「締切なし」の中は登録が古い順
+・各タスクに入れ物の名前のラベル(例:「卒論」「fx-practice」)をつけ、ラベルの色を大学・開発・就活の3色で分ける</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>F11 就活</t>
+  </si>
+  <si>
+    <t>就活を入れ物の種類に足し、企業ごとに締切や面接日を管理する</t>
+  </si>
+  <si>
+    <t>要件定義 追加の要望(就活は Google カレンダーや企業からの連絡が見たい)・追加4</t>
+  </si>
+  <si>
+    <t>・入れ物の種類「就活」で、企業ごとに入れ物を1つ作る(エントリーしたときに自分で作る)
+・ES の締切や面接日は、その企業の入れ物のタスクになる
+・企業からの連絡(個人の Gmail)を取り込む。読み方は Google の公式の連携(API)。最初に一度、Google の画面で許可する。許可の鍵は PC の中にだけ置き、公開リポジトリに入れない
+・企業の入れ物に、その企業のメールアドレス(@ から後ろ)を登録できる。差出人が一致したメールと、件名や本文に企業の入れ物の名前が入っているメール(就活サイト経由のもの)を、その企業の入れ物に振り分ける
+・振り分けを間違えたものは自分で入れ物を選び直せる。選び直した結果を覚える(F9 と同じ仕組み)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:企業からのメールをどう見分けるか → アドレスと企業名の両方で見分け、外れたら選び直し、覚える
+済:Gmail をどう読むか → Google の公式の連携(API)。F12・F13 のカレンダーと同じ許可を使う</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>F12 Google カレンダーを見る</t>
+  </si>
+  <si>
+    <t>Google カレンダーの今日の予定を、トップ画面に出す</t>
+  </si>
+  <si>
+    <t>要件定義 追加の要望(Google カレンダーの予定を見たい)・追加7(図で比べた)</t>
+  </si>
+  <si>
+    <t>・F10 の今日の授業と同じ「今日の時間」の列に、今日の予定を混ぜて時刻順に並べる
+・空き時間は書かない
+・読むのは個人の Google アカウントのメインのカレンダーだけ
+・読み方は F11 と同じ Google の公式の連携(API)。読めなかったときは、推測で埋めず「Google に接続できませんでした」と出す</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:どのカレンダーを読むか → 個人のアカウントのメインのカレンダーだけ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>F13 Google カレンダーに書く</t>
+  </si>
+  <si>
+    <t>締切や日時があるものを、Google カレンダーに自動で書き込む</t>
+  </si>
+  <si>
+    <t>要件定義 追加の要望(大学の連絡・面談の通知・課題の締切をカレンダーに自動で書きたい)・F13 は workbench に任せる・追加9</t>
+  </si>
+  <si>
+    <t>・書き込むもの:タスクの締切(大学・就活・締切をつけた開発)、面接・面談、休講・補講、奨学金の手続きなど、締切か日時があるもの
+・「その他」のメールから自動で入ったものは書き込まない
+・面接など日時の決まったものは、時刻つきの予定にする。締切は全部終日の予定にし、時刻は名前に書く(例:「締切 23:59 第10回レポート」)
+・重なる予定があって書かなかったときは、画面に「重なる予定があったので、カレンダーには書きませんでした」と出す
+・書き込み先は、F12 と同じ個人のアカウントのメインのカレンダー
+・workbench が書いた予定には目印をつける。workbench で締切や日時を変えたり、タスクを消したりしたら、目印のある予定だけを書き換え・削除する。自分や他の人が作った予定には一切触れない
+・タスクを完了にしたら、予定は消さずに名前の頭に「済」をつける(例:「済 第10回レポート」)。期限が過ぎて未完了のものは、そのまま残す
+・同じ予定がすでにカレンダーにあれば書き込まない。日時のある予定は、同じ日に時間帯が重なれば名前が違っても同じとみなす。時間帯のない締切は、同じ日に同じ名前なら同じとみなす
+・モーニングブリーフ(gmail-secretary)側の自動登録は止める(二重登録を防ぐため)。止めるのは、F13 が動くようになってから</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:締切や日時が変わったり、タスクを消したりしたとき、カレンダーの予定も直すか → 直す(workbench が書いた予定だけ)
+済:タスクを完了にしたとき、期限が過ぎたときの予定の扱い → 消さずに残し、完了したら「済」をつける
+済:同じ予定がすでにカレンダーにあるときの扱い → 時間帯が重なれば書かない(締切は同じ日・同じ名前で比べる)
+済:締切を時刻つきの予定にするか、終日の予定にするか → 締切は終日、時刻は名前に書く</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>F14 シフト表の写真の読み取り</t>
+  </si>
+  <si>
+    <t>アルバイトのシフト表の写真から、自分のシフトを読み取ってカレンダーに書き込む</t>
+  </si>
+  <si>
+    <t>要件定義 追加の要望(シフト表を写真で見せたら自動で書き込みたい)・追加14</t>
+  </si>
+  <si>
+    <t>・写真の読み取りは Claude(Claude Code の claude -p)に任せる。今の Claude Code の契約の範囲で動き、追加の費用はかからない
+・写真は、workbench の画面にドラッグして落とす。落とすとその場で読み取りが始まる
+・シフト表での自分の書かれ方(名字だけ、など)を最初に一度だけ設定しておき、その名前の行(列)だけを読む
+・設定した名前は PC の中の data/ にだけ置き、公開リポジトリに入れない。ほかのスタッフの名前や読み取った結果は、自分の分以外は残さない
+・読み取った結果を一覧で見せ、「書き込む」を押したら書き込む。間違いがあれば、その場で直してから押せる
+・書き込むときは、F13 と同じ決まり(目印・二重登録の防止)で Google カレンダーに書き込む</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:写真をどうやって workbench に渡すか → 画面にドラッグして落とす
+済:写真から「自分のシフト」をどう見分けるか → 自分の書かれ方を最初に設定し、その名前の行だけ読む
+済:読み取った結果を、確認してから書き込むか → 一覧で見せ、確認して「書き込む」を押す</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>F15 開発の中身と進み具合</t>
+  </si>
+  <si>
+    <t>開発の入れ物ごとに、何を作ろうとしているかと、どこまで進んでいるかを出す</t>
+  </si>
+  <si>
+    <t>要件定義 追加の要望(開発が何を作ろうとしていて、どこまで進んでいるかがわかる機能)・追加18</t>
+  </si>
+  <si>
+    <t>・「何を作ろうとしているか」は、そのアプリの README があれば自動で読み、最初の説明の部分を出す
+・README がないときや説明が長すぎるときは、自分で一言書ける。自分で書いた説明があれば、そちらを優先する
+・「どこまで進んでいるか」は、アプリの中に docs/spec-excel-status.md があれば、spec-excel の工程(要件定義〜テスト)のどこにいるかを出す。なければ、自分で選んだ状態(アイデア/作成中/動いている/休止)を出す
+・どちらの場合も、F6 の進み具合(完了したタスクの数 ÷ 全部の数)も並べて出す</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:「どこまで進んでいるか」を何で表すか → spec-excel の工程があればそれ、なければ自分で選んだ状態。F6 の割合も並べる</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -724,7 +840,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -803,11 +919,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -859,8 +1005,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1227,7 +1379,7 @@
         <v>7</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="16.5">
@@ -1648,10 +1800,10 @@
         <v>25</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="54">
@@ -1750,20 +1902,20 @@
       <c r="C6" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>115</v>
+      <c r="D6" s="19" t="s">
+        <v>161</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>48</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G6" s="10" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="115.5">
+    <row r="7" spans="1:7" ht="148.5">
       <c r="A7" s="8"/>
       <c r="B7" s="8" t="s">
         <v>49</v>
@@ -1771,14 +1923,14 @@
       <c r="C7" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>117</v>
+      <c r="D7" s="19" t="s">
+        <v>159</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>48</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>106</v>
@@ -1792,14 +1944,14 @@
       <c r="C8" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>119</v>
+      <c r="D8" s="19" t="s">
+        <v>162</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>48</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G8" s="10" t="s">
         <v>107</v>
@@ -1814,13 +1966,13 @@
         <v>54</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>48</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>108</v>
@@ -1835,13 +1987,13 @@
         <v>56</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>48</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G10" s="10" t="s">
         <v>109</v>
@@ -1856,13 +2008,13 @@
         <v>58</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>48</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>110</v>
@@ -1877,19 +2029,19 @@
         <v>60</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>48</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G12" s="10" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="148.5">
+    <row r="13" spans="1:7" ht="214.5">
       <c r="A13" s="8"/>
       <c r="B13" s="8" t="s">
         <v>61</v>
@@ -1898,13 +2050,13 @@
         <v>62</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>129</v>
+        <v>160</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>48</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>112</v>
@@ -1916,16 +2068,16 @@
         <v>85</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>48</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G14" s="10" t="s">
         <v>113</v>
@@ -1940,57 +2092,122 @@
         <v>87</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>48</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G15" s="10" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.5">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-    </row>
-    <row r="17" spans="1:6" ht="16.5">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-    </row>
-    <row r="18" spans="1:6" ht="16.5">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-    </row>
-    <row r="19" spans="1:6" ht="16.5">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-    </row>
-    <row r="20" spans="1:6" ht="16.5">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
+    <row r="16" spans="1:7" ht="198">
+      <c r="A16" s="19"/>
+      <c r="B16" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="G16" s="24" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="99">
+      <c r="A17" s="19"/>
+      <c r="B17" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G17" s="25" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="379.5">
+      <c r="A18" s="19"/>
+      <c r="B18" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="G18" s="25" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="214.5">
+      <c r="A19" s="19"/>
+      <c r="B19" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="G19" s="25" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="165">
+      <c r="A20" s="19"/>
+      <c r="B20" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="G20" s="25" t="s">
+        <v>185</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="8"/>
@@ -2085,10 +2302,10 @@
         <v>64</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16.5">
@@ -2099,7 +2316,7 @@
         <v>66</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>67</v>
@@ -2166,10 +2383,10 @@
         <v>83</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D12" s="19" t="s">
         <v>82</v>
@@ -2177,72 +2394,72 @@
     </row>
     <row r="13" spans="1:4" ht="16.5">
       <c r="A13" s="19" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="33">
       <c r="A14" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="B14" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="B14" s="19" t="s">
-        <v>153</v>
-      </c>
       <c r="C14" s="19" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="27">
       <c r="A15" s="21" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="20" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="54">
       <c r="A17" s="20" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="27">
@@ -2345,30 +2562,30 @@
     </row>
     <row r="25" spans="1:4" ht="40.5">
       <c r="A25" s="20" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="B26" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B26" s="20" t="s">
-        <v>141</v>
-      </c>
       <c r="C26" s="20" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/docs/requirements-v0.1.xlsx
+++ b/docs/requirements-v0.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Workspace\02_開発\workbench\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B696BD9F-E58E-4074-8491-C5A922E9FD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA0BE996-3FCC-49BA-8739-AC8448B6FB5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="192">
   <si>
     <t>チーム名:</t>
   </si>
@@ -146,9 +146,6 @@
   </si>
   <si>
     <t>目的</t>
-  </si>
-  <si>
-    <t>大学の課題と自分の開発のやることを1か所に集めて、締切の見落としと「次に何をやるか」で迷う時間をなくす。</t>
   </si>
   <si>
     <t>作業台(workbench)</t>
@@ -277,9 +274,6 @@
     <t>端末</t>
   </si>
   <si>
-    <t>Windows 11 の Chrome</t>
-  </si>
-  <si>
     <t>―</t>
   </si>
   <si>
@@ -331,9 +325,6 @@
   </si>
   <si>
     <t>C4 動作環境</t>
-  </si>
-  <si>
-    <t>Windows 11 の PC。Chrome と Outlook アプリ(クラシック版、大学のアカウントでサインイン済み)が入っていること</t>
   </si>
   <si>
     <t>C5 置き場所</t>
@@ -406,13 +397,6 @@
     <t>済:締切を過ぎたタスクをどこに出すか → 一番上に「期限切れ」として出す
 済:締切が同じときの並び順 → 時刻順 → 大学が先 → 登録が古い順
 済(点検で追加):「一目でわかる印」とは何か → 入れ物名のラベル、色は大学と開発の2色</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・記録するものを選んで開始する。入れ物は必ず選び、タスクは選んでも選ばなくてもよい
-・別のものを開始すると、前の記録は自動で止まる
-・記録中の作業と経過時間を、画面の一番上に常に出す
-・PC を閉じた・眠った時刻で、記録を自動で止める。戻ったら画面の一番上に「○○の記録を 12:10 に止めました。再開しますか?」と出し、ボタン1つで再開できる</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -442,14 +426,6 @@
   <si>
     <t>済:タスクが0件の入れ物をどう表示するか → 「タスクなし」と文字で出す
 済:どの画面に出すか → トップは今日・今週にタスクがある入れ物+自分で選んだ入れ物、一覧画面は全部</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・登録したリポジトリのコミットを読む
-・1つのリポジトリに複数のアプリがある場合(lab)は、変更されたフォルダで入れ物に振り分ける
-・同じコミットを二重に取り込まない
-・アプリを起動したときと、10分ごとに読む
-・コミットの時刻に、同じ入れ物の手の記録(F4)が動いていれば、その記録にコミットの内容をくっつける。なければ「その時刻に何をしたか」の点として並べ、作業時間の集計には入れない</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -478,119 +454,315 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
+    <t>済:時間割ファイルを直接読むか、写して持つか → モーニングブリーフの timetable.md を直接読む
+済:学期が変わったときの入れ替え → 自分が Claude に説明し、Claude が変更して、変更の仕方を説明する
+・学期の終わりの日をどこに持つか、米印をいつから出すか(案:1週間前)
+→ 基本設計で決める</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>見れば、次にやることがわかる</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>画面に目をやった瞬間に、大学と開発のやることが締切順に並び、次に手をつけるものが決まる。ずっと開いておく使い方に合わせ、「開いたとき」に限らず、見ればいつでもわかることを大事にする。機能を足すか迷ったら「見た瞬間に次がわかるようになるか」で判断する。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>目的の達成</t>
+  </si>
+  <si>
+    <t>締切の見落としがない</t>
+  </si>
+  <si>
+    <t>2週間のあいだに「期限切れ」に入ったタスクを数え、気づくのが締切より後だったものが0件か確かめる</t>
+  </si>
+  <si>
+    <t>迷う時間がない</t>
+  </si>
+  <si>
+    <t>5回測り、5回とも10秒以内か確かめる</t>
+  </si>
+  <si>
+    <t>タスク100件(Claude の案)を入れた状態で、画面が出てやることが並ぶまでを測る</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>記録中の作業を別のものに切り替えるのが2クリック以内(Claude の案)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>X1 大学からの連絡の取り込み</t>
+  </si>
+  <si>
+    <t>対象外から外し、機能 F9 として作る(要件定義 問8で「X1 だけは実現させたい」と決めた)</t>
+  </si>
+  <si>
+    <t>対象外</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>X2 ほかの学生の利用</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ほかの学生のユーザー登録・ログインは作らない。将来も広げない</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>―</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>X3 スマホ・サーバー公開</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>スマホからの利用と、ネット上のサーバーでの公開はしない</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>X4 チーム・ゼミでの共有</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ほかの人とデータを共有する機能は作らない</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>X5 販売・課金</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>販売や課金はしない</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>X6 学習サイトの読み取り</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>大学の学習サイトに自分のパスワードを持たせて、中身を読み取ることはしない(大学の利用規約に触れるおそれがあるため)。ただし、学習サイトから大学のアドレスで届く通知メールは F9 で読む。メール本文のリンクは画面に出すだけで、サイトを開いてログインするのは自分</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>2026年10月15日</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・タスクは必ず1つの入れ物に入る
+・締切(日付)をつけられる。締切のないタスクも登録できる
+・開発のタスクは、ふだんは締切を空のままにする。面接前のデモなど、必要なときだけつけられる
+・締切には時刻も入れられる(入れなくてもよい)。時刻のあるタスクは、同じ日の中で時刻順に並ぶ
+・毎週の繰り返しを作れる(例:毎週火曜 9:00まで)。1つ完了すると、次の週の分が自動で出る
+・完了にできる</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・入れ物の種類は「大学」「開発」「就活」の3つ
+・タスクと作業記録は、どれか1つの入れ物に入る
+・入れ物は消さずに「終了」にしてしまう。終了にすると一覧とトップ画面から見えなくなり、中身は残る。あとで戻せる
+・完全に消せるのは、中身が空の入れ物だけ
+・学期が終わった授業も「終了」にして片付ける</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>F11 就活</t>
+  </si>
+  <si>
+    <t>就活を入れ物の種類に足し、企業ごとに締切や面接日を管理する</t>
+  </si>
+  <si>
+    <t>要件定義 追加の要望(就活は Google カレンダーや企業からの連絡が見たい)・追加4</t>
+  </si>
+  <si>
+    <t>・入れ物の種類「就活」で、企業ごとに入れ物を1つ作る(エントリーしたときに自分で作る)
+・ES の締切や面接日は、その企業の入れ物のタスクになる
+・企業からの連絡(個人の Gmail)を取り込む。読み方は Google の公式の連携(API)。最初に一度、Google の画面で許可する。許可の鍵は PC の中にだけ置き、公開リポジトリに入れない
+・企業の入れ物に、その企業のメールアドレス(@ から後ろ)を登録できる。差出人が一致したメールと、件名や本文に企業の入れ物の名前が入っているメール(就活サイト経由のもの)を、その企業の入れ物に振り分ける
+・振り分けを間違えたものは自分で入れ物を選び直せる。選び直した結果を覚える(F9 と同じ仕組み)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:企業からのメールをどう見分けるか → アドレスと企業名の両方で見分け、外れたら選び直し、覚える
+済:Gmail をどう読むか → Google の公式の連携(API)。F12・F13 のカレンダーと同じ許可を使う</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>F12 Google カレンダーを見る</t>
+  </si>
+  <si>
+    <t>Google カレンダーの今日の予定を、トップ画面に出す</t>
+  </si>
+  <si>
+    <t>要件定義 追加の要望(Google カレンダーの予定を見たい)・追加7(図で比べた)</t>
+  </si>
+  <si>
+    <t>・F10 の今日の授業と同じ「今日の時間」の列に、今日の予定を混ぜて時刻順に並べる
+・空き時間は書かない
+・読むのは個人の Google アカウントのメインのカレンダーだけ
+・読み方は F11 と同じ Google の公式の連携(API)。読めなかったときは、推測で埋めず「Google に接続できませんでした」と出す</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:どのカレンダーを読むか → 個人のアカウントのメインのカレンダーだけ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>F13 Google カレンダーに書く</t>
+  </si>
+  <si>
+    <t>締切や日時があるものを、Google カレンダーに自動で書き込む</t>
+  </si>
+  <si>
+    <t>要件定義 追加の要望(大学の連絡・面談の通知・課題の締切をカレンダーに自動で書きたい)・F13 は workbench に任せる・追加9</t>
+  </si>
+  <si>
+    <t>・書き込むもの:タスクの締切(大学・就活・締切をつけた開発)、面接・面談、休講・補講、奨学金の手続きなど、締切か日時があるもの
+・「その他」のメールから自動で入ったものは書き込まない
+・面接など日時の決まったものは、時刻つきの予定にする。締切は全部終日の予定にし、時刻は名前に書く(例:「締切 23:59 第10回レポート」)
+・重なる予定があって書かなかったときは、画面に「重なる予定があったので、カレンダーには書きませんでした」と出す
+・書き込み先は、F12 と同じ個人のアカウントのメインのカレンダー
+・workbench が書いた予定には目印をつける。workbench で締切や日時を変えたり、タスクを消したりしたら、目印のある予定だけを書き換え・削除する。自分や他の人が作った予定には一切触れない
+・タスクを完了にしたら、予定は消さずに名前の頭に「済」をつける(例:「済 第10回レポート」)。期限が過ぎて未完了のものは、そのまま残す
+・同じ予定がすでにカレンダーにあれば書き込まない。日時のある予定は、同じ日に時間帯が重なれば名前が違っても同じとみなす。時間帯のない締切は、同じ日に同じ名前なら同じとみなす
+・モーニングブリーフ(gmail-secretary)側の自動登録は止める(二重登録を防ぐため)。止めるのは、F13 が動くようになってから</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:締切や日時が変わったり、タスクを消したりしたとき、カレンダーの予定も直すか → 直す(workbench が書いた予定だけ)
+済:タスクを完了にしたとき、期限が過ぎたときの予定の扱い → 消さずに残し、完了したら「済」をつける
+済:同じ予定がすでにカレンダーにあるときの扱い → 時間帯が重なれば書かない(締切は同じ日・同じ名前で比べる)
+済:締切を時刻つきの予定にするか、終日の予定にするか → 締切は終日、時刻は名前に書く</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>F14 シフト表の写真の読み取り</t>
+  </si>
+  <si>
+    <t>アルバイトのシフト表の写真から、自分のシフトを読み取ってカレンダーに書き込む</t>
+  </si>
+  <si>
+    <t>要件定義 追加の要望(シフト表を写真で見せたら自動で書き込みたい)・追加14</t>
+  </si>
+  <si>
+    <t>・写真の読み取りは Claude(Claude Code の claude -p)に任せる。今の Claude Code の契約の範囲で動き、追加の費用はかからない
+・写真は、workbench の画面にドラッグして落とす。落とすとその場で読み取りが始まる
+・シフト表での自分の書かれ方(名字だけ、など)を最初に一度だけ設定しておき、その名前の行(列)だけを読む
+・設定した名前は PC の中の data/ にだけ置き、公開リポジトリに入れない。ほかのスタッフの名前や読み取った結果は、自分の分以外は残さない
+・読み取った結果を一覧で見せ、「書き込む」を押したら書き込む。間違いがあれば、その場で直してから押せる
+・書き込むときは、F13 と同じ決まり(目印・二重登録の防止)で Google カレンダーに書き込む</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:写真をどうやって workbench に渡すか → 画面にドラッグして落とす
+済:写真から「自分のシフト」をどう見分けるか → 自分の書かれ方を最初に設定し、その名前の行だけ読む
+済:読み取った結果を、確認してから書き込むか → 一覧で見せ、確認して「書き込む」を押す</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>F15 開発の中身と進み具合</t>
+  </si>
+  <si>
+    <t>開発の入れ物ごとに、何を作ろうとしているかと、どこまで進んでいるかを出す</t>
+  </si>
+  <si>
+    <t>要件定義 追加の要望(開発が何を作ろうとしていて、どこまで進んでいるかがわかる機能)・追加18</t>
+  </si>
+  <si>
+    <t>・「何を作ろうとしているか」は、そのアプリの README があれば自動で読み、最初の説明の部分を出す
+・README がないときや説明が長すぎるときは、自分で一言書ける。自分で書いた説明があれば、そちらを優先する
+・「どこまで進んでいるか」は、アプリの中に docs/spec-excel-status.md があれば、spec-excel の工程(要件定義〜テスト)のどこにいるかを出す。なければ、自分で選んだ状態(アイデア/作成中/動いている/休止)を出す
+・どちらの場合も、F6 の進み具合(完了したタスクの数 ÷ 全部の数)も並べて出す</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:「どこまで進んでいるか」を何で表すか → spec-excel の工程があればそれ、なければ自分で選んだ状態。F6 の割合も並べる</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>大学・就活・アルバイトと自分の開発の、やることと予定を1か所に集めて、締切の見落としと「次に何をやるか」で迷う時間をなくす。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・画面の上の方は役割ごとに3段に分ける。1段目:記録中の作業(F4)。2段目:お知らせ(F9・F10・F12 の米印や「読めませんでした」、F4 の再開の確認、F8 の電源が切れていた間の通知など。あるときだけ出す)。3段目:「期限切れ」
+・「期限切れ」には、締切を過ぎたタスクを色を変えてまとめる。完了にするか締切を変えるまで残る
+・その下に、今日の時間(F10・F12)を出す
+・その下に「今日」と「今週」に分けて、締切の近い順に並べる
+・締切のないタスクは、その下に「締切なし」としてまとめて出す
+・同じ締切の日の中は、①時刻があるものは時刻順、時刻なしはその日の最後 ②同じなら大学・就活を開発より先 ③さらに同じなら登録が古い順。「締切なし」の中は登録が古い順
+・各タスクに入れ物の名前のラベル(例:「卒論」「fx-practice」)をつけ、ラベルの色を大学・開発・就活の3色で分ける</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・記録するものを選んで開始する。入れ物は必ず選び、タスクは選んでも選ばなくてもよい
+・別のものを開始すると、前の記録は自動で止まる
+・記録中の作業と経過時間を、画面の上の1段目に常に出す
+・PC を閉じた・眠った時刻で、記録を自動で止める。戻ったら2段目のお知らせに「○○の記録を 12:10 に止めました。再開しますか?」と出し、ボタン1つで再開できる</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
     <t>・モーニングブリーフの時間割(timetable.md)を直接読む。時間割を直すのはこのファイル1か所だけ。公開リポジトリには入れない
 ・時間割の科目を、大学の入れ物として登録する
 ・トップ画面に今日の授業を出す
 ・読めなかったときは、画面に「時間割を読めませんでした」と出す
 ・学期の入れ替えは自動にしない。学期が終わったら、自分が Claude に新しい時間割を説明し、Claude が時間割の書き換えと、終わった授業の入れ物の終了を行う。そのとき Claude は、何をどう変えたか(変更の仕方)を説明する
-・頼み忘れを防ぐため、学期の終わりが近づいたら、トップ画面に「※学期が終わります。時間割の入れ替えを Claude に頼む」と米印つきで出す(案:学期の終わりの1週間前から)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>済:時間割ファイルを直接読むか、写して持つか → モーニングブリーフの timetable.md を直接読む
-済:学期が変わったときの入れ替え → 自分が Claude に説明し、Claude が変更して、変更の仕方を説明する
-・学期の終わりの日をどこに持つか、米印をいつから出すか(案:1週間前)
-→ 基本設計で決める</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>見れば、次にやることがわかる</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>画面に目をやった瞬間に、大学と開発のやることが締切順に並び、次に手をつけるものが決まる。ずっと開いておく使い方に合わせ、「開いたとき」に限らず、見ればいつでもわかることを大事にする。機能を足すか迷ったら「見た瞬間に次がわかるようになるか」で判断する。</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>目的の達成</t>
-  </si>
-  <si>
-    <t>締切の見落としがない</t>
-  </si>
-  <si>
-    <t>2週間使って、締切を過ぎてから気づいた課題が0件</t>
-  </si>
-  <si>
-    <t>2週間のあいだに「期限切れ」に入ったタスクを数え、気づくのが締切より後だったものが0件か確かめる</t>
-  </si>
-  <si>
-    <t>迷う時間がない</t>
-  </si>
-  <si>
-    <t>画面を見てから次の作業を選ぶまで10秒以内</t>
-  </si>
-  <si>
-    <t>5回測り、5回とも10秒以内か確かめる</t>
-  </si>
-  <si>
-    <t>開いてから2秒以内に、今日・今週のやることが出る(Claude の案)。git とメールの読み込みは含めない。画面を先に出し、読み込みは裏で続け、読み込み中は「大学のメールを読み込み中…」と小さく出す</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスク100件(Claude の案)を入れた状態で、画面が出てやることが並ぶまでを測る</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>記録中の作業を別のものに切り替えるのが2クリック以内(Claude の案)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>X1 大学からの連絡の取り込み</t>
-  </si>
-  <si>
-    <t>対象外から外し、機能 F9 として作る(要件定義 問8で「X1 だけは実現させたい」と決めた)</t>
-  </si>
-  <si>
-    <t>対象外</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>X2 ほかの学生の利用</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>ほかの学生のユーザー登録・ログインは作らない。将来も広げない</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>―</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>X3 スマホ・サーバー公開</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>スマホからの利用と、ネット上のサーバーでの公開はしない</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>X4 チーム・ゼミでの共有</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>ほかの人とデータを共有する機能は作らない</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>X5 販売・課金</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>販売や課金はしない</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>X6 学習サイトの読み取り</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>大学の学習サイトに自分のパスワードを持たせて、中身を読み取ることはしない(大学の利用規約に触れるおそれがあるため)。ただし、学習サイトから大学のアドレスで届く通知メールは F9 で読む。メール本文のリンクは画面に出すだけで、サイトを開いてログインするのは自分</t>
+・頼み忘れを防ぐため、学期の終わりが近づいたら、2段目のお知らせに「※学期が終わります。時間割の入れ替えを Claude に頼む」と米印つきで出す(案:学期の終わりの1週間前から)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>開いてから2秒以内(Claude の案)に、今日・今週のやることが出る。git・メール・カレンダーの読み込みは含めない。画面を先に出し、読み込みは裏で続け、読み込み中は2段目のお知らせに「読み込み中」と出す</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>Windows 11 の PC の Chrome(画面の端に置いて、ずっと開いておく)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>Windows 11 の Chrome で、全部の機能を一通り動かす</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>Windows 11 の PC。次がそろっていること:Chrome/Outlook アプリ(クラシック版、大学のアカウントでサインイン済み)/Claude Code(ログイン済み。F14 で使う)/Google アカウントの許可(F11〜F13 で使う)/モーニングブリーフの時間割ファイル timetable.md(F10 で使う)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>2週間使って、締切を過ぎてから気づいた課題が0件(2週間・0件は Claude の案)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>画面を見てから次の作業を選ぶまで10秒以内(10秒・5回は Claude の案)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>Google は決めたことだけ</t>
+  </si>
+  <si>
+    <t>Gmail は読むだけ(送信・削除・既読化をしない)。Google カレンダーは、workbench が書いた目印のある予定だけを作成・書き換え・削除し、自分や他の人が作った予定には触れない。許可の鍵は公開リポジトリに入れない</t>
+  </si>
+  <si>
+    <t>コードに該当する操作が無いこと、目印のない予定を変えないことを確かめる</t>
+  </si>
+  <si>
+    <t>・登録したリポジトリのコミットを読む
+・1つのリポジトリに複数のアプリがある場合(lab)は、変更されたフォルダで入れ物に振り分ける
+・同じコミットを二重に取り込まない
+・アプリを起動したときと、10分ごと(Claude の案)に読む
+・コミットの時刻に、同じ入れ物の手の記録(F4)が動いていれば、その記録にコミットの内容をくっつける。なければ「その時刻に何をしたか」の点として並べ、作業時間の集計には入れない</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・締切の前日に知らせる
+・手つかずのタスクを知らせる。締切のあるタスクは、締切の3日前(Claude の案)になっても作業記録が1つもないとき。締切のないタスクは、登録してから3日間(Claude の案)、作業記録も完了もないとき(開発の締切のないタスクには出さない)
+・「手つかず」はタスクを選んだ作業記録だけで判断する。入れ物だけを選んだ記録は数えない。通知が来たら、その記録にタスクを選び直せば止まる
+・同じ作業記録が2時間(Claude の案)続いたら知らせる(切り替え忘れを防ぐため)
+・画面を閉じていても通知する。PC を起動したら裏の部分が自動で立ち上がる
+・PC の電源が切れていた間の通知は、次に画面を開いたときにまとめて見せる</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>・PC の Outlook アプリ(クラシック版)を読み取り専用で読む(モーニングブリーフと同じ方法)
-・アプリの起動時と10分ごとに読む。Outlook が起動していなければ、裏で立ち上げて読む
+・アプリの起動時と10分ごと(Claude の案)に読む。Outlook が起動していなければ、裏で立ち上げて読む
 ・読めなかったとき(サインイン切れなど)は推測で埋めず、画面に「大学のメールを読めませんでした」と出す
 ・差出人が大学のアドレス(@…kyusan-u.ac.jp)のメールだけを対象にする
 ・その中から「授業」「奨学金」「試合のチケット」の連絡を分けて見せる
@@ -600,158 +772,6 @@
 ・「奨学金」「試合のチケット」は大学の入れ物として自動で作り、授業と同じように扱う
 ・締切が書いてあるメールは、確認なしで自動でタスクにし、「メールから自動で入った」印をつける。間違っていたら1回の操作で消せ、消したものは次に読んだときに復活しない
 ・学習サイトから大学のアドレスで届く通知メールも読む。本文にあるサイトへのリンクを画面に出し、自分でクリックして開ける。アプリがサイトを開くことはしない(X6)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>2026年10月15日</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・タスクは必ず1つの入れ物に入る
-・締切(日付)をつけられる。締切のないタスクも登録できる
-・開発のタスクは、ふだんは締切を空のままにする。面接前のデモなど、必要なときだけつけられる
-・締切には時刻も入れられる(入れなくてもよい)。時刻のあるタスクは、同じ日の中で時刻順に並ぶ
-・毎週の繰り返しを作れる(例:毎週火曜 9:00まで)。1つ完了すると、次の週の分が自動で出る
-・完了にできる</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・締切の前日に知らせる
-・手つかずのタスクを知らせる。締切のあるタスクは、締切の3日前になっても作業記録が1つもないとき。締切のないタスクは、登録してから3日間、作業記録も完了もないとき(開発の締切のないタスクには出さない)
-・「手つかず」はタスクを選んだ作業記録だけで判断する。入れ物だけを選んだ記録は数えない。通知が来たら、その記録にタスクを選び直せば止まる
-・同じ作業記録が2時間続いたら知らせる(切り替え忘れを防ぐため)
-・画面を閉じていても通知する。PC を起動したら裏の部分が自動で立ち上がる
-・PC の電源が切れていた間の通知は、次に画面を開いたときにまとめて見せる</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・入れ物の種類は「大学」「開発」「就活」の3つ
-・タスクと作業記録は、どれか1つの入れ物に入る
-・入れ物は消さずに「終了」にしてしまう。終了にすると一覧とトップ画面から見えなくなり、中身は残る。あとで戻せる
-・完全に消せるのは、中身が空の入れ物だけ
-・学期が終わった授業も「終了」にして片付ける</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・一番上に「期限切れ」として、締切を過ぎたタスクを色を変えてまとめる。完了にするか締切を変えるまで残る
-・その下に「今日」と「今週」に分けて、締切の近い順に並べる
-・締切のないタスクは、その下に「締切なし」としてまとめて出す
-・同じ締切の日の中は、①時刻があるものは時刻順、時刻なしはその日の最後 ②同じなら大学・就活を開発より先 ③さらに同じなら登録が古い順。「締切なし」の中は登録が古い順
-・各タスクに入れ物の名前のラベル(例:「卒論」「fx-practice」)をつけ、ラベルの色を大学・開発・就活の3色で分ける</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>F11 就活</t>
-  </si>
-  <si>
-    <t>就活を入れ物の種類に足し、企業ごとに締切や面接日を管理する</t>
-  </si>
-  <si>
-    <t>要件定義 追加の要望(就活は Google カレンダーや企業からの連絡が見たい)・追加4</t>
-  </si>
-  <si>
-    <t>・入れ物の種類「就活」で、企業ごとに入れ物を1つ作る(エントリーしたときに自分で作る)
-・ES の締切や面接日は、その企業の入れ物のタスクになる
-・企業からの連絡(個人の Gmail)を取り込む。読み方は Google の公式の連携(API)。最初に一度、Google の画面で許可する。許可の鍵は PC の中にだけ置き、公開リポジトリに入れない
-・企業の入れ物に、その企業のメールアドレス(@ から後ろ)を登録できる。差出人が一致したメールと、件名や本文に企業の入れ物の名前が入っているメール(就活サイト経由のもの)を、その企業の入れ物に振り分ける
-・振り分けを間違えたものは自分で入れ物を選び直せる。選び直した結果を覚える(F9 と同じ仕組み)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>済:企業からのメールをどう見分けるか → アドレスと企業名の両方で見分け、外れたら選び直し、覚える
-済:Gmail をどう読むか → Google の公式の連携(API)。F12・F13 のカレンダーと同じ許可を使う</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>F12 Google カレンダーを見る</t>
-  </si>
-  <si>
-    <t>Google カレンダーの今日の予定を、トップ画面に出す</t>
-  </si>
-  <si>
-    <t>要件定義 追加の要望(Google カレンダーの予定を見たい)・追加7(図で比べた)</t>
-  </si>
-  <si>
-    <t>・F10 の今日の授業と同じ「今日の時間」の列に、今日の予定を混ぜて時刻順に並べる
-・空き時間は書かない
-・読むのは個人の Google アカウントのメインのカレンダーだけ
-・読み方は F11 と同じ Google の公式の連携(API)。読めなかったときは、推測で埋めず「Google に接続できませんでした」と出す</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>済:どのカレンダーを読むか → 個人のアカウントのメインのカレンダーだけ</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>F13 Google カレンダーに書く</t>
-  </si>
-  <si>
-    <t>締切や日時があるものを、Google カレンダーに自動で書き込む</t>
-  </si>
-  <si>
-    <t>要件定義 追加の要望(大学の連絡・面談の通知・課題の締切をカレンダーに自動で書きたい)・F13 は workbench に任せる・追加9</t>
-  </si>
-  <si>
-    <t>・書き込むもの:タスクの締切(大学・就活・締切をつけた開発)、面接・面談、休講・補講、奨学金の手続きなど、締切か日時があるもの
-・「その他」のメールから自動で入ったものは書き込まない
-・面接など日時の決まったものは、時刻つきの予定にする。締切は全部終日の予定にし、時刻は名前に書く(例:「締切 23:59 第10回レポート」)
-・重なる予定があって書かなかったときは、画面に「重なる予定があったので、カレンダーには書きませんでした」と出す
-・書き込み先は、F12 と同じ個人のアカウントのメインのカレンダー
-・workbench が書いた予定には目印をつける。workbench で締切や日時を変えたり、タスクを消したりしたら、目印のある予定だけを書き換え・削除する。自分や他の人が作った予定には一切触れない
-・タスクを完了にしたら、予定は消さずに名前の頭に「済」をつける(例:「済 第10回レポート」)。期限が過ぎて未完了のものは、そのまま残す
-・同じ予定がすでにカレンダーにあれば書き込まない。日時のある予定は、同じ日に時間帯が重なれば名前が違っても同じとみなす。時間帯のない締切は、同じ日に同じ名前なら同じとみなす
-・モーニングブリーフ(gmail-secretary)側の自動登録は止める(二重登録を防ぐため)。止めるのは、F13 が動くようになってから</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>済:締切や日時が変わったり、タスクを消したりしたとき、カレンダーの予定も直すか → 直す(workbench が書いた予定だけ)
-済:タスクを完了にしたとき、期限が過ぎたときの予定の扱い → 消さずに残し、完了したら「済」をつける
-済:同じ予定がすでにカレンダーにあるときの扱い → 時間帯が重なれば書かない(締切は同じ日・同じ名前で比べる)
-済:締切を時刻つきの予定にするか、終日の予定にするか → 締切は終日、時刻は名前に書く</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>F14 シフト表の写真の読み取り</t>
-  </si>
-  <si>
-    <t>アルバイトのシフト表の写真から、自分のシフトを読み取ってカレンダーに書き込む</t>
-  </si>
-  <si>
-    <t>要件定義 追加の要望(シフト表を写真で見せたら自動で書き込みたい)・追加14</t>
-  </si>
-  <si>
-    <t>・写真の読み取りは Claude(Claude Code の claude -p)に任せる。今の Claude Code の契約の範囲で動き、追加の費用はかからない
-・写真は、workbench の画面にドラッグして落とす。落とすとその場で読み取りが始まる
-・シフト表での自分の書かれ方(名字だけ、など)を最初に一度だけ設定しておき、その名前の行(列)だけを読む
-・設定した名前は PC の中の data/ にだけ置き、公開リポジトリに入れない。ほかのスタッフの名前や読み取った結果は、自分の分以外は残さない
-・読み取った結果を一覧で見せ、「書き込む」を押したら書き込む。間違いがあれば、その場で直してから押せる
-・書き込むときは、F13 と同じ決まり(目印・二重登録の防止)で Google カレンダーに書き込む</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>済:写真をどうやって workbench に渡すか → 画面にドラッグして落とす
-済:写真から「自分のシフト」をどう見分けるか → 自分の書かれ方を最初に設定し、その名前の行だけ読む
-済:読み取った結果を、確認してから書き込むか → 一覧で見せ、確認して「書き込む」を押す</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>F15 開発の中身と進み具合</t>
-  </si>
-  <si>
-    <t>開発の入れ物ごとに、何を作ろうとしているかと、どこまで進んでいるかを出す</t>
-  </si>
-  <si>
-    <t>要件定義 追加の要望(開発が何を作ろうとしていて、どこまで進んでいるかがわかる機能)・追加18</t>
-  </si>
-  <si>
-    <t>・「何を作ろうとしているか」は、そのアプリの README があれば自動で読み、最初の説明の部分を出す
-・README がないときや説明が長すぎるときは、自分で一言書ける。自分で書いた説明があれば、そちらを優先する
-・「どこまで進んでいるか」は、アプリの中に docs/spec-excel-status.md があれば、spec-excel の工程(要件定義〜テスト)のどこにいるかを出す。なければ、自分で選んだ状態(アイデア/作成中/動いている/休止)を出す
-・どちらの場合も、F6 の進み具合(完了したタスクの数 ÷ 全部の数)も並べて出す</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>済:「どこまで進んでいるか」を何で表すか → spec-excel の工程があればそれ、なければ自分で選んだ状態。F6 の割合も並べる</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1379,7 +1399,7 @@
         <v>7</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="16.5">
@@ -1791,7 +1811,7 @@
         <v>24</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C5" s="8"/>
     </row>
@@ -1800,34 +1820,34 @@
         <v>25</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="54">
       <c r="A7" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>40</v>
+      <c r="B7" s="21" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="54">
       <c r="A8" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="81">
       <c r="A9" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1856,7 +1876,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24">
       <c r="A1" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="16.5">
@@ -1889,324 +1909,324 @@
         <v>31</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="99">
       <c r="A6" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="D6" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>48</v>
-      </c>
       <c r="F6" s="8" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="148.5">
       <c r="A7" s="8"/>
       <c r="B7" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="D7" s="19" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="148.5">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="231">
       <c r="A8" s="8"/>
       <c r="B8" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>52</v>
-      </c>
       <c r="D8" s="19" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="115.5">
       <c r="A9" s="8"/>
       <c r="B9" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>54</v>
-      </c>
       <c r="D9" s="19" t="s">
-        <v>118</v>
+        <v>178</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="82.5">
       <c r="A10" s="8"/>
       <c r="B10" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>56</v>
-      </c>
       <c r="D10" s="19" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="132">
       <c r="A11" s="8"/>
       <c r="B11" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>58</v>
-      </c>
       <c r="D11" s="19" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="132">
       <c r="A12" s="8"/>
       <c r="B12" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>124</v>
+      <c r="D12" s="10" t="s">
+        <v>189</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="214.5">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="231">
       <c r="A13" s="8"/>
       <c r="B13" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>160</v>
+      <c r="D13" s="10" t="s">
+        <v>190</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="409.5">
       <c r="A14" s="8"/>
       <c r="B14" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>157</v>
+        <v>123</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>191</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="214.5">
       <c r="A15" s="8"/>
       <c r="B15" s="8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="198">
       <c r="A16" s="19"/>
       <c r="B16" s="19" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="99">
       <c r="A17" s="19"/>
       <c r="B17" s="19" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="G17" s="25" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="379.5">
       <c r="A18" s="19"/>
       <c r="B18" s="19" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="G18" s="25" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="214.5">
       <c r="A19" s="19"/>
       <c r="B19" s="19" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="165">
       <c r="A20" s="19"/>
       <c r="B20" s="19" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>186</v>
+        <v>172</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>174</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>187</v>
+        <v>47</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>175</v>
       </c>
       <c r="G20" s="25" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -2256,7 +2276,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2296,296 +2316,310 @@
     </row>
     <row r="6" spans="1:4" ht="49.5">
       <c r="A6" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>64</v>
-      </c>
       <c r="C6" s="19" t="s">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16.5">
       <c r="A7" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="C7" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>66</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16.5">
       <c r="A8" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>70</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="16.5">
       <c r="A9" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="D9" s="8" t="s">
         <v>73</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16.5">
       <c r="A10" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="C10" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="D10" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D10" s="8" t="s">
+    </row>
+    <row r="11" spans="1:4" ht="33">
+      <c r="A11" s="8" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="16.5">
-      <c r="A11" s="8" t="s">
+      <c r="B11" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>82</v>
+      <c r="C11" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="33">
       <c r="A12" s="19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="16.5">
       <c r="A13" s="19" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="33">
       <c r="A14" s="19" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="27">
       <c r="A15" s="21" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C16" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="B16" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>154</v>
-      </c>
       <c r="D16" s="20" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="54">
       <c r="A17" s="20" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="27">
       <c r="A18" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B18" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>88</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="B19" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>93</v>
-      </c>
       <c r="D19" s="11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B21" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="54">
+      <c r="A22" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="C21" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="27">
-      <c r="A22" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>99</v>
+      <c r="C22" s="20" t="s">
+        <v>183</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="27">
       <c r="A23" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="40.5">
       <c r="A25" s="20" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>135</v>
+        <v>184</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="27">
       <c r="A26" s="20" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>138</v>
+        <v>185</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>139</v>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="54">
+      <c r="A27" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>188</v>
       </c>
     </row>
   </sheetData>

--- a/docs/requirements-v0.1.xlsx
+++ b/docs/requirements-v0.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Workspace\02_開発\workbench\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA0BE996-3FCC-49BA-8739-AC8448B6FB5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856CDBDD-9B8C-40AF-9CE4-645A8DA2B11A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="208">
   <si>
     <t>チーム名:</t>
   </si>
@@ -203,9 +203,6 @@
   </si>
   <si>
     <t>F6 進み具合</t>
-  </si>
-  <si>
-    <t>入れ物ごとの進み具合を表示する</t>
   </si>
   <si>
     <t>F7 git からの取り込み</t>
@@ -413,19 +410,6 @@
   </si>
   <si>
     <t>済:記録の削除を許すか → 許す(確認つき。消した git の記録は復活しない)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・完了したタスクの数 ÷ 全部のタスクの数
-・タスクが0件の入れ物は、数字やバーを出さずに「タスクなし」と出す
-・トップ画面には、今日・今週にタスクがある入れ物の進み具合を出す
-・入れ物ごとに「トップに出す」を自分で選べる。選んだ入れ物は、タスクがなくてもトップに出る
-・入れ物の一覧画面には、全部の入れ物の進み具合を出す</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>済:タスクが0件の入れ物をどう表示するか → 「タスクなし」と文字で出す
-済:どの画面に出すか → トップは今日・今週にタスクがある入れ物+自分で選んだ入れ物、一覧画面は全部</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -550,15 +534,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>・タスクは必ず1つの入れ物に入る
-・締切(日付)をつけられる。締切のないタスクも登録できる
-・開発のタスクは、ふだんは締切を空のままにする。面接前のデモなど、必要なときだけつけられる
-・締切には時刻も入れられる(入れなくてもよい)。時刻のあるタスクは、同じ日の中で時刻順に並ぶ
-・毎週の繰り返しを作れる(例:毎週火曜 9:00まで)。1つ完了すると、次の週の分が自動で出る
-・完了にできる</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>・入れ物の種類は「大学」「開発」「就活」の3つ
 ・タスクと作業記録は、どれか1つの入れ物に入る
 ・入れ物は消さずに「終了」にしてしまう。終了にすると一覧とトップ画面から見えなくなり、中身は残る。あとで戻せる
@@ -596,13 +571,6 @@
   </si>
   <si>
     <t>要件定義 追加の要望(Google カレンダーの予定を見たい)・追加7(図で比べた)</t>
-  </si>
-  <si>
-    <t>・F10 の今日の授業と同じ「今日の時間」の列に、今日の予定を混ぜて時刻順に並べる
-・空き時間は書かない
-・読むのは個人の Google アカウントのメインのカレンダーだけ
-・読み方は F11 と同じ Google の公式の連携(API)。読めなかったときは、推測で埋めず「Google に接続できませんでした」と出す</t>
-    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>済:どのカレンダーを読むか → 個人のアカウントのメインのカレンダーだけ</t>
@@ -685,16 +653,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>・画面の上の方は役割ごとに3段に分ける。1段目:記録中の作業(F4)。2段目:お知らせ(F9・F10・F12 の米印や「読めませんでした」、F4 の再開の確認、F8 の電源が切れていた間の通知など。あるときだけ出す)。3段目:「期限切れ」
-・「期限切れ」には、締切を過ぎたタスクを色を変えてまとめる。完了にするか締切を変えるまで残る
-・その下に、今日の時間(F10・F12)を出す
-・その下に「今日」と「今週」に分けて、締切の近い順に並べる
-・締切のないタスクは、その下に「締切なし」としてまとめて出す
-・同じ締切の日の中は、①時刻があるものは時刻順、時刻なしはその日の最後 ②同じなら大学・就活を開発より先 ③さらに同じなら登録が古い順。「締切なし」の中は登録が古い順
-・各タスクに入れ物の名前のラベル(例:「卒論」「fx-practice」)をつけ、ラベルの色を大学・開発・就活の3色で分ける</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>・記録するものを選んで開始する。入れ物は必ず選び、タスクは選んでも選ばなくてもよい
 ・別のものを開始すると、前の記録は自動で止まる
 ・記録中の作業と経過時間を、画面の上の1段目に常に出す
@@ -749,15 +707,6 @@
 ・同じコミットを二重に取り込まない
 ・アプリを起動したときと、10分ごと(Claude の案)に読む
 ・コミットの時刻に、同じ入れ物の手の記録(F4)が動いていれば、その記録にコミットの内容をくっつける。なければ「その時刻に何をしたか」の点として並べ、作業時間の集計には入れない</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・締切の前日に知らせる
-・手つかずのタスクを知らせる。締切のあるタスクは、締切の3日前(Claude の案)になっても作業記録が1つもないとき。締切のないタスクは、登録してから3日間(Claude の案)、作業記録も完了もないとき(開発の締切のないタスクには出さない)
-・「手つかず」はタスクを選んだ作業記録だけで判断する。入れ物だけを選んだ記録は数えない。通知が来たら、その記録にタスクを選び直せば止まる
-・同じ作業記録が2時間(Claude の案)続いたら知らせる(切り替え忘れを防ぐため)
-・画面を閉じていても通知する。PC を起動したら裏の部分が自動で立ち上がる
-・PC の電源が切れていた間の通知は、次に画面を開いたときにまとめて見せる</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -773,6 +722,138 @@
 ・締切が書いてあるメールは、確認なしで自動でタスクにし、「メールから自動で入った」印をつける。間違っていたら1回の操作で消せ、消したものは次に読んだときに復活しない
 ・学習サイトから大学のアドレスで届く通知メールも読む。本文にあるサイトへのリンクを画面に出し、自分でクリックして開ける。アプリがサイトを開くことはしない(X6)</t>
     <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・タスクは必ず1つの入れ物に入る
+・締切(日付)をつけられる。締切のないタスクも登録できる
+・開発のタスクは、ふだんは締切を空のままにする。面接前のデモなど、必要なときだけつけられる
+・締切には時刻も入れられる(入れなくてもよい)。時刻のあるタスクは、同じ日の中で時刻順に並ぶ
+・毎週の繰り返しを作れる(例:毎週火曜 9:00まで)。1つ完了すると、次の週の分が自動で出る
+・完了にできる。合図を見つけて自動で完了になる場合は F18
+・入れ物が決まらないタスク(F17 の1行入力で読み取れなかったものなど)は「未分類」の入れ物に入り、「入れ物を選んで」の印がつく。印から1クリックで入れ物を選べる
+・「着手日」(この日から始める)をつけられる(F16)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・一番上に、全体の進み具合のゲージを細く1本出す(F6)
+・その下は役割ごとに3段に分ける。1段目:記録中の作業(F4)。2段目:お知らせ(F9・F10・F12 の米印や「読めませんでした」、F4 の再開の確認、F8 の電源が切れていた間の通知など。あるときだけ出す)。3段目:「期限切れ」
+・「期限切れ」には、締切を過ぎたタスクを色を変えてまとめる。完了にするか締切を変えるまで残る
+・その下に、今日の時間(F10・F12)を出す
+・その下に「今日」と「今週」に分けて、締切の近い順に並べる
+・締切のないタスクは、その下に「締切なし」としてまとめて出す
+・同じ締切の日の中は、①時刻があるものは時刻順、時刻なしはその日の最後 ②同じなら大学・就活を開発より先 ③さらに同じなら登録が古い順。「締切なし」の中は登録が古い順
+・各タスクに入れ物の名前のラベル(例:「卒論」「fx-practice」)をつけ、ラベルの色を大学・開発・就活の3色で分ける</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>入れ物ごと・種類ごと・全体の進み具合を、ゲージで表示する</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・完了したタスクの数 ÷ 全部のタスクの数
+・タスクが0件の入れ物は、数字やバーを出さずに「タスクなし」と出す
+・トップ画面には、今日・今週にタスクがある入れ物の進み具合を出す
+・入れ物ごとに「トップに出す」を自分で選べる。選んだ入れ物は、タスクがなくてもトップに出る
+・入れ物の一覧画面には、全部の入れ物の進み具合を出す
+・進み具合はゲージ(横に伸びるバー)と「○% 完了」で出す
+・入れ物ごとのゲージに加えて、種類ごと(大学・就活・開発)と全体のゲージを出す
+・種類ごと・全体で数えるのは、「終了」にしていない入れ物のタスクだけ
+・トップ画面の一番上に、全体のゲージを細く1本だけ出す。押すと小さな窓が開き、全体と種類ごとの3本が見える(小窓の細かい動きは UI 試作で決める)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:タスクが0件の入れ物をどう表示するか → 「タスクなし」と文字で出す
+済:どの画面に出すか → トップは今日・今週にタスクがある入れ物+自分で選んだ入れ物、一覧画面は全部
+済:全体のゲージを何で出すか → 種類ごと(大学・就活・開発)と全体
+済:種類ごと・全体で何を数えるか → 「終了」にしていない入れ物のタスクだけ
+済:全体と種類ごとのゲージをどこに出すか → トップの一番上に全体を細く1本、押すと小窓で種類ごと</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・締切の前日に知らせる
+・手つかずのタスクを知らせる。締切のあるタスクは、締切の3日前(Claude の案)になっても作業記録が1つもないとき。締切のないタスクは、登録してから3日間(Claude の案)、作業記録も完了もないとき(開発の締切のないタスクには出さない)
+・「手つかず」はタスクを選んだ作業記録だけで判断する。入れ物だけを選んだ記録は数えない。通知が来たら、その記録にタスクを選び直せば止まる
+・同じ作業記録が2時間(Claude の案)続いたら知らせる(切り替え忘れを防ぐため)
+・画面を閉じていても通知する。PC を起動したら裏の部分が自動で立ち上がる
+・PC の電源が切れていた間の通知は、次に画面を開いたときにまとめて見せる
+・着手日(F16)をつけたタスクは、着手日の翌日になっても作業記録が1つもないとき知らせる。締切の3日前の通知もそのまま残す</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・F10 の今日の授業と同じ「今日の時間」の列に、今日の予定を混ぜて時刻順に並べる
+・空き時間は書かない
+・読むのは個人の Google アカウントのメインのカレンダーだけ
+・読み方は F11 と同じ Google の公式の連携(API)。読めなかったときは、推測で埋めず「Google に接続できませんでした」と出す
+・アルバイトの予定は、入れ物を作らず、ここに予定として出す。入れ方は F14 のシフト表の写真か、Google カレンダーへの直接入力</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>F16 着手日</t>
+  </si>
+  <si>
+    <t>タスクに「この日から始める」日をつけ、その日から「今日」に上げる</t>
+  </si>
+  <si>
+    <t>・着手日はつけてもつけなくてもよい
+・着手日の前は、ふだんどおり締切の順で「今日」「今週」などに出す(隠さない)
+・着手日になると「今日」の欄に上がる
+・着手日の翌日になっても作業記録が1つもなければ、F8 で「着手日を過ぎましたが、まだ手をつけていません」と知らせる。締切の3日前の通知もそのまま残す</t>
+  </si>
+  <si>
+    <t>要検討</t>
+  </si>
+  <si>
+    <t>済:着手日の前にどう見せるか → 隠さず、着手日に「今日」へ上げる(図で比べた)
+済:着手日を過ぎても手をつけていないとき → 翌日に知らせる</t>
+  </si>
+  <si>
+    <t>要件定義 機能の提案(別のエージェント)・追加22・24・25</t>
+  </si>
+  <si>
+    <t>F17 1行入力</t>
+  </si>
+  <si>
+    <t>トップ画面の入力欄に1行打つだけで、タスクを登録する</t>
+  </si>
+  <si>
+    <t>・トップ画面の上の方に入力欄を1つ置く
+・打った文字から、締切・入れ物・タスク名を読み取る(例:「金 レポート 卒論」→ 締切:今週の金曜、入れ物:卒論、タスク名:レポート)
+・締切は「金」「10/25」「明日」などの書き方を読む。入れ物は、授業名・企業名など入れ物の名前の一部を読む
+・読み取れなかったときも、その場でタスクにする。入れ物が読めなければ「未分類」に入れて「入れ物を選んで」の印をつける。締切が読めなければ締切なしにする</t>
+  </si>
+  <si>
+    <t>済:何を読み取るか → 締切と入れ物の両方
+済:読み取れなかったとき → すぐ入れて、未分類と印であとから直す(図で比べた)</t>
+  </si>
+  <si>
+    <t>要件定義 機能の提案(別のエージェント)・追加22・26・32</t>
+  </si>
+  <si>
+    <t>F18 自動で完了</t>
+  </si>
+  <si>
+    <t>タスクが終わった合図を見つけて、自動で完了にする</t>
+  </si>
+  <si>
+    <t>・合図は次の4つ
+ ①提出を受け付けたメール(学習サイトの通知メール、企業のエントリー受付メールなど)
+ ②git のコミットのメッセージ(例:「完了: ログイン画面」)
+ ③作業記録を止めたとき
+ ④Claude(claude -p、追加の費用なし)がメールや git の様子を読んで「終わっていそう」と判断したもの
+・①②は、すぐ完了にする
+・③は、記録を止めたときに「このタスクは終わった?」と1回だけ聞き、1クリックで完了にできる
+・④は「終わっていそう」として2段目のお知らせに並べ、自分が「完了」を押す
+・自動で完了にしたタスクには「自動」の印をつけ、1クリックで元に戻せる</t>
+  </si>
+  <si>
+    <t>済:何を合図にするか → 4つ全部
+済:合図を見つけたらすぐ完了にするか → 確かさで分ける(①②はすぐ、③は聞く、④は確認してから)
+・大学の学習サイトが提出受付のメールを送るか(未確認。Outlook のメールを読んで確かめる)
+・メールやコミットを、どのタスクのものと見分けるか
+→ 基本設計で決める</t>
+  </si>
+  <si>
+    <t>要件定義 完了の判断の質問(手動だけだとめんどう)・追加27・28</t>
   </si>
 </sst>
 </file>
@@ -973,7 +1054,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1016,7 +1097,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1398,8 +1485,8 @@
       <c r="F13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="22" t="s">
-        <v>148</v>
+      <c r="G13" s="24" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="16.5">
@@ -1547,7 +1634,7 @@
         <v>22</v>
       </c>
       <c r="D7" s="4"/>
-      <c r="E7" s="23">
+      <c r="E7" s="25">
         <v>46310</v>
       </c>
       <c r="F7" s="4"/>
@@ -1820,18 +1907,18 @@
         <v>25</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="54">
       <c r="A7" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="21" t="s">
-        <v>176</v>
+      <c r="B7" s="23" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="54">
@@ -1839,7 +1926,7 @@
         <v>41</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="81">
@@ -1862,7 +1949,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1909,7 +1996,7 @@
         <v>31</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="99">
@@ -1923,19 +2010,19 @@
         <v>46</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>47</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="148.5">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="214.5">
       <c r="A7" s="8"/>
       <c r="B7" s="8" t="s">
         <v>48</v>
@@ -1943,20 +2030,20 @@
       <c r="C7" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="19" t="s">
-        <v>149</v>
+      <c r="D7" s="10" t="s">
+        <v>185</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>47</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="231">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="247.5">
       <c r="A8" s="8"/>
       <c r="B8" s="8" t="s">
         <v>50</v>
@@ -1964,17 +2051,17 @@
       <c r="C8" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="19" t="s">
-        <v>177</v>
+      <c r="D8" s="10" t="s">
+        <v>186</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>47</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="115.5">
@@ -1986,16 +2073,16 @@
         <v>53</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>47</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="82.5">
@@ -2007,67 +2094,67 @@
         <v>55</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>47</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="132">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="264">
       <c r="A11" s="8"/>
       <c r="B11" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>118</v>
+      <c r="C11" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>188</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="19" t="s">
-        <v>119</v>
+      <c r="F11" s="10" t="s">
+        <v>189</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="132">
       <c r="A12" s="8"/>
       <c r="B12" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>189</v>
+      <c r="D12" s="19" t="s">
+        <v>183</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>47</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="231">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="264">
       <c r="A13" s="8"/>
       <c r="B13" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>60</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>61</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>190</v>
@@ -2076,157 +2163,220 @@
         <v>47</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="409.5">
       <c r="A14" s="8"/>
       <c r="B14" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>191</v>
+        <v>120</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>184</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>47</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="214.5">
       <c r="A15" s="8"/>
       <c r="B15" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>85</v>
-      </c>
       <c r="D15" s="19" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>47</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="198">
       <c r="A16" s="19"/>
       <c r="B16" s="19" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E16" s="19" t="s">
         <v>47</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="G16" s="24" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="99">
+        <v>151</v>
+      </c>
+      <c r="G16" s="26" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="148.5">
       <c r="A17" s="19"/>
       <c r="B17" s="19" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>159</v>
+        <v>153</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>191</v>
       </c>
       <c r="E17" s="19" t="s">
         <v>47</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="G17" s="25" t="s">
-        <v>158</v>
+        <v>155</v>
+      </c>
+      <c r="G17" s="27" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="379.5">
       <c r="A18" s="19"/>
       <c r="B18" s="19" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E18" s="19" t="s">
         <v>47</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="G18" s="25" t="s">
-        <v>163</v>
+        <v>160</v>
+      </c>
+      <c r="G18" s="27" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="214.5">
       <c r="A19" s="19"/>
       <c r="B19" s="19" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E19" s="19" t="s">
         <v>47</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="G19" s="25" t="s">
-        <v>168</v>
+        <v>165</v>
+      </c>
+      <c r="G19" s="27" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="165">
       <c r="A20" s="19"/>
       <c r="B20" s="19" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E20" s="19" t="s">
         <v>47</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="G20" s="25" t="s">
-        <v>173</v>
+        <v>170</v>
+      </c>
+      <c r="G20" s="27" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="94.5">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22" t="s">
+        <v>192</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="121.5">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="189">
+      <c r="A23" s="20"/>
+      <c r="B23" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -2316,310 +2466,310 @@
     </row>
     <row r="6" spans="1:4" ht="49.5">
       <c r="A6" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>63</v>
-      </c>
       <c r="C6" s="19" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16.5">
       <c r="A7" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="C7" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16.5">
       <c r="A8" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>69</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="16.5">
       <c r="A9" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="D9" s="8" t="s">
         <v>72</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16.5">
       <c r="A10" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="C10" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="D10" s="8" t="s">
         <v>76</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="33">
       <c r="A11" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>79</v>
-      </c>
       <c r="C11" s="19" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="33">
       <c r="A12" s="19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="16.5">
       <c r="A13" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="D13" s="19" t="s">
         <v>136</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="33">
       <c r="A14" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="D14" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="B14" s="19" t="s">
+    </row>
+    <row r="15" spans="1:4" ht="27">
+      <c r="A15" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="C15" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="D15" s="23" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="B16" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="D14" s="19" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="27">
-      <c r="A15" s="21" t="s">
+      <c r="C16" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="D16" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="B15" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="C15" s="21" t="s">
+    </row>
+    <row r="17" spans="1:4" ht="54">
+      <c r="A17" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="B17" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="D15" s="21" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="20" t="s">
+      <c r="C17" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="D17" s="21" t="s">
         <v>136</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="54">
-      <c r="A17" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="27">
       <c r="A18" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B18" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="D18" s="11" t="s">
         <v>87</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="C19" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>91</v>
-      </c>
       <c r="D19" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B20" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>93</v>
-      </c>
       <c r="D20" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B21" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="C21" s="11" t="s">
-        <v>95</v>
-      </c>
       <c r="D21" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="54">
       <c r="A22" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>183</v>
+        <v>95</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>177</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="27">
       <c r="A23" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B23" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="C23" s="11" t="s">
-        <v>98</v>
-      </c>
       <c r="D23" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B24" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="C24" s="11" t="s">
-        <v>100</v>
-      </c>
       <c r="D24" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="40.5">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="27">
+      <c r="A26" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="B26" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="B25" s="20" t="s">
+      <c r="C26" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="D26" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="C25" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="27">
-      <c r="A26" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="C26" s="20" t="s">
-        <v>185</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="27" spans="1:4" ht="54">
-      <c r="A27" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="C27" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="D27" s="20" t="s">
-        <v>188</v>
+      <c r="A27" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/docs/requirements-v0.1.xlsx
+++ b/docs/requirements-v0.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Workspace\02_開発\workbench\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856CDBDD-9B8C-40AF-9CE4-645A8DA2B11A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45666FFA-4BF3-4AA1-89DF-7CF263CCF3A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="14190" yWindow="0" windowWidth="14610" windowHeight="7845" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="214">
   <si>
     <t>チーム名:</t>
   </si>
@@ -421,6 +421,373 @@
     <t>済:「手つかず」の決め方と日数 → 締切ありは締切の3日前に記録なし、締切なしは登録から3日間記録なし
 済:「長い」の時間 → 2時間
 済:アプリを閉じているときの通知 → 画面を閉じていても通知する(PC 起動時に自動で立ち上がる)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>大学の Outlook メールから、授業・奨学金・試合のチケット・その他の連絡を取り込む</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:時間割ファイルを直接読むか、写して持つか → モーニングブリーフの timetable.md を直接読む
+済:学期が変わったときの入れ替え → 自分が Claude に説明し、Claude が変更して、変更の仕方を説明する
+・学期の終わりの日をどこに持つか、米印をいつから出すか(案:1週間前)
+→ 基本設計で決める</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>見れば、次にやることがわかる</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>画面に目をやった瞬間に、大学と開発のやることが締切順に並び、次に手をつけるものが決まる。ずっと開いておく使い方に合わせ、「開いたとき」に限らず、見ればいつでもわかることを大事にする。機能を足すか迷ったら「見た瞬間に次がわかるようになるか」で判断する。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>目的の達成</t>
+  </si>
+  <si>
+    <t>締切の見落としがない</t>
+  </si>
+  <si>
+    <t>2週間のあいだに「期限切れ」に入ったタスクを数え、気づくのが締切より後だったものが0件か確かめる</t>
+  </si>
+  <si>
+    <t>迷う時間がない</t>
+  </si>
+  <si>
+    <t>5回測り、5回とも10秒以内か確かめる</t>
+  </si>
+  <si>
+    <t>タスク100件(Claude の案)を入れた状態で、画面が出てやることが並ぶまでを測る</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>記録中の作業を別のものに切り替えるのが2クリック以内(Claude の案)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>X1 大学からの連絡の取り込み</t>
+  </si>
+  <si>
+    <t>対象外から外し、機能 F9 として作る(要件定義 問8で「X1 だけは実現させたい」と決めた)</t>
+  </si>
+  <si>
+    <t>対象外</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>X2 ほかの学生の利用</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ほかの学生のユーザー登録・ログインは作らない。将来も広げない</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>―</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>X3 スマホ・サーバー公開</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>スマホからの利用と、ネット上のサーバーでの公開はしない</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>X4 チーム・ゼミでの共有</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ほかの人とデータを共有する機能は作らない</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>X5 販売・課金</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>販売や課金はしない</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>X6 学習サイトの読み取り</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>大学の学習サイトに自分のパスワードを持たせて、中身を読み取ることはしない(大学の利用規約に触れるおそれがあるため)。ただし、学習サイトから大学のアドレスで届く通知メールは F9 で読む。メール本文のリンクは画面に出すだけで、サイトを開いてログインするのは自分</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>2026年10月15日</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・入れ物の種類は「大学」「開発」「就活」の3つ
+・タスクと作業記録は、どれか1つの入れ物に入る
+・入れ物は消さずに「終了」にしてしまう。終了にすると一覧とトップ画面から見えなくなり、中身は残る。あとで戻せる
+・完全に消せるのは、中身が空の入れ物だけ
+・学期が終わった授業も「終了」にして片付ける</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>F11 就活</t>
+  </si>
+  <si>
+    <t>就活を入れ物の種類に足し、企業ごとに締切や面接日を管理する</t>
+  </si>
+  <si>
+    <t>要件定義 追加の要望(就活は Google カレンダーや企業からの連絡が見たい)・追加4</t>
+  </si>
+  <si>
+    <t>済:企業からのメールをどう見分けるか → アドレスと企業名の両方で見分け、外れたら選び直し、覚える
+済:Gmail をどう読むか → Google の公式の連携(API)。F12・F13 のカレンダーと同じ許可を使う</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>F12 Google カレンダーを見る</t>
+  </si>
+  <si>
+    <t>Google カレンダーの今日の予定を、トップ画面に出す</t>
+  </si>
+  <si>
+    <t>要件定義 追加の要望(Google カレンダーの予定を見たい)・追加7(図で比べた)</t>
+  </si>
+  <si>
+    <t>済:どのカレンダーを読むか → 個人のアカウントのメインのカレンダーだけ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>F13 Google カレンダーに書く</t>
+  </si>
+  <si>
+    <t>締切や日時があるものを、Google カレンダーに自動で書き込む</t>
+  </si>
+  <si>
+    <t>要件定義 追加の要望(大学の連絡・面談の通知・課題の締切をカレンダーに自動で書きたい)・F13 は workbench に任せる・追加9</t>
+  </si>
+  <si>
+    <t>F14 シフト表の写真の読み取り</t>
+  </si>
+  <si>
+    <t>アルバイトのシフト表の写真から、自分のシフトを読み取ってカレンダーに書き込む</t>
+  </si>
+  <si>
+    <t>要件定義 追加の要望(シフト表を写真で見せたら自動で書き込みたい)・追加14</t>
+  </si>
+  <si>
+    <t>・写真の読み取りは Claude(Claude Code の claude -p)に任せる。今の Claude Code の契約の範囲で動き、追加の費用はかからない
+・写真は、workbench の画面にドラッグして落とす。落とすとその場で読み取りが始まる
+・シフト表での自分の書かれ方(名字だけ、など)を最初に一度だけ設定しておき、その名前の行(列)だけを読む
+・設定した名前は PC の中の data/ にだけ置き、公開リポジトリに入れない。ほかのスタッフの名前や読み取った結果は、自分の分以外は残さない
+・読み取った結果を一覧で見せ、「書き込む」を押したら書き込む。間違いがあれば、その場で直してから押せる
+・書き込むときは、F13 と同じ決まり(目印・二重登録の防止)で Google カレンダーに書き込む</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:写真をどうやって workbench に渡すか → 画面にドラッグして落とす
+済:写真から「自分のシフト」をどう見分けるか → 自分の書かれ方を最初に設定し、その名前の行だけ読む
+済:読み取った結果を、確認してから書き込むか → 一覧で見せ、確認して「書き込む」を押す</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>F15 開発の中身と進み具合</t>
+  </si>
+  <si>
+    <t>開発の入れ物ごとに、何を作ろうとしているかと、どこまで進んでいるかを出す</t>
+  </si>
+  <si>
+    <t>要件定義 追加の要望(開発が何を作ろうとしていて、どこまで進んでいるかがわかる機能)・追加18</t>
+  </si>
+  <si>
+    <t>・「何を作ろうとしているか」は、そのアプリの README があれば自動で読み、最初の説明の部分を出す
+・README がないときや説明が長すぎるときは、自分で一言書ける。自分で書いた説明があれば、そちらを優先する
+・「どこまで進んでいるか」は、アプリの中に docs/spec-excel-status.md があれば、spec-excel の工程(要件定義〜テスト)のどこにいるかを出す。なければ、自分で選んだ状態(アイデア/作成中/動いている/休止)を出す
+・どちらの場合も、F6 の進み具合(完了したタスクの数 ÷ 全部の数)も並べて出す</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:「どこまで進んでいるか」を何で表すか → spec-excel の工程があればそれ、なければ自分で選んだ状態。F6 の割合も並べる</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>大学・就活・アルバイトと自分の開発の、やることと予定を1か所に集めて、締切の見落としと「次に何をやるか」で迷う時間をなくす。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・記録するものを選んで開始する。入れ物は必ず選び、タスクは選んでも選ばなくてもよい
+・別のものを開始すると、前の記録は自動で止まる
+・記録中の作業と経過時間を、画面の上の1段目に常に出す
+・PC を閉じた・眠った時刻で、記録を自動で止める。戻ったら2段目のお知らせに「○○の記録を 12:10 に止めました。再開しますか?」と出し、ボタン1つで再開できる</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・モーニングブリーフの時間割(timetable.md)を直接読む。時間割を直すのはこのファイル1か所だけ。公開リポジトリには入れない
+・時間割の科目を、大学の入れ物として登録する
+・トップ画面に今日の授業を出す
+・読めなかったときは、画面に「時間割を読めませんでした」と出す
+・学期の入れ替えは自動にしない。学期が終わったら、自分が Claude に新しい時間割を説明し、Claude が時間割の書き換えと、終わった授業の入れ物の終了を行う。そのとき Claude は、何をどう変えたか(変更の仕方)を説明する
+・頼み忘れを防ぐため、学期の終わりが近づいたら、2段目のお知らせに「※学期が終わります。時間割の入れ替えを Claude に頼む」と米印つきで出す(案:学期の終わりの1週間前から)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>開いてから2秒以内(Claude の案)に、今日・今週のやることが出る。git・メール・カレンダーの読み込みは含めない。画面を先に出し、読み込みは裏で続け、読み込み中は2段目のお知らせに「読み込み中」と出す</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>Windows 11 の PC の Chrome(画面の端に置いて、ずっと開いておく)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>Windows 11 の Chrome で、全部の機能を一通り動かす</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>Windows 11 の PC。次がそろっていること:Chrome/Outlook アプリ(クラシック版、大学のアカウントでサインイン済み)/Claude Code(ログイン済み。F14 で使う)/Google アカウントの許可(F11〜F13 で使う)/モーニングブリーフの時間割ファイル timetable.md(F10 で使う)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>2週間使って、締切を過ぎてから気づいた課題が0件(2週間・0件は Claude の案)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>画面を見てから次の作業を選ぶまで10秒以内(10秒・5回は Claude の案)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>Google は決めたことだけ</t>
+  </si>
+  <si>
+    <t>Gmail は読むだけ(送信・削除・既読化をしない)。Google カレンダーは、workbench が書いた目印のある予定だけを作成・書き換え・削除し、自分や他の人が作った予定には触れない。許可の鍵は公開リポジトリに入れない</t>
+  </si>
+  <si>
+    <t>コードに該当する操作が無いこと、目印のない予定を変えないことを確かめる</t>
+  </si>
+  <si>
+    <t>・登録したリポジトリのコミットを読む
+・1つのリポジトリに複数のアプリがある場合(lab)は、変更されたフォルダで入れ物に振り分ける
+・同じコミットを二重に取り込まない
+・アプリを起動したときと、10分ごと(Claude の案)に読む
+・コミットの時刻に、同じ入れ物の手の記録(F4)が動いていれば、その記録にコミットの内容をくっつける。なければ「その時刻に何をしたか」の点として並べ、作業時間の集計には入れない</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・一番上に、全体の進み具合のゲージを細く1本出す(F6)
+・その下は役割ごとに3段に分ける。1段目:記録中の作業(F4)。2段目:お知らせ(F9・F10・F12 の米印や「読めませんでした」、F4 の再開の確認、F8 の電源が切れていた間の通知など。あるときだけ出す)。3段目:「期限切れ」
+・「期限切れ」には、締切を過ぎたタスクを色を変えてまとめる。完了にするか締切を変えるまで残る
+・その下に、今日の時間(F10・F12)を出す
+・その下に「今日」と「今週」に分けて、締切の近い順に並べる
+・締切のないタスクは、その下に「締切なし」としてまとめて出す
+・同じ締切の日の中は、①時刻があるものは時刻順、時刻なしはその日の最後 ②同じなら大学・就活を開発より先 ③さらに同じなら登録が古い順。「締切なし」の中は登録が古い順
+・各タスクに入れ物の名前のラベル(例:「卒論」「fx-practice」)をつけ、ラベルの色を大学・開発・就活の3色で分ける</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>入れ物ごと・種類ごと・全体の進み具合を、ゲージで表示する</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・完了したタスクの数 ÷ 全部のタスクの数
+・タスクが0件の入れ物は、数字やバーを出さずに「タスクなし」と出す
+・トップ画面には、今日・今週にタスクがある入れ物の進み具合を出す
+・入れ物ごとに「トップに出す」を自分で選べる。選んだ入れ物は、タスクがなくてもトップに出る
+・入れ物の一覧画面には、全部の入れ物の進み具合を出す
+・進み具合はゲージ(横に伸びるバー)と「○% 完了」で出す
+・入れ物ごとのゲージに加えて、種類ごと(大学・就活・開発)と全体のゲージを出す
+・種類ごと・全体で数えるのは、「終了」にしていない入れ物のタスクだけ
+・トップ画面の一番上に、全体のゲージを細く1本だけ出す。押すと小さな窓が開き、全体と種類ごとの3本が見える(小窓の細かい動きは UI 試作で決める)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:タスクが0件の入れ物をどう表示するか → 「タスクなし」と文字で出す
+済:どの画面に出すか → トップは今日・今週にタスクがある入れ物+自分で選んだ入れ物、一覧画面は全部
+済:全体のゲージを何で出すか → 種類ごと(大学・就活・開発)と全体
+済:種類ごと・全体で何を数えるか → 「終了」にしていない入れ物のタスクだけ
+済:全体と種類ごとのゲージをどこに出すか → トップの一番上に全体を細く1本、押すと小窓で種類ごと</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・締切の前日に知らせる
+・手つかずのタスクを知らせる。締切のあるタスクは、締切の3日前(Claude の案)になっても作業記録が1つもないとき。締切のないタスクは、登録してから3日間(Claude の案)、作業記録も完了もないとき(開発の締切のないタスクには出さない)
+・「手つかず」はタスクを選んだ作業記録だけで判断する。入れ物だけを選んだ記録は数えない。通知が来たら、その記録にタスクを選び直せば止まる
+・同じ作業記録が2時間(Claude の案)続いたら知らせる(切り替え忘れを防ぐため)
+・画面を閉じていても通知する。PC を起動したら裏の部分が自動で立ち上がる
+・PC の電源が切れていた間の通知は、次に画面を開いたときにまとめて見せる
+・着手日(F16)をつけたタスクは、着手日の翌日になっても作業記録が1つもないとき知らせる。締切の3日前の通知もそのまま残す</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>F16 着手日</t>
+  </si>
+  <si>
+    <t>タスクに「この日から始める」日をつけ、その日から「今日」に上げる</t>
+  </si>
+  <si>
+    <t>・着手日はつけてもつけなくてもよい
+・着手日の前は、ふだんどおり締切の順で「今日」「今週」などに出す(隠さない)
+・着手日になると「今日」の欄に上がる
+・着手日の翌日になっても作業記録が1つもなければ、F8 で「着手日を過ぎましたが、まだ手をつけていません」と知らせる。締切の3日前の通知もそのまま残す</t>
+  </si>
+  <si>
+    <t>済:着手日の前にどう見せるか → 隠さず、着手日に「今日」へ上げる(図で比べた)
+済:着手日を過ぎても手をつけていないとき → 翌日に知らせる</t>
+  </si>
+  <si>
+    <t>要件定義 機能の提案(別のエージェント)・追加22・24・25</t>
+  </si>
+  <si>
+    <t>F17 1行入力</t>
+  </si>
+  <si>
+    <t>トップ画面の入力欄に1行打つだけで、タスクを登録する</t>
+  </si>
+  <si>
+    <t>・トップ画面の上の方に入力欄を1つ置く
+・打った文字から、締切・入れ物・タスク名を読み取る(例:「金 レポート 卒論」→ 締切:今週の金曜、入れ物:卒論、タスク名:レポート)
+・締切は「金」「10/25」「明日」などの書き方を読む。入れ物は、授業名・企業名など入れ物の名前の一部を読む
+・読み取れなかったときも、その場でタスクにする。入れ物が読めなければ「未分類」に入れて「入れ物を選んで」の印をつける。締切が読めなければ締切なしにする</t>
+  </si>
+  <si>
+    <t>済:何を読み取るか → 締切と入れ物の両方
+済:読み取れなかったとき → すぐ入れて、未分類と印であとから直す(図で比べた)</t>
+  </si>
+  <si>
+    <t>要件定義 機能の提案(別のエージェント)・追加22・26・32</t>
+  </si>
+  <si>
+    <t>F18 自動で完了</t>
+  </si>
+  <si>
+    <t>タスクが終わった合図を見つけて、自動で完了にする</t>
+  </si>
+  <si>
+    <t>・合図は次の4つ
+ ①提出を受け付けたメール(学習サイトの通知メール、企業のエントリー受付メールなど)
+ ②git のコミットのメッセージ(例:「完了: ログイン画面」)
+ ③作業記録を止めたとき
+ ④Claude(claude -p、追加の費用なし)がメールや git の様子を読んで「終わっていそう」と判断したもの
+・①②は、すぐ完了にする
+・③は、記録を止めたときに「このタスクは終わった?」と1回だけ聞き、1クリックで完了にできる
+・④は「終わっていそう」として2段目のお知らせに並べ、自分が「完了」を押す
+・自動で完了にしたタスクには「自動」の印をつけ、1クリックで元に戻せる</t>
+  </si>
+  <si>
+    <t>済:何を合図にするか → 4つ全部
+済:合図を見つけたらすぐ完了にするか → 確かさで分ける(①②はすぐ、③は聞く、④は確認してから)
+・大学の学習サイトが提出受付のメールを送るか(未確認。Outlook のメールを読んで確かめる)
+・メールやコミットを、どのタスクのものと見分けるか
+→ 基本設計で決める</t>
+  </si>
+  <si>
+    <t>要件定義 完了の判断の質問(手動だけだとめんどう)・追加27・28</t>
+  </si>
+  <si>
+    <t>Should</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>Must</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -430,283 +797,20 @@
 済:奨学金・試合のチケットの連絡をどこに出すか → それぞれ大学の入れ物にする
 済:授業への振り分け方 → 科目名で自動、外れたら選び直し、選び直しを覚える
 済:タスクの候補を、確認なしで登録するか → 自動で登録し、印をつけ、1回で消せる
-済:いつ読むか、Outlook が起動していないときの扱い → 起動時と10分ごと。閉じていれば裏で立ち上げる</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>大学の Outlook メールから、授業・奨学金・試合のチケット・その他の連絡を取り込む</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>済:時間割ファイルを直接読むか、写して持つか → モーニングブリーフの timetable.md を直接読む
-済:学期が変わったときの入れ替え → 自分が Claude に説明し、Claude が変更して、変更の仕方を説明する
-・学期の終わりの日をどこに持つか、米印をいつから出すか(案:1週間前)
-→ 基本設計で決める</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>見れば、次にやることがわかる</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>画面に目をやった瞬間に、大学と開発のやることが締切順に並び、次に手をつけるものが決まる。ずっと開いておく使い方に合わせ、「開いたとき」に限らず、見ればいつでもわかることを大事にする。機能を足すか迷ったら「見た瞬間に次がわかるようになるか」で判断する。</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>目的の達成</t>
-  </si>
-  <si>
-    <t>締切の見落としがない</t>
-  </si>
-  <si>
-    <t>2週間のあいだに「期限切れ」に入ったタスクを数え、気づくのが締切より後だったものが0件か確かめる</t>
-  </si>
-  <si>
-    <t>迷う時間がない</t>
-  </si>
-  <si>
-    <t>5回測り、5回とも10秒以内か確かめる</t>
-  </si>
-  <si>
-    <t>タスク100件(Claude の案)を入れた状態で、画面が出てやることが並ぶまでを測る</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>記録中の作業を別のものに切り替えるのが2クリック以内(Claude の案)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>X1 大学からの連絡の取り込み</t>
-  </si>
-  <si>
-    <t>対象外から外し、機能 F9 として作る(要件定義 問8で「X1 だけは実現させたい」と決めた)</t>
-  </si>
-  <si>
-    <t>対象外</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>X2 ほかの学生の利用</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>ほかの学生のユーザー登録・ログインは作らない。将来も広げない</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>―</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>X3 スマホ・サーバー公開</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>スマホからの利用と、ネット上のサーバーでの公開はしない</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>X4 チーム・ゼミでの共有</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>ほかの人とデータを共有する機能は作らない</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>X5 販売・課金</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>販売や課金はしない</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>X6 学習サイトの読み取り</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>大学の学習サイトに自分のパスワードを持たせて、中身を読み取ることはしない(大学の利用規約に触れるおそれがあるため)。ただし、学習サイトから大学のアドレスで届く通知メールは F9 で読む。メール本文のリンクは画面に出すだけで、サイトを開いてログインするのは自分</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>2026年10月15日</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・入れ物の種類は「大学」「開発」「就活」の3つ
-・タスクと作業記録は、どれか1つの入れ物に入る
-・入れ物は消さずに「終了」にしてしまう。終了にすると一覧とトップ画面から見えなくなり、中身は残る。あとで戻せる
-・完全に消せるのは、中身が空の入れ物だけ
-・学期が終わった授業も「終了」にして片付ける</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>F11 就活</t>
-  </si>
-  <si>
-    <t>就活を入れ物の種類に足し、企業ごとに締切や面接日を管理する</t>
-  </si>
-  <si>
-    <t>要件定義 追加の要望(就活は Google カレンダーや企業からの連絡が見たい)・追加4</t>
-  </si>
-  <si>
-    <t>・入れ物の種類「就活」で、企業ごとに入れ物を1つ作る(エントリーしたときに自分で作る)
-・ES の締切や面接日は、その企業の入れ物のタスクになる
-・企業からの連絡(個人の Gmail)を取り込む。読み方は Google の公式の連携(API)。最初に一度、Google の画面で許可する。許可の鍵は PC の中にだけ置き、公開リポジトリに入れない
-・企業の入れ物に、その企業のメールアドレス(@ から後ろ)を登録できる。差出人が一致したメールと、件名や本文に企業の入れ物の名前が入っているメール(就活サイト経由のもの)を、その企業の入れ物に振り分ける
-・振り分けを間違えたものは自分で入れ物を選び直せる。選び直した結果を覚える(F9 と同じ仕組み)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>済:企業からのメールをどう見分けるか → アドレスと企業名の両方で見分け、外れたら選び直し、覚える
-済:Gmail をどう読むか → Google の公式の連携(API)。F12・F13 のカレンダーと同じ許可を使う</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>F12 Google カレンダーを見る</t>
-  </si>
-  <si>
-    <t>Google カレンダーの今日の予定を、トップ画面に出す</t>
-  </si>
-  <si>
-    <t>要件定義 追加の要望(Google カレンダーの予定を見たい)・追加7(図で比べた)</t>
-  </si>
-  <si>
-    <t>済:どのカレンダーを読むか → 個人のアカウントのメインのカレンダーだけ</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>F13 Google カレンダーに書く</t>
-  </si>
-  <si>
-    <t>締切や日時があるものを、Google カレンダーに自動で書き込む</t>
-  </si>
-  <si>
-    <t>要件定義 追加の要望(大学の連絡・面談の通知・課題の締切をカレンダーに自動で書きたい)・F13 は workbench に任せる・追加9</t>
-  </si>
-  <si>
-    <t>・書き込むもの:タスクの締切(大学・就活・締切をつけた開発)、面接・面談、休講・補講、奨学金の手続きなど、締切か日時があるもの
-・「その他」のメールから自動で入ったものは書き込まない
-・面接など日時の決まったものは、時刻つきの予定にする。締切は全部終日の予定にし、時刻は名前に書く(例:「締切 23:59 第10回レポート」)
-・重なる予定があって書かなかったときは、画面に「重なる予定があったので、カレンダーには書きませんでした」と出す
-・書き込み先は、F12 と同じ個人のアカウントのメインのカレンダー
-・workbench が書いた予定には目印をつける。workbench で締切や日時を変えたり、タスクを消したりしたら、目印のある予定だけを書き換え・削除する。自分や他の人が作った予定には一切触れない
-・タスクを完了にしたら、予定は消さずに名前の頭に「済」をつける(例:「済 第10回レポート」)。期限が過ぎて未完了のものは、そのまま残す
-・同じ予定がすでにカレンダーにあれば書き込まない。日時のある予定は、同じ日に時間帯が重なれば名前が違っても同じとみなす。時間帯のない締切は、同じ日に同じ名前なら同じとみなす
-・モーニングブリーフ(gmail-secretary)側の自動登録は止める(二重登録を防ぐため)。止めるのは、F13 が動くようになってから</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>済:締切や日時が変わったり、タスクを消したりしたとき、カレンダーの予定も直すか → 直す(workbench が書いた予定だけ)
-済:タスクを完了にしたとき、期限が過ぎたときの予定の扱い → 消さずに残し、完了したら「済」をつける
-済:同じ予定がすでにカレンダーにあるときの扱い → 時間帯が重なれば書かない(締切は同じ日・同じ名前で比べる)
-済:締切を時刻つきの予定にするか、終日の予定にするか → 締切は終日、時刻は名前に書く</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>F14 シフト表の写真の読み取り</t>
-  </si>
-  <si>
-    <t>アルバイトのシフト表の写真から、自分のシフトを読み取ってカレンダーに書き込む</t>
-  </si>
-  <si>
-    <t>要件定義 追加の要望(シフト表を写真で見せたら自動で書き込みたい)・追加14</t>
-  </si>
-  <si>
-    <t>・写真の読み取りは Claude(Claude Code の claude -p)に任せる。今の Claude Code の契約の範囲で動き、追加の費用はかからない
-・写真は、workbench の画面にドラッグして落とす。落とすとその場で読み取りが始まる
-・シフト表での自分の書かれ方(名字だけ、など)を最初に一度だけ設定しておき、その名前の行(列)だけを読む
-・設定した名前は PC の中の data/ にだけ置き、公開リポジトリに入れない。ほかのスタッフの名前や読み取った結果は、自分の分以外は残さない
-・読み取った結果を一覧で見せ、「書き込む」を押したら書き込む。間違いがあれば、その場で直してから押せる
-・書き込むときは、F13 と同じ決まり(目印・二重登録の防止)で Google カレンダーに書き込む</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>済:写真をどうやって workbench に渡すか → 画面にドラッグして落とす
-済:写真から「自分のシフト」をどう見分けるか → 自分の書かれ方を最初に設定し、その名前の行だけ読む
-済:読み取った結果を、確認してから書き込むか → 一覧で見せ、確認して「書き込む」を押す</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>F15 開発の中身と進み具合</t>
-  </si>
-  <si>
-    <t>開発の入れ物ごとに、何を作ろうとしているかと、どこまで進んでいるかを出す</t>
-  </si>
-  <si>
-    <t>要件定義 追加の要望(開発が何を作ろうとしていて、どこまで進んでいるかがわかる機能)・追加18</t>
-  </si>
-  <si>
-    <t>・「何を作ろうとしているか」は、そのアプリの README があれば自動で読み、最初の説明の部分を出す
-・README がないときや説明が長すぎるときは、自分で一言書ける。自分で書いた説明があれば、そちらを優先する
-・「どこまで進んでいるか」は、アプリの中に docs/spec-excel-status.md があれば、spec-excel の工程(要件定義〜テスト)のどこにいるかを出す。なければ、自分で選んだ状態(アイデア/作成中/動いている/休止)を出す
-・どちらの場合も、F6 の進み具合(完了したタスクの数 ÷ 全部の数)も並べて出す</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>済:「どこまで進んでいるか」を何で表すか → spec-excel の工程があればそれ、なければ自分で選んだ状態。F6 の割合も並べる</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>大学・就活・アルバイトと自分の開発の、やることと予定を1か所に集めて、締切の見落としと「次に何をやるか」で迷う時間をなくす。</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・記録するものを選んで開始する。入れ物は必ず選び、タスクは選んでも選ばなくてもよい
-・別のものを開始すると、前の記録は自動で止まる
-・記録中の作業と経過時間を、画面の上の1段目に常に出す
-・PC を閉じた・眠った時刻で、記録を自動で止める。戻ったら2段目のお知らせに「○○の記録を 12:10 に止めました。再開しますか?」と出し、ボタン1つで再開できる</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・モーニングブリーフの時間割(timetable.md)を直接読む。時間割を直すのはこのファイル1か所だけ。公開リポジトリには入れない
-・時間割の科目を、大学の入れ物として登録する
-・トップ画面に今日の授業を出す
-・読めなかったときは、画面に「時間割を読めませんでした」と出す
-・学期の入れ替えは自動にしない。学期が終わったら、自分が Claude に新しい時間割を説明し、Claude が時間割の書き換えと、終わった授業の入れ物の終了を行う。そのとき Claude は、何をどう変えたか(変更の仕方)を説明する
-・頼み忘れを防ぐため、学期の終わりが近づいたら、2段目のお知らせに「※学期が終わります。時間割の入れ替えを Claude に頼む」と米印つきで出す(案:学期の終わりの1週間前から)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>開いてから2秒以内(Claude の案)に、今日・今週のやることが出る。git・メール・カレンダーの読み込みは含めない。画面を先に出し、読み込みは裏で続け、読み込み中は2段目のお知らせに「読み込み中」と出す</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>Windows 11 の PC の Chrome(画面の端に置いて、ずっと開いておく)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>Windows 11 の Chrome で、全部の機能を一通り動かす</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>Windows 11 の PC。次がそろっていること:Chrome/Outlook アプリ(クラシック版、大学のアカウントでサインイン済み)/Claude Code(ログイン済み。F14 で使う)/Google アカウントの許可(F11〜F13 で使う)/モーニングブリーフの時間割ファイル timetable.md(F10 で使う)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>2週間使って、締切を過ぎてから気づいた課題が0件(2週間・0件は Claude の案)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>画面を見てから次の作業を選ぶまで10秒以内(10秒・5回は Claude の案)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>Google は決めたことだけ</t>
-  </si>
-  <si>
-    <t>Gmail は読むだけ(送信・削除・既読化をしない)。Google カレンダーは、workbench が書いた目印のある予定だけを作成・書き換え・削除し、自分や他の人が作った予定には触れない。許可の鍵は公開リポジトリに入れない</t>
-  </si>
-  <si>
-    <t>コードに該当する操作が無いこと、目印のない予定を変えないことを確かめる</t>
-  </si>
-  <si>
-    <t>・登録したリポジトリのコミットを読む
-・1つのリポジトリに複数のアプリがある場合(lab)は、変更されたフォルダで入れ物に振り分ける
-・同じコミットを二重に取り込まない
-・アプリを起動したときと、10分ごと(Claude の案)に読む
-・コミットの時刻に、同じ入れ物の手の記録(F4)が動いていれば、その記録にコミットの内容をくっつける。なければ「その時刻に何をしたか」の点として並べ、作業時間の集計には入れない</t>
+済:いつ読むか、Outlook が起動していないときの扱い → 起動時と10分ごと。閉じていれば裏で立ち上げる
+済(点検で追加):「その他」のメールから自動で入ったタスクの入れ物 → 未分類に入れて印をつける</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・タスクは必ず1つの入れ物に入る
+・締切(日付)をつけられる。締切のないタスクも登録できる
+・開発のタスクは、ふだんは締切を空のままにする。面接前のデモなど、必要なときだけつけられる
+・締切には時刻も入れられる(入れなくてもよい)。時刻のあるタスクは、同じ日の中で時刻順に並ぶ
+・毎週の繰り返しを作れる(例:毎週火曜 9:00まで)。1つ完了すると、次の週の分が自動で出る
+・完了にできる。合図を見つけて自動で完了になる場合は F18
+・入れ物が決まらないタスク(F17 の1行入力で読み取れなかったものなど)は「未分類」の入れ物に入り、「入れ物を選んで」の印がつく。印から1クリックで入れ物を選べる
+・「着手日」(この日から始める)をつけられる(F16)
+・面接・補講など日時が決まったもの(始まりと終わりの時刻があるもの)は、タスクではなくスケジュール(F19)として持つ</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -720,63 +824,17 @@
 ・振り分けを間違えたものや「その他」に入ったものは、自分で入れ物を選び直せる。選び直した結果を覚え、次から同じ差出人・同じ件名なら、その入れ物に入れる
 ・「奨学金」「試合のチケット」は大学の入れ物として自動で作り、授業と同じように扱う
 ・締切が書いてあるメールは、確認なしで自動でタスクにし、「メールから自動で入った」印をつける。間違っていたら1回の操作で消せ、消したものは次に読んだときに復活しない
-・学習サイトから大学のアドレスで届く通知メールも読む。本文にあるサイトへのリンクを画面に出し、自分でクリックして開ける。アプリがサイトを開くことはしない(X6)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・タスクは必ず1つの入れ物に入る
-・締切(日付)をつけられる。締切のないタスクも登録できる
-・開発のタスクは、ふだんは締切を空のままにする。面接前のデモなど、必要なときだけつけられる
-・締切には時刻も入れられる(入れなくてもよい)。時刻のあるタスクは、同じ日の中で時刻順に並ぶ
-・毎週の繰り返しを作れる(例:毎週火曜 9:00まで)。1つ完了すると、次の週の分が自動で出る
-・完了にできる。合図を見つけて自動で完了になる場合は F18
-・入れ物が決まらないタスク(F17 の1行入力で読み取れなかったものなど)は「未分類」の入れ物に入り、「入れ物を選んで」の印がつく。印から1クリックで入れ物を選べる
-・「着手日」(この日から始める)をつけられる(F16)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・一番上に、全体の進み具合のゲージを細く1本出す(F6)
-・その下は役割ごとに3段に分ける。1段目:記録中の作業(F4)。2段目:お知らせ(F9・F10・F12 の米印や「読めませんでした」、F4 の再開の確認、F8 の電源が切れていた間の通知など。あるときだけ出す)。3段目:「期限切れ」
-・「期限切れ」には、締切を過ぎたタスクを色を変えてまとめる。完了にするか締切を変えるまで残る
-・その下に、今日の時間(F10・F12)を出す
-・その下に「今日」と「今週」に分けて、締切の近い順に並べる
-・締切のないタスクは、その下に「締切なし」としてまとめて出す
-・同じ締切の日の中は、①時刻があるものは時刻順、時刻なしはその日の最後 ②同じなら大学・就活を開発より先 ③さらに同じなら登録が古い順。「締切なし」の中は登録が古い順
-・各タスクに入れ物の名前のラベル(例:「卒論」「fx-practice」)をつけ、ラベルの色を大学・開発・就活の3色で分ける</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>入れ物ごと・種類ごと・全体の進み具合を、ゲージで表示する</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・完了したタスクの数 ÷ 全部のタスクの数
-・タスクが0件の入れ物は、数字やバーを出さずに「タスクなし」と出す
-・トップ画面には、今日・今週にタスクがある入れ物の進み具合を出す
-・入れ物ごとに「トップに出す」を自分で選べる。選んだ入れ物は、タスクがなくてもトップに出る
-・入れ物の一覧画面には、全部の入れ物の進み具合を出す
-・進み具合はゲージ(横に伸びるバー)と「○% 完了」で出す
-・入れ物ごとのゲージに加えて、種類ごと(大学・就活・開発)と全体のゲージを出す
-・種類ごと・全体で数えるのは、「終了」にしていない入れ物のタスクだけ
-・トップ画面の一番上に、全体のゲージを細く1本だけ出す。押すと小さな窓が開き、全体と種類ごとの3本が見える(小窓の細かい動きは UI 試作で決める)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>済:タスクが0件の入れ物をどう表示するか → 「タスクなし」と文字で出す
-済:どの画面に出すか → トップは今日・今週にタスクがある入れ物+自分で選んだ入れ物、一覧画面は全部
-済:全体のゲージを何で出すか → 種類ごと(大学・就活・開発)と全体
-済:種類ごと・全体で何を数えるか → 「終了」にしていない入れ物のタスクだけ
-済:全体と種類ごとのゲージをどこに出すか → トップの一番上に全体を細く1本、押すと小窓で種類ごと</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・締切の前日に知らせる
-・手つかずのタスクを知らせる。締切のあるタスクは、締切の3日前(Claude の案)になっても作業記録が1つもないとき。締切のないタスクは、登録してから3日間(Claude の案)、作業記録も完了もないとき(開発の締切のないタスクには出さない)
-・「手つかず」はタスクを選んだ作業記録だけで判断する。入れ物だけを選んだ記録は数えない。通知が来たら、その記録にタスクを選び直せば止まる
-・同じ作業記録が2時間(Claude の案)続いたら知らせる(切り替え忘れを防ぐため)
-・画面を閉じていても通知する。PC を起動したら裏の部分が自動で立ち上がる
-・PC の電源が切れていた間の通知は、次に画面を開いたときにまとめて見せる
-・着手日(F16)をつけたタスクは、着手日の翌日になっても作業記録が1つもないとき知らせる。締切の3日前の通知もそのまま残す</t>
+・「その他」のメールから自動で入ったタスクは、「未分類」の入れ物に入れ、「入れ物を選んで」の印をつける(F2)
+・学習サイトから大学のアドレスで届く通知メールも読む。本文にあるサイトへのリンクを画面に出し、自分でクリックして開ける。アプリがサイトを開くことはしない(X6)
+・休講・補講の連絡は、その授業の入れ物のスケジュール(F19)にする</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・入れ物の種類「就活」で、企業ごとに入れ物を1つ作る(エントリーしたときに自分で作る)
+・ES の締切は、その企業の入れ物のタスクになる。面接日など日時が決まったものは、その企業の入れ物のスケジュール(F19)になる
+・企業からの連絡(個人の Gmail)を取り込む。読み方は Google の公式の連携(API)。最初に一度、Google の画面で許可する。許可の鍵は PC の中にだけ置き、公開リポジトリに入れない
+・企業の入れ物に、その企業のメールアドレス(@ から後ろ)を登録できる。差出人が一致したメールと、件名や本文に企業の入れ物の名前が入っているメール(就活サイト経由のもの)を、その企業の入れ物に振り分ける
+・振り分けを間違えたものは自分で入れ物を選び直せる。選び直した結果を覚える(F9 と同じ仕組み)</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -784,76 +842,61 @@
 ・空き時間は書かない
 ・読むのは個人の Google アカウントのメインのカレンダーだけ
 ・読み方は F11 と同じ Google の公式の連携(API)。読めなかったときは、推測で埋めず「Google に接続できませんでした」と出す
-・アルバイトの予定は、入れ物を作らず、ここに予定として出す。入れ方は F14 のシフト表の写真か、Google カレンダーへの直接入力</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>F16 着手日</t>
-  </si>
-  <si>
-    <t>タスクに「この日から始める」日をつけ、その日から「今日」に上げる</t>
-  </si>
-  <si>
-    <t>・着手日はつけてもつけなくてもよい
-・着手日の前は、ふだんどおり締切の順で「今日」「今週」などに出す(隠さない)
-・着手日になると「今日」の欄に上がる
-・着手日の翌日になっても作業記録が1つもなければ、F8 で「着手日を過ぎましたが、まだ手をつけていません」と知らせる。締切の3日前の通知もそのまま残す</t>
-  </si>
-  <si>
-    <t>要検討</t>
-  </si>
-  <si>
-    <t>済:着手日の前にどう見せるか → 隠さず、着手日に「今日」へ上げる(図で比べた)
-済:着手日を過ぎても手をつけていないとき → 翌日に知らせる</t>
-  </si>
-  <si>
-    <t>要件定義 機能の提案(別のエージェント)・追加22・24・25</t>
-  </si>
-  <si>
-    <t>F17 1行入力</t>
-  </si>
-  <si>
-    <t>トップ画面の入力欄に1行打つだけで、タスクを登録する</t>
-  </si>
-  <si>
-    <t>・トップ画面の上の方に入力欄を1つ置く
-・打った文字から、締切・入れ物・タスク名を読み取る(例:「金 レポート 卒論」→ 締切:今週の金曜、入れ物:卒論、タスク名:レポート)
-・締切は「金」「10/25」「明日」などの書き方を読む。入れ物は、授業名・企業名など入れ物の名前の一部を読む
-・読み取れなかったときも、その場でタスクにする。入れ物が読めなければ「未分類」に入れて「入れ物を選んで」の印をつける。締切が読めなければ締切なしにする</t>
-  </si>
-  <si>
-    <t>済:何を読み取るか → 締切と入れ物の両方
-済:読み取れなかったとき → すぐ入れて、未分類と印であとから直す(図で比べた)</t>
-  </si>
-  <si>
-    <t>要件定義 機能の提案(別のエージェント)・追加22・26・32</t>
-  </si>
-  <si>
-    <t>F18 自動で完了</t>
-  </si>
-  <si>
-    <t>タスクが終わった合図を見つけて、自動で完了にする</t>
-  </si>
-  <si>
-    <t>・合図は次の4つ
- ①提出を受け付けたメール(学習サイトの通知メール、企業のエントリー受付メールなど)
- ②git のコミットのメッセージ(例:「完了: ログイン画面」)
- ③作業記録を止めたとき
- ④Claude(claude -p、追加の費用なし)がメールや git の様子を読んで「終わっていそう」と判断したもの
-・①②は、すぐ完了にする
-・③は、記録を止めたときに「このタスクは終わった?」と1回だけ聞き、1クリックで完了にできる
-・④は「終わっていそう」として2段目のお知らせに並べ、自分が「完了」を押す
-・自動で完了にしたタスクには「自動」の印をつけ、1クリックで元に戻せる</t>
-  </si>
-  <si>
-    <t>済:何を合図にするか → 4つ全部
-済:合図を見つけたらすぐ完了にするか → 確かさで分ける(①②はすぐ、③は聞く、④は確認してから)
-・大学の学習サイトが提出受付のメールを送るか(未確認。Outlook のメールを読んで確かめる)
-・メールやコミットを、どのタスクのものと見分けるか
-→ 基本設計で決める</t>
-  </si>
-  <si>
-    <t>要件定義 完了の判断の質問(手動だけだとめんどう)・追加27・28</t>
+・アルバイトの予定は、入れ物を作らず、ここに予定として出す。入れ方は F14 のシフト表の写真か、Google カレンダーへの直接入力
+・今日より先の予定は、F19 のスケジュールの画面で見る</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・書き込むもの:タスクの締切(大学・就活・締切をつけた開発)、面接・面談、休講・補講、奨学金の手続きなど、締切か日時があるもの
+・「その他」のメールから自動で入ったものは書き込まない
+・面接など日時の決まったものは、時刻つきの予定にする。締切は全部終日の予定にし、時刻は名前に書く(例:「締切 23:59 第10回レポート」)
+・重なる予定があって書かなかったときは、画面に「重なる予定があったので、カレンダーには書きませんでした」と出す
+・書き込み先は、F12 と同じ個人のアカウントのメインのカレンダー
+・workbench が書いた予定には目印をつける。締切や日時が変わったり、タスクを消したりしたときに、自動で書き換え・削除するのは目印のある予定だけ
+・自分の手で直すときは、F19 のスケジュールの画面から、自分が作った予定を全部直せる。人から招待された予定は、予定ごとのトグルで許したものだけ直せる
+・タスクを完了にしたら、予定は消さずに名前の頭に「済」をつける(例:「済 第10回レポート」)。期限が過ぎて未完了のものは、そのまま残す
+・同じ予定がすでにカレンダーにあれば書き込まない。日時のある予定は、同じ日に時間帯が重なれば名前が違っても同じとみなす。時間帯のない締切は、同じ日に同じ名前なら同じとみなす
+・モーニングブリーフ(gmail-secretary)側の自動登録は止める(二重登録を防ぐため)。止めるのは、F13 が動くようになってから</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:締切や日時が変わったり、タスクを消したりしたとき、カレンダーの予定も直すか → 直す(workbench が書いた予定だけ)
+済:タスクを完了にしたとき、期限が過ぎたときの予定の扱い → 消さずに残し、完了したら「済」をつける
+済:同じ予定がすでにカレンダーにあるときの扱い → 時間帯が重なれば書かない(締切は同じ日・同じ名前で比べる)
+済:締切を時刻つきの予定にするか、終日の予定にするか → 締切は終日、時刻は名前に書く
+済(F19 で変更):自分の手で直せる予定 → 自分が作った予定は全部。招待された予定は、予定ごとのトグルで許したものだけ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>F19 スケジュール</t>
+  </si>
+  <si>
+    <t>Google カレンダーと同じ内容の予定を、workbench の画面で見る・足す・直す</t>
+  </si>
+  <si>
+    <t>・予定の本体は Google カレンダー(個人のアカウントのメインのカレンダー)に置く。workbench の中に別の写しは持たない
+・workbench で予定を足す・直す・消すと、その場で Google カレンダーにも反映する
+・Google カレンダーで足した・直した予定(スマホからも)は、画面を開いたときと10分ごと(Claude の案)に読んで出す
+・時間割の授業(F10)とタスクの締切も、同じ画面にまとめて出す
+・面接・面談・補講・休講など日時が決まったものは、スケジュールとして持つ。入れ物に入るが、完了はなく、進み具合のゲージにも数えない
+・見え方は、ふだんは「一覧」(日付ごとに縦に並ぶ)。「月」を押すと月のマス目に切り替わり、予定は点で出る
+・自分が作った予定は全部直せる。人から招待された予定は見るだけ。予定ごとのトグルで編集を許せる(初めは見るだけ)
+・招待された予定は、主催者が Google 側で変更を許していなければ直せない。そのときは「主催者が変更を許可していないため、直せませんでした」と出す
+・予定を消す前には確認を出す
+・Google に接続できないときは、足す・直すことができない。「Google に接続できませんでした」と出す</t>
+  </si>
+  <si>
+    <t>済:面接・補講など日時が決まったものをどう持つか → タスクとは別のスケジュール(完了なし、ゲージに数えない)
+済:何ができるか → 見る+足す・直す。Google カレンダーと同じ内容になるよう、両方向に反映する
+済:どの予定を編集できるか → 自分が作った予定は全部。招待された予定は予定ごとのトグル
+済:見え方 → 一覧と月の切り替え(図で比べた)
+・月の画面の点の色を何で分けるか
+→ 基本設計で決める
+・編集できる状態の予定につける印
+→ UI 試作で決める</t>
+  </si>
+  <si>
+    <t>要件定義 点検の差4・Google カレンダーのような機能を足したい・追加35〜40</t>
   </si>
 </sst>
 </file>
@@ -1054,7 +1097,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1101,9 +1144,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1485,8 +1525,8 @@
       <c r="F13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="24" t="s">
-        <v>145</v>
+      <c r="G13" s="23" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="16.5">
@@ -1634,7 +1674,7 @@
         <v>22</v>
       </c>
       <c r="D7" s="4"/>
-      <c r="E7" s="25">
+      <c r="E7" s="24">
         <v>46310</v>
       </c>
       <c r="F7" s="4"/>
@@ -1907,18 +1947,18 @@
         <v>25</v>
       </c>
       <c r="B6" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="19" t="s">
         <v>122</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="54">
       <c r="A7" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="23" t="s">
-        <v>171</v>
+      <c r="B7" s="22" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="54">
@@ -1949,7 +1989,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2010,7 +2050,7 @@
         <v>46</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>47</v>
@@ -2022,7 +2062,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="214.5">
+    <row r="7" spans="1:7" ht="247.5">
       <c r="A7" s="8"/>
       <c r="B7" s="8" t="s">
         <v>48</v>
@@ -2031,7 +2071,7 @@
         <v>49</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>47</v>
@@ -2051,8 +2091,8 @@
       <c r="C8" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="10" t="s">
-        <v>186</v>
+      <c r="D8" s="19" t="s">
+        <v>180</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>47</v>
@@ -2073,7 +2113,7 @@
         <v>53</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>47</v>
@@ -2111,17 +2151,17 @@
       <c r="B11" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>188</v>
+      <c r="C11" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>182</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>189</v>
+      <c r="F11" s="19" t="s">
+        <v>183</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>106</v>
@@ -2136,7 +2176,7 @@
         <v>58</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>47</v>
@@ -2156,8 +2196,8 @@
       <c r="C13" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="10" t="s">
-        <v>190</v>
+      <c r="D13" s="19" t="s">
+        <v>184</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>47</v>
@@ -2175,16 +2215,16 @@
         <v>82</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>184</v>
+        <v>119</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>204</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>47</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>119</v>
+        <v>202</v>
       </c>
       <c r="G14" s="10" t="s">
         <v>109</v>
@@ -2199,184 +2239,205 @@
         <v>84</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>47</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G15" s="10" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="198">
+    <row r="16" spans="1:7" ht="231">
       <c r="A16" s="19"/>
       <c r="B16" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C16" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="C16" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>150</v>
+      <c r="D16" s="10" t="s">
+        <v>205</v>
       </c>
       <c r="E16" s="19" t="s">
         <v>47</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="G16" s="26" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="148.5">
+      <c r="G16" s="25" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="165">
       <c r="A17" s="19"/>
       <c r="B17" s="19" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="E17" s="19" t="s">
         <v>47</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="G17" s="27" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="379.5">
+        <v>153</v>
+      </c>
+      <c r="G17" s="26" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="409.5">
       <c r="A18" s="19"/>
       <c r="B18" s="19" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>159</v>
+        <v>155</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>207</v>
       </c>
       <c r="E18" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="F18" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="G18" s="27" t="s">
-        <v>158</v>
+      <c r="F18" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="G18" s="26" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="214.5">
       <c r="A19" s="19"/>
       <c r="B19" s="19" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E19" s="19" t="s">
         <v>47</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="G19" s="27" t="s">
-        <v>163</v>
+        <v>161</v>
+      </c>
+      <c r="G19" s="26" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="165">
       <c r="A20" s="19"/>
       <c r="B20" s="19" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E20" s="19" t="s">
         <v>47</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="G20" s="27" t="s">
-        <v>168</v>
+        <v>166</v>
+      </c>
+      <c r="G20" s="26" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="94.5">
       <c r="A21" s="22"/>
       <c r="B21" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="121.5">
+      <c r="A22" s="21"/>
+      <c r="B22" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="D22" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="E22" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="F22" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="G22" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="E21" s="22" t="s">
+    </row>
+    <row r="23" spans="1:7" ht="189">
+      <c r="A23" s="21"/>
+      <c r="B23" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="F21" s="22" t="s">
+      <c r="C23" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="G21" s="20" t="s">
+      <c r="D23" s="21" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="121.5">
-      <c r="A22" s="20"/>
-      <c r="B22" s="20" t="s">
+      <c r="E23" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="F23" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="G23" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="D22" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="F22" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="G22" s="20" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="189">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>204</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="F23" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="G23" s="20" t="s">
-        <v>207</v>
+    </row>
+    <row r="24" spans="1:7" ht="283.5">
+      <c r="A24" s="20"/>
+      <c r="B24" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>210</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -2472,10 +2533,10 @@
         <v>62</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16.5">
@@ -2486,7 +2547,7 @@
         <v>64</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>65</v>
@@ -2542,10 +2603,10 @@
         <v>78</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="33">
@@ -2553,10 +2614,10 @@
         <v>80</v>
       </c>
       <c r="B12" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="C12" s="19" t="s">
         <v>131</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>132</v>
       </c>
       <c r="D12" s="19" t="s">
         <v>79</v>
@@ -2564,72 +2625,72 @@
     </row>
     <row r="13" spans="1:4" ht="16.5">
       <c r="A13" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="B13" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="C13" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="D13" s="19" t="s">
         <v>135</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="33">
       <c r="A14" s="19" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B14" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="C14" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="D14" s="19" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="27">
+      <c r="A15" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="B15" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D14" s="19" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="27">
-      <c r="A15" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="B15" s="23" t="s">
+      <c r="C15" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="C15" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="D15" s="23" t="s">
-        <v>136</v>
+      <c r="D15" s="22" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="21" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B16" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="C16" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="C16" s="21" t="s">
-        <v>142</v>
-      </c>
       <c r="D16" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="54">
       <c r="A17" s="21" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B17" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="C17" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="C17" s="21" t="s">
-        <v>144</v>
-      </c>
       <c r="D17" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="27">
@@ -2696,7 +2757,7 @@
         <v>95</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>79</v>
@@ -2732,30 +2793,30 @@
     </row>
     <row r="25" spans="1:4" ht="40.5">
       <c r="A25" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="B25" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="C25" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="D25" s="21" t="s">
         <v>125</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="D25" s="21" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="27">
       <c r="A26" s="21" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B26" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="D26" s="21" t="s">
         <v>127</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="54">
@@ -2763,13 +2824,13 @@
         <v>73</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/docs/requirements-v0.1.xlsx
+++ b/docs/requirements-v0.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Workspace\02_開発\workbench\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45666FFA-4BF3-4AA1-89DF-7CF263CCF3A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A58CB0A0-EDFF-4697-9047-A4BE88058E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="14190" yWindow="0" windowWidth="14610" windowHeight="7845" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="219">
   <si>
     <t>チーム名:</t>
   </si>
@@ -38,9 +38,6 @@
   </si>
   <si>
     <t>案 件 名 称</t>
-  </si>
-  <si>
-    <t>大学と開発の一元管理</t>
   </si>
   <si>
     <t>システム名称</t>
@@ -172,9 +169,6 @@
     <t>F1 入れ物の管理</t>
   </si>
   <si>
-    <t>授業と開発プロジェクトを「入れ物」として登録・編集・削除する</t>
-  </si>
-  <si>
     <t>Must</t>
   </si>
   <si>
@@ -187,9 +181,6 @@
     <t>F3 トップ画面</t>
   </si>
   <si>
-    <t>今日・今週やることを、大学と開発を混ぜて締切順に並べる</t>
-  </si>
-  <si>
     <t>F4 作業記録</t>
   </si>
   <si>
@@ -245,9 +236,6 @@
   </si>
   <si>
     <t>公開しないこと</t>
-  </si>
-  <si>
-    <t>作業記録・授業名などのデータは GitHub に上がらない</t>
   </si>
   <si>
     <t>公開リポジトリに data/ が無いことを確かめる</t>
@@ -388,12 +376,6 @@
     <t>済:締切のないタスクを許すか → 許す(トップでは「締切なし」にまとめる)
 済:締切に時刻まで要るか → 締切をつけるときは日付が必須、時刻は任意
 済:毎週出る課題のような繰り返しをどうするか → 毎週の繰り返しだけ作れる</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>済:締切を過ぎたタスクをどこに出すか → 一番上に「期限切れ」として出す
-済:締切が同じときの並び順 → 時刻順 → 大学が先 → 登録が古い順
-済(点検で追加):「一目でわかる印」とは何か → 入れ物名のラベル、色は大学と開発の2色</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -439,17 +421,10 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>画面に目をやった瞬間に、大学と開発のやることが締切順に並び、次に手をつけるものが決まる。ずっと開いておく使い方に合わせ、「開いたとき」に限らず、見ればいつでもわかることを大事にする。機能を足すか迷ったら「見た瞬間に次がわかるようになるか」で判断する。</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>目的の達成</t>
   </si>
   <si>
     <t>締切の見落としがない</t>
-  </si>
-  <si>
-    <t>2週間のあいだに「期限切れ」に入ったタスクを数え、気づくのが締切より後だったものが0件か確かめる</t>
   </si>
   <si>
     <t>迷う時間がない</t>
@@ -539,11 +514,6 @@
   </si>
   <si>
     <t>要件定義 追加の要望(就活は Google カレンダーや企業からの連絡が見たい)・追加4</t>
-  </si>
-  <si>
-    <t>済:企業からのメールをどう見分けるか → アドレスと企業名の両方で見分け、外れたら選び直し、覚える
-済:Gmail をどう読むか → Google の公式の連携(API)。F12・F13 のカレンダーと同じ許可を使う</t>
-    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>F12 Google カレンダーを見る</t>
@@ -601,17 +571,6 @@
     <t>要件定義 追加の要望(開発が何を作ろうとしていて、どこまで進んでいるかがわかる機能)・追加18</t>
   </si>
   <si>
-    <t>・「何を作ろうとしているか」は、そのアプリの README があれば自動で読み、最初の説明の部分を出す
-・README がないときや説明が長すぎるときは、自分で一言書ける。自分で書いた説明があれば、そちらを優先する
-・「どこまで進んでいるか」は、アプリの中に docs/spec-excel-status.md があれば、spec-excel の工程(要件定義〜テスト)のどこにいるかを出す。なければ、自分で選んだ状態(アイデア/作成中/動いている/休止)を出す
-・どちらの場合も、F6 の進み具合(完了したタスクの数 ÷ 全部の数)も並べて出す</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>済:「どこまで進んでいるか」を何で表すか → spec-excel の工程があればそれ、なければ自分で選んだ状態。F6 の割合も並べる</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>大学・就活・アルバイトと自分の開発の、やることと予定を1か所に集めて、締切の見落としと「次に何をやるか」で迷う時間をなくす。</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -648,10 +607,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>2週間使って、締切を過ぎてから気づいた課題が0件(2週間・0件は Claude の案)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>画面を見てから次の作業を選ぶまで10秒以内(10秒・5回は Claude の案)</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -670,17 +625,6 @@
 ・同じコミットを二重に取り込まない
 ・アプリを起動したときと、10分ごと(Claude の案)に読む
 ・コミットの時刻に、同じ入れ物の手の記録(F4)が動いていれば、その記録にコミットの内容をくっつける。なければ「その時刻に何をしたか」の点として並べ、作業時間の集計には入れない</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・一番上に、全体の進み具合のゲージを細く1本出す(F6)
-・その下は役割ごとに3段に分ける。1段目:記録中の作業(F4)。2段目:お知らせ(F9・F10・F12 の米印や「読めませんでした」、F4 の再開の確認、F8 の電源が切れていた間の通知など。あるときだけ出す)。3段目:「期限切れ」
-・「期限切れ」には、締切を過ぎたタスクを色を変えてまとめる。完了にするか締切を変えるまで残る
-・その下に、今日の時間(F10・F12)を出す
-・その下に「今日」と「今週」に分けて、締切の近い順に並べる
-・締切のないタスクは、その下に「締切なし」としてまとめて出す
-・同じ締切の日の中は、①時刻があるものは時刻順、時刻なしはその日の最後 ②同じなら大学・就活を開発より先 ③さらに同じなら登録が古い順。「締切なし」の中は登録が古い順
-・各タスクに入れ物の名前のラベル(例:「卒論」「fx-practice」)をつけ、ラベルの色を大学・開発・就活の3色で分ける</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -791,17 +735,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>済:どのメールを「大学からの連絡」とみなすか → 差出人が大学のアドレスのもの。授業・奨学金・試合のチケットを分けて見せる
-済:3種類に当てはまらない大学のメールをどうするか → 「その他」としてたたんで出す
-済:「学内連絡:」の一斉配信をどこまで拾うか → 3種類以外は全部「その他」に入る
-済:奨学金・試合のチケットの連絡をどこに出すか → それぞれ大学の入れ物にする
-済:授業への振り分け方 → 科目名で自動、外れたら選び直し、選び直しを覚える
-済:タスクの候補を、確認なしで登録するか → 自動で登録し、印をつけ、1回で消せる
-済:いつ読むか、Outlook が起動していないときの扱い → 起動時と10分ごと。閉じていれば裏で立ち上げる
-済(点検で追加):「その他」のメールから自動で入ったタスクの入れ物 → 未分類に入れて印をつける</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>・タスクは必ず1つの入れ物に入る
 ・締切(日付)をつけられる。締切のないタスクも登録できる
 ・開発のタスクは、ふだんは締切を空のままにする。面接前のデモなど、必要なときだけつけられる
@@ -811,6 +744,67 @@
 ・入れ物が決まらないタスク(F17 の1行入力で読み取れなかったものなど)は「未分類」の入れ物に入り、「入れ物を選んで」の印がつく。印から1クリックで入れ物を選べる
 ・「着手日」(この日から始める)をつけられる(F16)
 ・面接・補講など日時が決まったもの(始まりと終わりの時刻があるもの)は、タスクではなくスケジュール(F19)として持つ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・F10 の今日の授業と同じ「今日の時間」の列に、今日の予定を混ぜて時刻順に並べる
+・空き時間は書かない
+・読むのは個人の Google アカウントのメインのカレンダーだけ
+・読み方は F11 と同じ Google の公式の連携(API)。読めなかったときは、推測で埋めず「Google に接続できませんでした」と出す
+・アルバイトの予定は、入れ物を作らず、ここに予定として出す。入れ方は F14 のシフト表の写真か、Google カレンダーへの直接入力
+・今日より先の予定は、F19 のスケジュールの画面で見る</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・書き込むもの:タスクの締切(大学・就活・締切をつけた開発)、面接・面談、休講・補講、奨学金の手続きなど、締切か日時があるもの
+・「その他」のメールから自動で入ったものは書き込まない
+・面接など日時の決まったものは、時刻つきの予定にする。締切は全部終日の予定にし、時刻は名前に書く(例:「締切 23:59 第10回レポート」)
+・重なる予定があって書かなかったときは、画面に「重なる予定があったので、カレンダーには書きませんでした」と出す
+・書き込み先は、F12 と同じ個人のアカウントのメインのカレンダー
+・workbench が書いた予定には目印をつける。締切や日時が変わったり、タスクを消したりしたときに、自動で書き換え・削除するのは目印のある予定だけ
+・自分の手で直すときは、F19 のスケジュールの画面から、自分が作った予定を全部直せる。人から招待された予定は、予定ごとのトグルで許したものだけ直せる
+・タスクを完了にしたら、予定は消さずに名前の頭に「済」をつける(例:「済 第10回レポート」)。期限が過ぎて未完了のものは、そのまま残す
+・同じ予定がすでにカレンダーにあれば書き込まない。日時のある予定は、同じ日に時間帯が重なれば名前が違っても同じとみなす。時間帯のない締切は、同じ日に同じ名前なら同じとみなす
+・モーニングブリーフ(gmail-secretary)側の自動登録は止める(二重登録を防ぐため)。止めるのは、F13 が動くようになってから</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:締切や日時が変わったり、タスクを消したりしたとき、カレンダーの予定も直すか → 直す(workbench が書いた予定だけ)
+済:タスクを完了にしたとき、期限が過ぎたときの予定の扱い → 消さずに残し、完了したら「済」をつける
+済:同じ予定がすでにカレンダーにあるときの扱い → 時間帯が重なれば書かない(締切は同じ日・同じ名前で比べる)
+済:締切を時刻つきの予定にするか、終日の予定にするか → 締切は終日、時刻は名前に書く
+済(F19 で変更):自分の手で直せる予定 → 自分が作った予定は全部。招待された予定は、予定ごとのトグルで許したものだけ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>F19 スケジュール</t>
+  </si>
+  <si>
+    <t>Google カレンダーと同じ内容の予定を、workbench の画面で見る・足す・直す</t>
+  </si>
+  <si>
+    <t>済:面接・補講など日時が決まったものをどう持つか → タスクとは別のスケジュール(完了なし、ゲージに数えない)
+済:何ができるか → 見る+足す・直す。Google カレンダーと同じ内容になるよう、両方向に反映する
+済:どの予定を編集できるか → 自分が作った予定は全部。招待された予定は予定ごとのトグル
+済:見え方 → 一覧と月の切り替え(図で比べた)
+・月の画面の点の色を何で分けるか
+→ 基本設計で決める
+・編集できる状態の予定につける印
+→ UI 試作で決める</t>
+  </si>
+  <si>
+    <t>要件定義 点検の差4・Google カレンダーのような機能を足したい・追加35〜40</t>
+  </si>
+  <si>
+    <t>・一番上に、全体の進み具合のゲージを細く1本出す(F6)
+・その下は役割ごとに3段に分ける。1段目:記録中の作業(F4)。2段目:お知らせ(あるときだけ出す)。3段目:「期限切れ」
+・2段目に出すものは次の9つ:①作業記録の再開の確認(F4)②PC の電源が切れていた間の通知(F8)③学期の終わりの米印(F10)④読めなかった・つながらなかった(F9・F10・F11・F12・F19)⑤読み込み中(非機能要件)⑥カレンダーに書かなかった予定(F13)⑦新しい連絡の件数(F9・F11)⑧「終わっていそう」なタスクの件数(F18)⑨未分類の件数(F2)
+・「期限切れ」には、締切を過ぎたタスクを色を変えてまとめる。完了にするか締切を変えるまで残る
+・その下に、今日の時間(F10・F12)を出す
+・その下に「今日」と「今週」に分けて、締切の近い順に並べる
+・締切のないタスクは、その下に「締切なし」としてまとめて出す
+・同じ締切の日の中は、①時刻があるものは時刻順、時刻なしはその日の最後 ②同じなら大学・就活を開発より先 ③さらに同じなら登録が古い順。「締切なし」の中は登録が古い順
+・各タスクに入れ物の名前のラベル(例:「卒論」「fx-practice」)をつけ、ラベルの色を大学・開発・就活の3色で分ける</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -826,7 +820,20 @@
 ・締切が書いてあるメールは、確認なしで自動でタスクにし、「メールから自動で入った」印をつける。間違っていたら1回の操作で消せ、消したものは次に読んだときに復活しない
 ・「その他」のメールから自動で入ったタスクは、「未分類」の入れ物に入れ、「入れ物を選んで」の印をつける(F2)
 ・学習サイトから大学のアドレスで届く通知メールも読む。本文にあるサイトへのリンクを画面に出し、自分でクリックして開ける。アプリがサイトを開くことはしない(X6)
-・休講・補講の連絡は、その授業の入れ物のスケジュール(F19)にする</t>
+・休講・補講の連絡は、その授業の入れ物のスケジュール(F19)にする
+・取り込んだ連絡は「連絡」の画面で、授業・奨学金・試合のチケット・企業・その他に分けて見る。トップには2段目に「新しい連絡 ○件」と件数だけ出し、押すと「連絡」の画面が開く。開いたら件数は0に戻る(「見た」は workbench の中だけで覚え、メールの既読には触らない)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:どのメールを「大学からの連絡」とみなすか → 差出人が大学のアドレスのもの。授業・奨学金・試合のチケットを分けて見せる
+済:3種類に当てはまらない大学のメールをどうするか → 「その他」としてたたんで出す
+済:「学内連絡:」の一斉配信をどこまで拾うか → 3種類以外は全部「その他」に入る
+済:奨学金・試合のチケットの連絡をどこに出すか → それぞれ大学の入れ物にする
+済:授業への振り分け方 → 科目名で自動、外れたら選び直し、選び直しを覚える
+済:タスクの候補を、確認なしで登録するか → 自動で登録し、印をつけ、1回で消せる
+済:いつ読むか、Outlook が起動していないときの扱い → 起動時と10分ごと。閉じていれば裏で立ち上げる
+済(点検で追加):「その他」のメールから自動で入ったタスクの入れ物 → 未分類に入れて印をつける
+済(点検で追加):取り込んだ連絡をどこで見るか → 「連絡」の画面。トップは2段目に件数だけ</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -834,69 +841,97 @@
 ・ES の締切は、その企業の入れ物のタスクになる。面接日など日時が決まったものは、その企業の入れ物のスケジュール(F19)になる
 ・企業からの連絡(個人の Gmail)を取り込む。読み方は Google の公式の連携(API)。最初に一度、Google の画面で許可する。許可の鍵は PC の中にだけ置き、公開リポジトリに入れない
 ・企業の入れ物に、その企業のメールアドレス(@ から後ろ)を登録できる。差出人が一致したメールと、件名や本文に企業の入れ物の名前が入っているメール(就活サイト経由のもの)を、その企業の入れ物に振り分ける
-・振り分けを間違えたものは自分で入れ物を選び直せる。選び直した結果を覚える(F9 と同じ仕組み)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・F10 の今日の授業と同じ「今日の時間」の列に、今日の予定を混ぜて時刻順に並べる
-・空き時間は書かない
-・読むのは個人の Google アカウントのメインのカレンダーだけ
-・読み方は F11 と同じ Google の公式の連携(API)。読めなかったときは、推測で埋めず「Google に接続できませんでした」と出す
-・アルバイトの予定は、入れ物を作らず、ここに予定として出す。入れ方は F14 のシフト表の写真か、Google カレンダーへの直接入力
-・今日より先の予定は、F19 のスケジュールの画面で見る</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・書き込むもの:タスクの締切(大学・就活・締切をつけた開発)、面接・面談、休講・補講、奨学金の手続きなど、締切か日時があるもの
-・「その他」のメールから自動で入ったものは書き込まない
-・面接など日時の決まったものは、時刻つきの予定にする。締切は全部終日の予定にし、時刻は名前に書く(例:「締切 23:59 第10回レポート」)
-・重なる予定があって書かなかったときは、画面に「重なる予定があったので、カレンダーには書きませんでした」と出す
-・書き込み先は、F12 と同じ個人のアカウントのメインのカレンダー
-・workbench が書いた予定には目印をつける。締切や日時が変わったり、タスクを消したりしたときに、自動で書き換え・削除するのは目印のある予定だけ
-・自分の手で直すときは、F19 のスケジュールの画面から、自分が作った予定を全部直せる。人から招待された予定は、予定ごとのトグルで許したものだけ直せる
-・タスクを完了にしたら、予定は消さずに名前の頭に「済」をつける(例:「済 第10回レポート」)。期限が過ぎて未完了のものは、そのまま残す
-・同じ予定がすでにカレンダーにあれば書き込まない。日時のある予定は、同じ日に時間帯が重なれば名前が違っても同じとみなす。時間帯のない締切は、同じ日に同じ名前なら同じとみなす
-・モーニングブリーフ(gmail-secretary)側の自動登録は止める(二重登録を防ぐため)。止めるのは、F13 が動くようになってから</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>済:締切や日時が変わったり、タスクを消したりしたとき、カレンダーの予定も直すか → 直す(workbench が書いた予定だけ)
-済:タスクを完了にしたとき、期限が過ぎたときの予定の扱い → 消さずに残し、完了したら「済」をつける
-済:同じ予定がすでにカレンダーにあるときの扱い → 時間帯が重なれば書かない(締切は同じ日・同じ名前で比べる)
-済:締切を時刻つきの予定にするか、終日の予定にするか → 締切は終日、時刻は名前に書く
-済(F19 で変更):自分の手で直せる予定 → 自分が作った予定は全部。招待された予定は、予定ごとのトグルで許したものだけ</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>F19 スケジュール</t>
-  </si>
-  <si>
-    <t>Google カレンダーと同じ内容の予定を、workbench の画面で見る・足す・直す</t>
+・振り分けを間違えたものは自分で入れ物を選び直せる。選び直した結果を覚える(F9 と同じ仕組み)
+・企業からの連絡は、F9 と同じ「連絡」の画面に「企業」として出す
+・Gmail は、アプリの起動時と10分ごと(Claude の案)に読む(F9 と同じ)
+・読めなかったとき(許可切れなど)は推測で埋めず、画面に「Gmail を読めませんでした」と出す
+・企業の入れ物に振り分けたメールに締切が書いてあれば、確認なしで自動でタスクに、面接日などの日時があれば自動でスケジュールにし、「メールから自動で入った」印をつける。間違っていたら1回の操作で消せ、消したものは次に読んだときに復活しない(F9 と同じ)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:企業からのメールをどう見分けるか → アドレスと企業名の両方で見分け、外れたら選び直し、覚える
+済:Gmail をどう読むか → Google の公式の連携(API)。F12・F13 のカレンダーと同じ許可を使う
+済(点検で追加):いつ読むか、読めなかったとき、締切や面接日の扱い → 3つとも F9 と同じ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>2週間使って、締切を過ぎても完了していないタスクが0件(2週間・0件は Claude の案)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>2週間のあいだに「期限切れ」の欄に入ったタスクを数え、0件か確かめる。わざと遅らせるタスクは、締切を先に直しておく</t>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>・予定の本体は Google カレンダー(個人のアカウントのメインのカレンダー)に置く。workbench の中に別の写しは持たない
 ・workbench で予定を足す・直す・消すと、その場で Google カレンダーにも反映する
 ・Google カレンダーで足した・直した予定(スマホからも)は、画面を開いたときと10分ごと(Claude の案)に読んで出す
 ・時間割の授業(F10)とタスクの締切も、同じ画面にまとめて出す
-・面接・面談・補講・休講など日時が決まったものは、スケジュールとして持つ。入れ物に入るが、完了はなく、進み具合のゲージにも数えない
+・面接・面談・補講・休講など日時が決まったものは、スケジュールとして持つ。完了はなく、進み具合のゲージにも数えない
+・スケジュールは入れ物に入れられる(企業の面接はその企業の入れ物など)。入れ物なしでも持てる(アルバイトの面接 F20、Google カレンダーで足した予定など)
 ・見え方は、ふだんは「一覧」(日付ごとに縦に並ぶ)。「月」を押すと月のマス目に切り替わり、予定は点で出る
 ・自分が作った予定は全部直せる。人から招待された予定は見るだけ。予定ごとのトグルで編集を許せる(初めは見るだけ)
 ・招待された予定は、主催者が Google 側で変更を許していなければ直せない。そのときは「主催者が変更を許可していないため、直せませんでした」と出す
 ・予定を消す前には確認を出す
 ・Google に接続できないときは、足す・直すことができない。「Google に接続できませんでした」と出す</t>
-  </si>
-  <si>
-    <t>済:面接・補講など日時が決まったものをどう持つか → タスクとは別のスケジュール(完了なし、ゲージに数えない)
-済:何ができるか → 見る+足す・直す。Google カレンダーと同じ内容になるよう、両方向に反映する
-済:どの予定を編集できるか → 自分が作った予定は全部。招待された予定は予定ごとのトグル
-済:見え方 → 一覧と月の切り替え(図で比べた)
-・月の画面の点の色を何で分けるか
-→ 基本設計で決める
-・編集できる状態の予定につける印
-→ UI 試作で決める</t>
-  </si>
-  <si>
-    <t>要件定義 点検の差4・Google カレンダーのような機能を足したい・追加35〜40</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>F20 アルバイトの面接</t>
+  </si>
+  <si>
+    <t>アルバイトの面接のメールを Gmail から拾い、スケジュールに入れる</t>
+  </si>
+  <si>
+    <t>・応募したバイト先の名前とメールアドレス(@ から後ろ)を、一覧に登録しておく。入れ物は作らない
+・Gmail の読み方・読めなかったときの扱いは F11 と同じ
+・登録したバイト先から届いたメールに面接の日時があれば、自動で入れ物なしのスケジュール(F19)にし、「メールから自動で入った」印をつける。間違っていたら1回の操作で消せ、消したものは次に読んだときに復活しない
+・バイト先からの連絡は、「連絡」の画面(F9)に「アルバイト」として出す</t>
+  </si>
+  <si>
+    <t>済:どう見分けて、どこに入れるか → バイト先を一覧に登録して見分け、入れ物なしのスケジュールに入れる</t>
+  </si>
+  <si>
+    <t>要件定義 Gmail でアルバイトの面接も取り上げたい・追加45</t>
+  </si>
+  <si>
+    <t>画面に目をやった瞬間に、大学・就活・アルバイトと開発のやることと予定が並び、次に手をつけるものが決まる。ずっと開いておく使い方に合わせ、「開いたとき」に限らず、見ればいつでもわかることを大事にする。機能を足すか迷ったら「見た瞬間に次がわかるようになるか」で判断する。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>大学の授業・就活の企業・開発プロジェクトを「入れ物」として登録・編集・削除する</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>今日・今週やることを、大学・就活・開発を混ぜて締切順に並べる</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:締切を過ぎたタスクをどこに出すか → 一番上に「期限切れ」として出す
+済:締切が同じときの並び順 → 時刻順 → 大学・就活が先 → 登録が古い順(F11 で就活を足したときに直した)
+済(点検で追加):「一目でわかる印」とは何か → 入れ物名のラベル、色は大学・開発・就活の3色(F11 で就活を足したときに直した)
+済(点検で追加):2段目に何を出すか → 9つに決めた</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・「何を作ろうとしているか」は、そのアプリの README があれば自動で読み、一番上の見出しのすぐ下の段落(空行まで)を出す。100文字(Claude の案)を超えたら、100文字で切って「…」をつける
+・README がないときや、その段落がないときは、自分で一言書ける。自分で書いた説明があれば、そちらを優先する
+・「どこまで進んでいるか」は、アプリの中に docs/spec-excel-status.md があれば、spec-excel の工程(要件定義〜テスト)のどこにいるかを出す。なければ、自分で選んだ状態(アイデア/作成中/動いている/休止)を出す
+・どちらの場合も、F6 の進み具合(完了したタスクの数 ÷ 全部の数)も並べて出す</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:「どこまで進んでいるか」を何で表すか → spec-excel の工程があればそれ、なければ自分で選んだ状態。F6 の割合も並べる
+済(点検で追加):README のどこを説明として出すか → 一番上の見出しのすぐ下の段落。100文字を超えたら切る</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>data/ に置く個人のデータ(作業記録・タスク・入れ物の名前・取り込んだメール・設定)は、どれも GitHub に上がらない</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>大学・就活・アルバイトと開発の一元管理</t>
+    <phoneticPr fontId="8"/>
   </si>
 </sst>
 </file>
@@ -1097,7 +1132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1140,9 +1175,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1159,6 +1191,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1499,21 +1537,21 @@
       <c r="C8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
+      <c r="E8" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
     </row>
     <row r="10" spans="1:10" ht="19.5">
       <c r="C10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="13" t="s">
         <v>5</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>6</v>
       </c>
       <c r="F10" s="14"/>
       <c r="G10" s="14"/>
@@ -1523,42 +1561,42 @@
     </row>
     <row r="13" spans="1:10" ht="37.5">
       <c r="F13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G13" s="23" t="s">
-        <v>144</v>
+        <v>6</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="16.5">
       <c r="E15" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="12"/>
       <c r="H15" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I15" s="12"/>
       <c r="J15" s="12"/>
     </row>
     <row r="16" spans="1:10" ht="16.5">
       <c r="E16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="H16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="17" spans="5:10" ht="45.95" customHeight="1">
@@ -1604,39 +1642,39 @@
   <sheetData>
     <row r="1" spans="1:9" ht="24">
       <c r="A1" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="16.5">
       <c r="A2" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="16.5">
       <c r="A3" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="C5" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="D5" s="16" t="s">
         <v>18</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>19</v>
       </c>
       <c r="E5" s="18"/>
       <c r="F5" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G5" s="18"/>
       <c r="H5" s="16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I5" s="18"/>
     </row>
@@ -1645,22 +1683,22 @@
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
       <c r="D6" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="16.5">
@@ -1668,13 +1706,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>22</v>
-      </c>
       <c r="D7" s="4"/>
-      <c r="E7" s="24">
+      <c r="E7" s="23">
         <v>46310</v>
       </c>
       <c r="F7" s="4"/>
@@ -1920,61 +1958,61 @@
   <sheetData>
     <row r="1" spans="1:3" ht="24">
       <c r="A1" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16.5">
       <c r="A2" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="16.5">
       <c r="A3" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="36" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" s="8"/>
     </row>
     <row r="6" spans="1:3" ht="36" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="54">
       <c r="A7" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>167</v>
+        <v>38</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="54">
       <c r="A8" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="81">
       <c r="A9" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>43</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1989,7 +2027,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2003,441 +2041,462 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24">
       <c r="A1" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="16.5">
       <c r="A2" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="16.5">
       <c r="A3" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="16.5">
       <c r="A5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>31</v>
-      </c>
       <c r="G5" s="7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="99">
       <c r="A6" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>47</v>
-      </c>
       <c r="F6" s="8" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="247.5">
       <c r="A7" s="8"/>
       <c r="B7" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>203</v>
+        <v>47</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>190</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="247.5">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="313.5">
       <c r="A8" s="8"/>
       <c r="B8" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>51</v>
+        <v>48</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>213</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>113</v>
+        <v>45</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>214</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="115.5">
       <c r="A9" s="8"/>
       <c r="B9" s="8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="82.5">
       <c r="A10" s="8"/>
       <c r="B10" s="8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="264">
       <c r="A11" s="8"/>
       <c r="B11" s="8" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="132">
       <c r="A12" s="8"/>
       <c r="B12" s="8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="264">
       <c r="A13" s="8"/>
       <c r="B13" s="8" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="409.5">
       <c r="A14" s="8"/>
       <c r="B14" s="8" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>204</v>
+        <v>114</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>199</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="214.5">
       <c r="A15" s="8"/>
       <c r="B15" s="8" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="231">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="409.5">
       <c r="A16" s="19"/>
       <c r="B16" s="19" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>205</v>
+        <v>140</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>201</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="G16" s="25" t="s">
-        <v>148</v>
+        <v>202</v>
+      </c>
+      <c r="G16" s="24" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="165">
       <c r="A17" s="19"/>
       <c r="B17" s="19" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>206</v>
+        <v>143</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>191</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="G17" s="26" t="s">
-        <v>152</v>
+        <v>145</v>
+      </c>
+      <c r="G17" s="25" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="409.5">
       <c r="A18" s="19"/>
       <c r="B18" s="19" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>207</v>
+        <v>147</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>192</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="G18" s="26" t="s">
-        <v>156</v>
+        <v>45</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="G18" s="25" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="214.5">
       <c r="A19" s="19"/>
       <c r="B19" s="19" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="G19" s="26" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="165">
+        <v>153</v>
+      </c>
+      <c r="G19" s="25" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="198">
       <c r="A20" s="19"/>
       <c r="B20" s="19" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>165</v>
+        <v>215</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="G20" s="26" t="s">
-        <v>164</v>
+        <v>216</v>
+      </c>
+      <c r="G20" s="25" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="94.5">
-      <c r="A21" s="22"/>
-      <c r="B21" s="22" t="s">
+      <c r="A21" s="21"/>
+      <c r="B21" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="121.5">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="189">
+      <c r="A23" s="20"/>
+      <c r="B23" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="D23" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="E23" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="F23" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="G23" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="E21" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="F21" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="G21" s="21" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="121.5">
-      <c r="A22" s="21"/>
-      <c r="B22" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="D22" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="E22" s="21" t="s">
-        <v>200</v>
-      </c>
-      <c r="F22" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="G22" s="21" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="189">
-      <c r="A23" s="21"/>
-      <c r="B23" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="C23" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="E23" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="F23" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="G23" s="21" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="283.5">
+    </row>
+    <row r="24" spans="1:7" ht="324">
       <c r="A24" s="20"/>
       <c r="B24" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="121.5">
+      <c r="A25" s="20"/>
+      <c r="B25" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="F25" s="20" t="s">
         <v>209</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="G25" s="20" t="s">
         <v>210</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="E24" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="F24" s="20" t="s">
-        <v>212</v>
-      </c>
-      <c r="G24" s="20" t="s">
-        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -2457,22 +2516,22 @@
   <sheetData>
     <row r="1" spans="1:1" ht="24">
       <c r="A1" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="16.5">
       <c r="A2" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="16.5">
       <c r="A3" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="16.5">
       <c r="A5" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -2498,339 +2557,339 @@
   <sheetData>
     <row r="1" spans="1:4" ht="24">
       <c r="A1" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.5">
       <c r="A2" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.5">
       <c r="A3" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16.5">
       <c r="A5" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>37</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="49.5">
       <c r="A6" s="8" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16.5">
       <c r="A7" s="8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16.5">
       <c r="A8" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B8" s="8" t="s">
+    </row>
+    <row r="9" spans="1:4" ht="33">
+      <c r="A9" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C9" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>68</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="16.5">
-      <c r="A9" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16.5">
       <c r="A10" s="8" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="33">
       <c r="A11" s="8" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="33">
       <c r="A12" s="19" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="16.5">
       <c r="A13" s="19" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="33">
       <c r="A14" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="27">
+      <c r="A15" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="C15" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="D15" s="21" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="54">
+      <c r="A17" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="C17" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="C14" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="27">
-      <c r="A15" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="B15" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="B16" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="54">
-      <c r="A17" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>135</v>
+      <c r="D17" s="20" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="27">
       <c r="A18" s="11" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="B20" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>92</v>
-      </c>
       <c r="D20" s="11" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="54">
       <c r="A22" s="11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>173</v>
+        <v>91</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>163</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="27">
       <c r="A23" s="11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="40.5">
-      <c r="A25" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="B25" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="D25" s="21" t="s">
-        <v>125</v>
+      <c r="A25" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="27">
-      <c r="A26" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="B26" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>127</v>
+      <c r="A26" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="54">
-      <c r="A27" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="B27" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>178</v>
+      <c r="A27" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/docs/requirements-v0.1.xlsx
+++ b/docs/requirements-v0.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Workspace\02_開発\workbench\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A58CB0A0-EDFF-4697-9047-A4BE88058E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EFD81D7-8416-4273-A566-46F062721BE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -808,23 +808,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>・PC の Outlook アプリ(クラシック版)を読み取り専用で読む(モーニングブリーフと同じ方法)
-・アプリの起動時と10分ごと(Claude の案)に読む。Outlook が起動していなければ、裏で立ち上げて読む
-・読めなかったとき(サインイン切れなど)は推測で埋めず、画面に「大学のメールを読めませんでした」と出す
-・差出人が大学のアドレス(@…kyusan-u.ac.jp)のメールだけを対象にする
-・その中から「授業」「奨学金」「試合のチケット」の連絡を分けて見せる
-・3種類に当てはまらない大学のメール(「学内連絡:」の一斉配信も含む)は、「その他」としてまとめ、3種類より下にたたんだ状態で置く
-・授業の連絡は、件名や本文に時間割の科目名が入っているかで、その授業の入れ物に振り分ける
-・振り分けを間違えたものや「その他」に入ったものは、自分で入れ物を選び直せる。選び直した結果を覚え、次から同じ差出人・同じ件名なら、その入れ物に入れる
-・「奨学金」「試合のチケット」は大学の入れ物として自動で作り、授業と同じように扱う
-・締切が書いてあるメールは、確認なしで自動でタスクにし、「メールから自動で入った」印をつける。間違っていたら1回の操作で消せ、消したものは次に読んだときに復活しない
-・「その他」のメールから自動で入ったタスクは、「未分類」の入れ物に入れ、「入れ物を選んで」の印をつける(F2)
-・学習サイトから大学のアドレスで届く通知メールも読む。本文にあるサイトへのリンクを画面に出し、自分でクリックして開ける。アプリがサイトを開くことはしない(X6)
-・休講・補講の連絡は、その授業の入れ物のスケジュール(F19)にする
-・取り込んだ連絡は「連絡」の画面で、授業・奨学金・試合のチケット・企業・その他に分けて見る。トップには2段目に「新しい連絡 ○件」と件数だけ出し、押すと「連絡」の画面が開く。開いたら件数は0に戻る(「見た」は workbench の中だけで覚え、メールの既読には触らない)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>済:どのメールを「大学からの連絡」とみなすか → 差出人が大学のアドレスのもの。授業・奨学金・試合のチケットを分けて見せる
 済:3種類に当てはまらない大学のメールをどうするか → 「その他」としてたたんで出す
 済:「学内連絡:」の一斉配信をどこまで拾うか → 3種類以外は全部「その他」に入る
@@ -931,6 +914,23 @@
   </si>
   <si>
     <t>大学・就活・アルバイトと開発の一元管理</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・PC の Outlook アプリ(クラシック版)を読み取り専用で読む(モーニングブリーフと同じ方法)
+・アプリの起動時と10分ごと(Claude の案)に読む。Outlook が起動していなければ、裏で立ち上げて読む
+・読めなかったとき(サインイン切れなど)は推測で埋めず、画面に「大学のメールを読めませんでした」と出す
+・差出人が大学のアドレスのメールだけを対象にする。大学のアドレスの形(@ から後ろ)は PC の中の data/ の設定に置き、公開リポジトリの資料には書かない
+・その中から「授業」「奨学金」「試合のチケット」の連絡を分けて見せる
+・3種類に当てはまらない大学のメール(「学内連絡:」の一斉配信も含む)は、「その他」としてまとめ、3種類より下にたたんだ状態で置く
+・授業の連絡は、件名や本文に時間割の科目名が入っているかで、その授業の入れ物に振り分ける
+・振り分けを間違えたものや「その他」に入ったものは、自分で入れ物を選び直せる。選び直した結果を覚え、次から同じ差出人・同じ件名なら、その入れ物に入れる
+・「奨学金」「試合のチケット」は大学の入れ物として自動で作り、授業と同じように扱う
+・締切が書いてあるメールは、確認なしで自動でタスクにし、「メールから自動で入った」印をつける。間違っていたら1回の操作で消せ、消したものは次に読んだときに復活しない
+・「その他」のメールから自動で入ったタスクは、「未分類」の入れ物に入れ、「入れ物を選んで」の印をつける(F2)
+・学習サイトから大学のアドレスで届く通知メールも読む。本文にあるサイトへのリンクを画面に出し、自分でクリックして開ける。アプリがサイトを開くことはしない(X6)
+・休講・補講の連絡は、その授業の入れ物のスケジュール(F19)にする
+・取り込んだ連絡は「連絡」の画面で、授業・奨学金・試合のチケット・企業・その他に分けて見る。トップには2段目に「新しい連絡 ○件」と件数だけ出し、押すと「連絡」の画面が開く。開いたら件数は0に戻る(「見た」は workbench の中だけで覚え、メールの既読には触らない)</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1196,7 +1196,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1538,7 +1538,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F8" s="26"/>
       <c r="G8" s="26"/>
@@ -1988,7 +1988,7 @@
         <v>116</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="54">
@@ -2085,7 +2085,7 @@
         <v>44</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>138</v>
@@ -2127,7 +2127,7 @@
         <v>48</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>198</v>
@@ -2136,7 +2136,7 @@
         <v>45</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G8" s="10" t="s">
         <v>99</v>
@@ -2255,14 +2255,14 @@
       <c r="C14" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="D14" s="19" t="s">
-        <v>199</v>
+      <c r="D14" s="10" t="s">
+        <v>218</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>45</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G14" s="10" t="s">
         <v>105</v>
@@ -2298,13 +2298,13 @@
         <v>140</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E16" s="19" t="s">
         <v>45</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G16" s="24" t="s">
         <v>141</v>
@@ -2382,13 +2382,13 @@
         <v>155</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E20" s="19" t="s">
         <v>45</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G20" s="25" t="s">
         <v>156</v>
@@ -2466,7 +2466,7 @@
         <v>195</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E24" s="20" t="s">
         <v>45</v>
@@ -2481,22 +2481,22 @@
     <row r="25" spans="1:7" ht="121.5">
       <c r="A25" s="20"/>
       <c r="B25" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="C25" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="C25" s="20" t="s">
+      <c r="D25" s="20" t="s">
         <v>207</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>208</v>
       </c>
       <c r="E25" s="20" t="s">
         <v>189</v>
       </c>
       <c r="F25" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="G25" s="20" t="s">
         <v>209</v>
-      </c>
-      <c r="G25" s="20" t="s">
-        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -2634,7 +2634,7 @@
         <v>67</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>68</v>
@@ -2858,10 +2858,10 @@
         <v>118</v>
       </c>
       <c r="C25" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="D25" s="20" t="s">
         <v>203</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="27">

--- a/docs/requirements-v0.1.xlsx
+++ b/docs/requirements-v0.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Workspace\02_開発\workbench\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EFD81D7-8416-4273-A566-46F062721BE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DBD0E39-ED6C-495F-8E4F-E6C6699BC9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,9 +67,6 @@
     <t>要件定義書(改版履歴)</t>
   </si>
   <si>
-    <t>　(案　件　名)大学と開発の一元管理</t>
-  </si>
-  <si>
     <t>　(システム名)workbench(作業台)</t>
   </si>
   <si>
@@ -365,11 +362,6 @@
   </si>
   <si>
     <t>要件定義 問10</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>済:入れ物を消したとき、中のタスクと作業記録をどうするか → 消さずに終了にする
-済:学期が終わった授業をどう片付けるか → 終了にする</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -400,12 +392,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>済:「手つかず」の決め方と日数 → 締切ありは締切の3日前に記録なし、締切なしは登録から3日間記録なし
-済:「長い」の時間 → 2時間
-済:アプリを閉じているときの通知 → 画面を閉じていても通知する(PC 起動時に自動で立ち上がる)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>大学の Outlook メールから、授業・奨学金・試合のチケット・その他の連絡を取り込む</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -499,14 +485,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>・入れ物の種類は「大学」「開発」「就活」の3つ
-・タスクと作業記録は、どれか1つの入れ物に入る
-・入れ物は消さずに「終了」にしてしまう。終了にすると一覧とトップ画面から見えなくなり、中身は残る。あとで戻せる
-・完全に消せるのは、中身が空の入れ物だけ
-・学期が終わった授業も「終了」にして片付ける</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>F11 就活</t>
   </si>
   <si>
@@ -523,10 +501,6 @@
   </si>
   <si>
     <t>要件定義 追加の要望(Google カレンダーの予定を見たい)・追加7(図で比べた)</t>
-  </si>
-  <si>
-    <t>済:どのカレンダーを読むか → 個人のアカウントのメインのカレンダーだけ</t>
-    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>F13 Google カレンダーに書く</t>
@@ -614,12 +588,6 @@
     <t>Google は決めたことだけ</t>
   </si>
   <si>
-    <t>Gmail は読むだけ(送信・削除・既読化をしない)。Google カレンダーは、workbench が書いた目印のある予定だけを作成・書き換え・削除し、自分や他の人が作った予定には触れない。許可の鍵は公開リポジトリに入れない</t>
-  </si>
-  <si>
-    <t>コードに該当する操作が無いこと、目印のない予定を変えないことを確かめる</t>
-  </si>
-  <si>
     <t>・登録したリポジトリのコミットを読む
 ・1つのリポジトリに複数のアプリがある場合(lab)は、変更されたフォルダで入れ物に振り分ける
 ・同じコミットを二重に取り込まない
@@ -632,36 +600,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>・完了したタスクの数 ÷ 全部のタスクの数
-・タスクが0件の入れ物は、数字やバーを出さずに「タスクなし」と出す
-・トップ画面には、今日・今週にタスクがある入れ物の進み具合を出す
-・入れ物ごとに「トップに出す」を自分で選べる。選んだ入れ物は、タスクがなくてもトップに出る
-・入れ物の一覧画面には、全部の入れ物の進み具合を出す
-・進み具合はゲージ(横に伸びるバー)と「○% 完了」で出す
-・入れ物ごとのゲージに加えて、種類ごと(大学・就活・開発)と全体のゲージを出す
-・種類ごと・全体で数えるのは、「終了」にしていない入れ物のタスクだけ
-・トップ画面の一番上に、全体のゲージを細く1本だけ出す。押すと小さな窓が開き、全体と種類ごとの3本が見える(小窓の細かい動きは UI 試作で決める)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>済:タスクが0件の入れ物をどう表示するか → 「タスクなし」と文字で出す
-済:どの画面に出すか → トップは今日・今週にタスクがある入れ物+自分で選んだ入れ物、一覧画面は全部
-済:全体のゲージを何で出すか → 種類ごと(大学・就活・開発)と全体
-済:種類ごと・全体で何を数えるか → 「終了」にしていない入れ物のタスクだけ
-済:全体と種類ごとのゲージをどこに出すか → トップの一番上に全体を細く1本、押すと小窓で種類ごと</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・締切の前日に知らせる
-・手つかずのタスクを知らせる。締切のあるタスクは、締切の3日前(Claude の案)になっても作業記録が1つもないとき。締切のないタスクは、登録してから3日間(Claude の案)、作業記録も完了もないとき(開発の締切のないタスクには出さない)
-・「手つかず」はタスクを選んだ作業記録だけで判断する。入れ物だけを選んだ記録は数えない。通知が来たら、その記録にタスクを選び直せば止まる
-・同じ作業記録が2時間(Claude の案)続いたら知らせる(切り替え忘れを防ぐため)
-・画面を閉じていても通知する。PC を起動したら裏の部分が自動で立ち上がる
-・PC の電源が切れていた間の通知は、次に画面を開いたときにまとめて見せる
-・着手日(F16)をつけたタスクは、着手日の翌日になっても作業記録が1つもないとき知らせる。締切の3日前の通知もそのまま残す</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>F16 着手日</t>
   </si>
   <si>
@@ -691,10 +629,6 @@
 ・打った文字から、締切・入れ物・タスク名を読み取る(例:「金 レポート 卒論」→ 締切:今週の金曜、入れ物:卒論、タスク名:レポート)
 ・締切は「金」「10/25」「明日」などの書き方を読む。入れ物は、授業名・企業名など入れ物の名前の一部を読む
 ・読み取れなかったときも、その場でタスクにする。入れ物が読めなければ「未分類」に入れて「入れ物を選んで」の印をつける。締切が読めなければ締切なしにする</t>
-  </si>
-  <si>
-    <t>済:何を読み取るか → 締切と入れ物の両方
-済:読み取れなかったとき → すぐ入れて、未分類と印であとから直す(図で比べた)</t>
   </si>
   <si>
     <t>要件定義 機能の提案(別のエージェント)・追加22・26・32</t>
@@ -717,13 +651,6 @@
 ・自動で完了にしたタスクには「自動」の印をつけ、1クリックで元に戻せる</t>
   </si>
   <si>
-    <t>済:何を合図にするか → 4つ全部
-済:合図を見つけたらすぐ完了にするか → 確かさで分ける(①②はすぐ、③は聞く、④は確認してから)
-・大学の学習サイトが提出受付のメールを送るか(未確認。Outlook のメールを読んで確かめる)
-・メールやコミットを、どのタスクのものと見分けるか
-→ 基本設計で決める</t>
-  </si>
-  <si>
     <t>要件定義 完了の判断の質問(手動だけだとめんどう)・追加27・28</t>
   </si>
   <si>
@@ -732,48 +659,6 @@
   </si>
   <si>
     <t>Must</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・タスクは必ず1つの入れ物に入る
-・締切(日付)をつけられる。締切のないタスクも登録できる
-・開発のタスクは、ふだんは締切を空のままにする。面接前のデモなど、必要なときだけつけられる
-・締切には時刻も入れられる(入れなくてもよい)。時刻のあるタスクは、同じ日の中で時刻順に並ぶ
-・毎週の繰り返しを作れる(例:毎週火曜 9:00まで)。1つ完了すると、次の週の分が自動で出る
-・完了にできる。合図を見つけて自動で完了になる場合は F18
-・入れ物が決まらないタスク(F17 の1行入力で読み取れなかったものなど)は「未分類」の入れ物に入り、「入れ物を選んで」の印がつく。印から1クリックで入れ物を選べる
-・「着手日」(この日から始める)をつけられる(F16)
-・面接・補講など日時が決まったもの(始まりと終わりの時刻があるもの)は、タスクではなくスケジュール(F19)として持つ</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・F10 の今日の授業と同じ「今日の時間」の列に、今日の予定を混ぜて時刻順に並べる
-・空き時間は書かない
-・読むのは個人の Google アカウントのメインのカレンダーだけ
-・読み方は F11 と同じ Google の公式の連携(API)。読めなかったときは、推測で埋めず「Google に接続できませんでした」と出す
-・アルバイトの予定は、入れ物を作らず、ここに予定として出す。入れ方は F14 のシフト表の写真か、Google カレンダーへの直接入力
-・今日より先の予定は、F19 のスケジュールの画面で見る</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・書き込むもの:タスクの締切(大学・就活・締切をつけた開発)、面接・面談、休講・補講、奨学金の手続きなど、締切か日時があるもの
-・「その他」のメールから自動で入ったものは書き込まない
-・面接など日時の決まったものは、時刻つきの予定にする。締切は全部終日の予定にし、時刻は名前に書く(例:「締切 23:59 第10回レポート」)
-・重なる予定があって書かなかったときは、画面に「重なる予定があったので、カレンダーには書きませんでした」と出す
-・書き込み先は、F12 と同じ個人のアカウントのメインのカレンダー
-・workbench が書いた予定には目印をつける。締切や日時が変わったり、タスクを消したりしたときに、自動で書き換え・削除するのは目印のある予定だけ
-・自分の手で直すときは、F19 のスケジュールの画面から、自分が作った予定を全部直せる。人から招待された予定は、予定ごとのトグルで許したものだけ直せる
-・タスクを完了にしたら、予定は消さずに名前の頭に「済」をつける(例:「済 第10回レポート」)。期限が過ぎて未完了のものは、そのまま残す
-・同じ予定がすでにカレンダーにあれば書き込まない。日時のある予定は、同じ日に時間帯が重なれば名前が違っても同じとみなす。時間帯のない締切は、同じ日に同じ名前なら同じとみなす
-・モーニングブリーフ(gmail-secretary)側の自動登録は止める(二重登録を防ぐため)。止めるのは、F13 が動くようになってから</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>済:締切や日時が変わったり、タスクを消したりしたとき、カレンダーの予定も直すか → 直す(workbench が書いた予定だけ)
-済:タスクを完了にしたとき、期限が過ぎたときの予定の扱い → 消さずに残し、完了したら「済」をつける
-済:同じ予定がすでにカレンダーにあるときの扱い → 時間帯が重なれば書かない(締切は同じ日・同じ名前で比べる)
-済:締切を時刻つきの予定にするか、終日の予定にするか → 締切は終日、時刻は名前に書く
-済(F19 で変更):自分の手で直せる予定 → 自分が作った予定は全部。招待された予定は、予定ごとのトグルで許したものだけ</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -794,18 +679,6 @@
   </si>
   <si>
     <t>要件定義 点検の差4・Google カレンダーのような機能を足したい・追加35〜40</t>
-  </si>
-  <si>
-    <t>・一番上に、全体の進み具合のゲージを細く1本出す(F6)
-・その下は役割ごとに3段に分ける。1段目:記録中の作業(F4)。2段目:お知らせ(あるときだけ出す)。3段目:「期限切れ」
-・2段目に出すものは次の9つ:①作業記録の再開の確認(F4)②PC の電源が切れていた間の通知(F8)③学期の終わりの米印(F10)④読めなかった・つながらなかった(F9・F10・F11・F12・F19)⑤読み込み中(非機能要件)⑥カレンダーに書かなかった予定(F13)⑦新しい連絡の件数(F9・F11)⑧「終わっていそう」なタスクの件数(F18)⑨未分類の件数(F2)
-・「期限切れ」には、締切を過ぎたタスクを色を変えてまとめる。完了にするか締切を変えるまで残る
-・その下に、今日の時間(F10・F12)を出す
-・その下に「今日」と「今週」に分けて、締切の近い順に並べる
-・締切のないタスクは、その下に「締切なし」としてまとめて出す
-・同じ締切の日の中は、①時刻があるものは時刻順、時刻なしはその日の最後 ②同じなら大学・就活を開発より先 ③さらに同じなら登録が古い順。「締切なし」の中は登録が古い順
-・各タスクに入れ物の名前のラベル(例:「卒論」「fx-practice」)をつけ、ラベルの色を大学・開発・就活の3色で分ける</t>
-    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>済:どのメールを「大学からの連絡」とみなすか → 差出人が大学のアドレスのもの。授業・奨学金・試合のチケットを分けて見せる
@@ -846,20 +719,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>・予定の本体は Google カレンダー(個人のアカウントのメインのカレンダー)に置く。workbench の中に別の写しは持たない
-・workbench で予定を足す・直す・消すと、その場で Google カレンダーにも反映する
-・Google カレンダーで足した・直した予定(スマホからも)は、画面を開いたときと10分ごと(Claude の案)に読んで出す
-・時間割の授業(F10)とタスクの締切も、同じ画面にまとめて出す
-・面接・面談・補講・休講など日時が決まったものは、スケジュールとして持つ。完了はなく、進み具合のゲージにも数えない
-・スケジュールは入れ物に入れられる(企業の面接はその企業の入れ物など)。入れ物なしでも持てる(アルバイトの面接 F20、Google カレンダーで足した予定など)
-・見え方は、ふだんは「一覧」(日付ごとに縦に並ぶ)。「月」を押すと月のマス目に切り替わり、予定は点で出る
-・自分が作った予定は全部直せる。人から招待された予定は見るだけ。予定ごとのトグルで編集を許せる(初めは見るだけ)
-・招待された予定は、主催者が Google 側で変更を許していなければ直せない。そのときは「主催者が変更を許可していないため、直せませんでした」と出す
-・予定を消す前には確認を出す
-・Google に接続できないときは、足す・直すことができない。「Google に接続できませんでした」と出す</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>F20 アルバイトの面接</t>
   </si>
   <si>
@@ -887,13 +746,6 @@
   </si>
   <si>
     <t>今日・今週やることを、大学・就活・開発を混ぜて締切順に並べる</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>済:締切を過ぎたタスクをどこに出すか → 一番上に「期限切れ」として出す
-済:締切が同じときの並び順 → 時刻順 → 大学・就活が先 → 登録が古い順(F11 で就活を足したときに直した)
-済(点検で追加):「一目でわかる印」とは何か → 入れ物名のラベル、色は大学・開発・就活の3色(F11 で就活を足したときに直した)
-済(点検で追加):2段目に何を出すか → 9つに決めた</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -930,7 +782,190 @@
 ・「その他」のメールから自動で入ったタスクは、「未分類」の入れ物に入れ、「入れ物を選んで」の印をつける(F2)
 ・学習サイトから大学のアドレスで届く通知メールも読む。本文にあるサイトへのリンクを画面に出し、自分でクリックして開ける。アプリがサイトを開くことはしない(X6)
 ・休講・補講の連絡は、その授業の入れ物のスケジュール(F19)にする
-・取り込んだ連絡は「連絡」の画面で、授業・奨学金・試合のチケット・企業・その他に分けて見る。トップには2段目に「新しい連絡 ○件」と件数だけ出し、押すと「連絡」の画面が開く。開いたら件数は0に戻る(「見た」は workbench の中だけで覚え、メールの既読には触らない)</t>
+・取り込んだ連絡は「連絡」の画面で、授業・奨学金・試合のチケット・企業・アルバイト・その他に分けて見る。トップには2段目に「新しい連絡 ○件」と件数だけ出し、押すと「連絡」の画面が開く。開いたら件数は0に戻る(「見た」は workbench の中だけで覚え、メールの既読には触らない)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・タスクは必ず1つの入れ物に入る
+・締切(日付)をつけられる。締切のないタスクも登録できる
+・開発のタスクは、ふだんは締切を空のままにする。面接前のデモなど、必要なときだけつけられる
+・締切には時刻も入れられる(入れなくてもよい)。時刻のあるタスクは、同じ日の中で時刻順に並ぶ
+・毎週の繰り返しを作れる(例:毎週火曜 9:00まで)。1つ完了すると、次の週の分が自動で出る
+・完了にできる。合図を見つけて自動で完了になる場合は F18
+・入れ物が決まらないタスク(「その他」のメールから入ったもの、F17 の1行入力で読み取れなかったもの)は「未分類」の入れ物に入り、「入れ物を選んで」の印がつく。印から1クリックで入れ物を選べる
+・(Should:F16 を作ったとき)「着手日」(この日から始める)をつけられる
+・面接・補講など日時が決まったもの(始まりと終わりの時刻があるもの)は、タスクではなくスケジュール(F19)として持つ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:締切を過ぎたタスクをどこに出すか → 一番上に「期限切れ」として出す
+済:締切が同じときの並び順 → 時刻順 → 大学・就活が先 → 登録が古い順(F11 で就活を足したときに直した)
+済(点検で追加):「一目でわかる印」とは何か → 入れ物名のラベル、色は大学・開発・就活の3色(F11 で就活を足したときに直した)
+済(点検で追加):2段目に何を出すか → 9つに決めた
+・1行入力の欄(F17)と、着手日で「今日」に上がったタスク(F16)の、トップでの置き場所と並び順
+・「今週」の範囲(何曜日から何曜日までか。F17 の「金」の読み方もこれに合わせる)
+→ 基本設計で決める</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:「手つかず」の決め方と日数 → 締切ありは締切の3日前に記録なし、締切なしは登録から3日間記録なし
+済:「長い」の時間 → 2時間
+済:アプリを閉じているときの通知 → 画面を閉じていても通知する(PC 起動時に自動で立ち上がる)
+・画面での知らせ(締切の前日・手つかず・2時間・着手日)と、F18 ③の「このタスクは終わった?」を、画面のどこに出すか
+・F14 と F18 ④(claude -p)が読み取れなかったときの出し方
+→ 基本設計で決める</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:どのカレンダーを読むか → 個人のアカウントのメインのカレンダーだけ
+・Google カレンダーをいつ読むか(案:起動時と10分ごと。F19 と同じ)
+→ 基本設計で決める</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:何を読み取るか → 締切と入れ物の両方
+済:読み取れなかったとき → すぐ入れて、未分類と印であとから直す(図で比べた)
+・読み取る日付の書き方の範囲(「金」「10/25」「明日」のほかに何を読むか)
+→ 基本設計で決める</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:何を合図にするか → 4つ全部
+済:合図を見つけたらすぐ完了にするか → 確かさで分ける(①②はすぐ、③は聞く、④は確認してから)
+・大学の学習サイトが提出受付のメールを送るか(未確認。Outlook のメールを読んで確かめる)
+・メールやコミットを、どのタスクのものと見分けるか
+→ 基本設計で決める
+・①に入るメールの範囲(学習サイトの提出受付・企業のエントリー受付のほかに何を入れるか)
+・「自動」から元に戻したとき、繰り返しで出た次の週の分と、カレンダーの「済」をどうするか
+・③を、記録が自動で止まったとき(別のものを開始・PC が眠った)にも聞くか。「1回だけ」の単位。切り替え2クリック以内(非機能要件)との関係
+→ 基本設計で決める</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>　(案　件　名)大学・就活・アルバイトと開発の一元管理</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>Gmail は読むだけ(送信・削除・既読化をしない)。Google カレンダーで、自動で書き換え・削除するのは目印のある予定だけ。手で直せるのは、自分が作った予定と、トグルで許した招待された予定だけ。許可の鍵は公開リポジトリに入れない</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>Gmail に読む以外の操作がないこと、自動の処理が目印のない予定を変えないこと、トグルを入れていない招待された予定を直せないことを確かめる</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・F10 の今日の授業と同じ「今日の時間」の列に、今日の予定を混ぜて時刻順に並べる
+・空き時間は書かない
+・読むのは個人の Google アカウントのメインのカレンダーだけ
+・読み方は F11 と同じ Google の公式の連携(API)。読めなかったときは、推測で埋めず「Google に接続できませんでした」と出す
+・アルバイトの予定は、入れ物を作らず、ここに予定として出す。入れ方は F14 のシフト表の写真か、Google カレンダーへの直接入力
+・今日より先の予定は、F19 のスケジュールの画面で見る
+・workbench が書いた締切の予定は、F12 の「今日の時間」と F19 のスケジュールの画面では、タスクとして1回だけ出す(予定としては出さない)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・書き込むもの:タスクの締切(大学・就活・締切をつけた開発)、面接・面談、休講・補講、奨学金の手続きなど、締切か日時があるもの
+・「その他」のメールから自動で入ったものは書き込まない
+・面接など日時の決まったものは、時刻つきの予定にする。締切は全部終日の予定にし、時刻は名前に書く(例:「締切 23:59 第10回レポート」)
+・書けなかった予定は、workbench の中に「書けなかった予定」として一時的に残す。Google に接続できなかったときは、つながったら自動でもう一度書く。重なる予定があって書かなかったときは、2段目のお知らせに「重なる予定があるため書いていません」と出し、「それでも書く」「書かない」を選べる。書けたら、または「書かない」を選んだら、一時的な分は消す
+・書き込み先は、F12 と同じ個人のアカウントのメインのカレンダー
+・タスクやメールから自動で書いた予定には目印をつける。F19 の画面で手で足した予定には目印をつけない(スマホから足した予定と同じ扱い)。締切や日時が変わったり、タスクを消したりしたときに、自動で書き換え・削除するのは目印のある予定だけ
+・自分の手で直すときは、F19 のスケジュールの画面から、自分が作った予定を全部直せる。人から招待された予定は、予定ごとのトグルで許したものだけ直せる
+・タスクを完了にしたら、予定は消さずに名前の頭に「済」をつける(例:「済 第10回レポート」)。期限が過ぎて未完了のものは、そのまま残す
+・同じ予定がすでにカレンダーにあれば書き込まない。日時のある予定は、同じ日に時間帯が重なれば名前が違っても同じとみなす。時間帯のない締切は、同じ日に同じ名前なら同じとみなす
+・モーニングブリーフ(gmail-secretary)側の自動登録は止める(二重登録を防ぐため)。止めるのは、F13 が動くようになってから
+・目印のある締切の予定を Google 側(スマホなど)で動かしたら、workbench のタスクの締切もそれに合わせる</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:締切や日時が変わったり、タスクを消したりしたとき、カレンダーの予定も直すか → 直す(workbench が書いた予定だけ)
+済:タスクを完了にしたとき、期限が過ぎたときの予定の扱い → 消さずに残し、完了したら「済」をつける
+済:同じ予定がすでにカレンダーにあるときの扱い → 時間帯が重なれば書かない(締切は同じ日・同じ名前で比べる)
+済:締切を時刻つきの予定にするか、終日の予定にするか → 締切は終日、時刻は名前に書く
+済(F19 で変更):自分の手で直せる予定 → 自分が作った予定は全部。招待された予定は、予定ごとのトグルで許したものだけ
+・未分類から入れ物を選び直したタスクを、カレンダーに書くか
+→ 基本設計で決める
+済(点検で追加):Google に書けなかった予定 → workbench に一時的に残し、つながったら書き直す。重なりは2段目で選ぶ
+済(点検で追加):締切の予定がタスクと2回出る件、Google 側で動かしたとき → 画面には1回だけ。Google で動かしたらタスクの締切も合わせる</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・予定の本体は Google カレンダー(個人のアカウントのメインのカレンダー)に置く。workbench の中に別の写しは持たない。ただし、Google に書けなかった予定だけは一時的に預かる(F13)
+・workbench で予定を足す・直す・消すと、その場で Google カレンダーにも反映する
+・Google カレンダーで足した・直した予定(スマホからも)は、画面を開いたときと10分ごと(Claude の案)に読んで出す
+・時間割の授業(F10)とタスクの締切も、同じ画面にまとめて出す
+・面接・面談・補講・休講など日時が決まったものは、スケジュールとして持つ。完了はなく、進み具合のゲージにも数えない
+・スケジュールは入れ物に入れられる(企業の面接はその企業の入れ物など)。入れ物なしでも持てる(アルバイトの面接 F20、Google カレンダーで足した予定など)
+・見え方は、ふだんは「一覧」(日付ごとに縦に並ぶ)。「月」を押すと月のマス目に切り替わり、予定は点で出る
+・自分が作った予定は全部直せる。人から招待された予定は見るだけ。予定ごとのトグルで編集を許せる(初めは見るだけ)
+・招待された予定は、主催者が Google 側で変更を許していなければ直せない。そのときは「主催者が変更を許可していないため、直せませんでした」と出す
+・予定を消す前には確認を出す
+・Google に接続できないときは、足す・直すことができない。「Google に接続できませんでした」と出す
+・画面で手で足した予定には、workbench の目印をつけない(F13)
+・workbench が書いた締切の予定は、F12 の「今日の時間」と F19 のスケジュールの画面では、タスクとして1回だけ出す(予定としては出さない)。Google 側で動かしたら、タスクの締切も合わせる(F13)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:タスクが0件の入れ物をどう表示するか → 「タスクなし」と文字で出す
+済:どの画面に出すか → トップは今日・今週にタスクがある入れ物+自分で選んだ入れ物、一覧画面は全部
+済:全体のゲージを何で出すか → 種類ごと(大学・就活・開発)と全体
+済:種類ごと・全体で何を数えるか → 「終了」にしていない入れ物のタスクだけ
+済:全体と種類ごとのゲージをどこに出すか → トップの一番上に全体を細く1本、押すと小窓で種類ごと
+済(点検で追加):入れ物ごとのゲージをトップのどこに出すか → 選んだ入れ物は全体のすぐ下にいつも、今日・今週の入れ物は小窓の中(図で比べた)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・入れ物の種類は、初めは「大学」「就活」「開発」の3つ。種類は自分で足す・名前と色を変える・消すことができる。中に入れ物がある種類は消せない
+・種類ごとに2つの設定を持つ:①同じ締切のとき先に並べるか(初めは大学・就活がオン)②締切のないタスクに手つかずの通知を出すか(初めは開発だけオフ)
+・F9・F10 が自動で作る入れ物は「大学」の種類に、F11 の企業は「就活」の種類に入る。名前を変えても同じ種類として扱う
+・タスクと作業記録は、どれか1つの入れ物に入る
+・入れ物は消さずに「終了」にしてしまう。終了にすると一覧とトップ画面から見えなくなり、中身は残る。あとで戻せる
+・完全に消せるのは、中身が空の入れ物だけ
+・学期が終わった授業も「終了」にして片付ける
+・種類とは別に、特別な入れ物「未分類」が1つだけある。入れ物が決まらないタスクの一時的な置き場所(F2)。ラベルは灰色。進み具合は全体のゲージには数えるが、種類ごとのゲージには入れない。締切のないタスクの手つかずの通知(F8)は、ほかと同じく登録から3日で出す</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・一番上に、全体の進み具合のゲージを細く1本出す。そのすぐ下に、「トップに出す」を選んだ入れ物のゲージを出す(F6)
+・その下は役割ごとに3段に分ける。1段目:記録中の作業(F4)。2段目:お知らせ(あるときだけ出す)。3段目:「期限切れ」
+・2段目に出すものは次の9つ:①作業記録の再開の確認(F4)②PC の電源が切れていた間の通知(F8)③学期の終わりの米印(F10)④読めなかった・つながらなかった(F9・F10・F11・F12・F19)⑤読み込み中(非機能要件)⑥カレンダーに書かなかった予定(F13)⑦新しい連絡の件数(F9・F11・F20)⑧「終わっていそう」なタスクの件数(F18)⑨未分類の件数(F2)
+・「期限切れ」には、締切を過ぎたタスクを色を変えてまとめる。完了にするか締切を変えるまで残る
+・その下に、今日の時間(F10・F12)を出す
+・その下に「今日」と「今週」に分けて、締切の近い順に並べる
+・締切のないタスクは、その下に「締切なし」としてまとめて出す
+・同じ締切の日の中は、①時刻があるものは時刻順、時刻なしはその日の最後 ②同じなら「先に並べる」設定の種類を先(初めは大学・就活) ③さらに同じなら登録が古い順。「締切なし」の中は登録が古い順
+・各タスクに入れ物の名前のラベル(例:「卒論」「fx-practice」)をつけ、ラベルの色を種類ごとの色で分ける(F1)
+・「未分類」のタスクのラベルは灰色にする(F1)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・完了したタスクの数 ÷ 全部のタスクの数
+・タスクが0件の入れ物は、数字やバーを出さずに「タスクなし」と出す
+・トップ画面では、「トップに出す」を選んだ入れ物のゲージを、全体のゲージのすぐ下にいつも出す。今日・今週にタスクがある入れ物のゲージは、全体のゲージを押して開く小窓の中に、全体と種類ごとのゲージに続けて並べる
+・入れ物ごとに「トップに出す」を自分で選べる。選んだ入れ物は、タスクがなくてもトップに出る
+・入れ物の一覧画面には、全部の入れ物の進み具合を出す
+・進み具合はゲージ(横に伸びるバー)と「○% 完了」で出す
+・入れ物ごとのゲージに加えて、種類ごと(初めは大学・就活・開発)と全体のゲージを出す
+・種類ごと・全体で数えるのは、「終了」にしていない入れ物のタスクだけ
+・トップ画面の一番上に、全体のゲージを細く1本だけ出す。押すと小さな窓が開き、全体と種類ごとのゲージが見える(小窓の細かい動きは UI 試作で決める)
+・「未分類」のタスクは、全体のゲージにだけ数え、種類ごとのゲージには入れない(F1)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・締切の前日に知らせる
+・手つかずのタスクを知らせる。締切のあるタスクは、締切の3日前(Claude の案)になっても作業記録が1つもないとき。締切のないタスクは、登録してから3日間(Claude の案)、作業記録も完了もないとき(「手つかずの通知を出す」をオフにした種類には出さない。初めは開発だけオフ。F1)
+・「手つかず」はタスクを選んだ作業記録だけで判断する。入れ物だけを選んだ記録は数えない。通知が来たら、その記録にタスクを選び直せば止まる
+・同じ作業記録が2時間(Claude の案)続いたら知らせる(切り替え忘れを防ぐため)
+・画面を閉じていても通知する。PC を起動したら裏の部分が自動で立ち上がる
+・PC の電源が切れていた間の通知は、次に画面を開いたときにまとめて見せる
+・(Should:F16 を作ったとき)着手日をつけたタスクは、着手日の翌日になっても作業記録が1つもないとき知らせる。締切の3日前の通知もそのまま残す</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:入れ物を消したとき、中のタスクと作業記録をどうするか → 消さずに終了にする
+済:学期が終わった授業をどう片付けるか → 終了にする
+済(点検で追加):「未分類」はどの種類か → 3種類の外の特別な入れ物。ラベルは灰色、全体のゲージにだけ数える
+済(追加55):種類を自分でカスタマイズできるか → 足す・名前と色を変える・消すことができる。種類ごとに「先に並べるか」「締切なしに手つかずの通知を出すか」の2つの設定を持つ</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1132,7 +1167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1197,6 +1232,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1538,7 +1576,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="F8" s="26"/>
       <c r="G8" s="26"/>
@@ -1564,7 +1602,7 @@
         <v>6</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="16.5">
@@ -1645,28 +1683,28 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16.5">
-      <c r="A2" s="6" t="s">
-        <v>13</v>
+    <row r="2" spans="1:9" ht="148.5">
+      <c r="A2" s="28" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="16.5">
       <c r="A3" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="C5" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="D5" s="16" t="s">
         <v>17</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>18</v>
       </c>
       <c r="E5" s="18"/>
       <c r="F5" s="16" t="s">
@@ -1683,19 +1721,19 @@
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
       <c r="D6" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>10</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>10</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>10</v>
@@ -1706,10 +1744,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>20</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>21</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="23">
@@ -1958,61 +1996,61 @@
   <sheetData>
     <row r="1" spans="1:3" ht="24">
       <c r="A1" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="16.5">
-      <c r="A2" s="6" t="s">
-        <v>13</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="66">
+      <c r="A2" s="28" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="16.5">
       <c r="A3" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="36" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" s="8"/>
     </row>
     <row r="6" spans="1:3" ht="36" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="54">
       <c r="A7" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="54">
       <c r="A8" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="81">
       <c r="A9" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>42</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2041,462 +2079,462 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24">
       <c r="A1" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="16.5">
-      <c r="A2" s="6" t="s">
-        <v>13</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="66">
+      <c r="A2" s="28" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="16.5">
       <c r="A3" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="16.5">
       <c r="A5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>30</v>
-      </c>
       <c r="G5" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="297">
+      <c r="A6" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G6" s="10" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="99">
-      <c r="A6" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="247.5">
+    <row r="7" spans="1:7" ht="280.5">
       <c r="A7" s="8"/>
       <c r="B7" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>47</v>
-      </c>
       <c r="D7" s="19" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="313.5">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="363">
       <c r="A8" s="8"/>
       <c r="B8" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>198</v>
+        <v>194</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>215</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="115.5">
       <c r="A9" s="8"/>
       <c r="B9" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="D9" s="19" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="82.5">
       <c r="A10" s="8"/>
       <c r="B10" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>52</v>
-      </c>
       <c r="D10" s="19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="264">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="330">
       <c r="A11" s="8"/>
       <c r="B11" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>170</v>
+        <v>162</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>216</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="132">
       <c r="A12" s="8"/>
       <c r="B12" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>55</v>
-      </c>
       <c r="D12" s="19" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="264">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="297">
       <c r="A13" s="8"/>
       <c r="B13" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>172</v>
+      <c r="D13" s="10" t="s">
+        <v>217</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>113</v>
+        <v>202</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="409.5">
       <c r="A14" s="8"/>
       <c r="B14" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>218</v>
+        <v>111</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>199</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="214.5">
       <c r="A15" s="8"/>
       <c r="B15" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>80</v>
-      </c>
       <c r="D15" s="19" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="409.5">
       <c r="A16" s="19"/>
       <c r="B16" s="19" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="165">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="214.5">
       <c r="A17" s="19"/>
       <c r="B17" s="19" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>145</v>
+        <v>203</v>
       </c>
       <c r="G17" s="25" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="409.5">
       <c r="A18" s="19"/>
       <c r="B18" s="19" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="G18" s="25" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="214.5">
       <c r="A19" s="19"/>
       <c r="B19" s="19" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="198">
       <c r="A20" s="19"/>
       <c r="B20" s="19" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="G20" s="25" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="94.5">
       <c r="A21" s="21"/>
       <c r="B21" s="21" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="121.5">
       <c r="A22" s="20"/>
       <c r="B22" s="20" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="G22" s="20" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="189">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="283.5">
       <c r="A23" s="20"/>
       <c r="B23" s="20" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="324">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="409.5">
       <c r="A24" s="20"/>
       <c r="B24" s="20" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="G24" s="20" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="121.5">
       <c r="A25" s="20"/>
       <c r="B25" s="20" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -2516,22 +2554,22 @@
   <sheetData>
     <row r="1" spans="1:1" ht="24">
       <c r="A1" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="16.5">
-      <c r="A2" s="6" t="s">
-        <v>13</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="99">
+      <c r="A2" s="28" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="16.5">
       <c r="A3" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="16.5">
       <c r="A5" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -2557,339 +2595,339 @@
   <sheetData>
     <row r="1" spans="1:4" ht="24">
       <c r="A1" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="16.5">
-      <c r="A2" s="6" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="66">
+      <c r="A2" s="28" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.5">
       <c r="A3" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16.5">
       <c r="A5" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="49.5">
       <c r="A6" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>59</v>
-      </c>
       <c r="C6" s="19" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16.5">
       <c r="A7" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="C7" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>61</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16.5">
       <c r="A8" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="33">
       <c r="A9" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>67</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16.5">
       <c r="A10" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="C10" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="D10" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="33">
       <c r="A11" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>74</v>
-      </c>
       <c r="C11" s="19" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="33">
       <c r="A12" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="16.5">
       <c r="A13" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D13" s="19" t="s">
         <v>125</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="33">
       <c r="A14" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="D14" s="19" t="s">
         <v>125</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="27">
       <c r="A15" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="D15" s="21" t="s">
         <v>125</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="D16" s="20" t="s">
         <v>125</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="54">
       <c r="A17" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="D17" s="20" t="s">
         <v>125</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="27">
       <c r="A18" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B18" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="D18" s="11" t="s">
         <v>82</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="C19" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>86</v>
-      </c>
       <c r="D19" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B20" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>88</v>
-      </c>
       <c r="D20" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B21" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="11" t="s">
-        <v>90</v>
-      </c>
       <c r="D21" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="54">
       <c r="A22" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="27">
       <c r="A23" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B23" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C23" s="11" t="s">
-        <v>93</v>
-      </c>
       <c r="D23" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B24" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="C24" s="11" t="s">
-        <v>95</v>
-      </c>
       <c r="D24" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="40.5">
       <c r="A25" s="20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="27">
       <c r="A26" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="D26" s="20" t="s">
         <v>117</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="C26" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="54">
       <c r="A27" s="20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>166</v>
+        <v>207</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>167</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>

--- a/docs/requirements-v0.1.xlsx
+++ b/docs/requirements-v0.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Workspace\02_開発\workbench\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DBD0E39-ED6C-495F-8E4F-E6C6699BC9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{506DD2F1-98FF-4276-AB10-2B7CA9DD0FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -196,9 +196,6 @@
     <t>F7 git からの取り込み</t>
   </si>
   <si>
-    <t>git のコミット履歴から、開発の作業記録を自動で取り込む</t>
-  </si>
-  <si>
     <t>F8 通知</t>
   </si>
   <si>
@@ -224,9 +221,6 @@
   </si>
   <si>
     <t>消えないこと</t>
-  </si>
-  <si>
-    <t>アプリや PC を再起動しても、入れ物・タスク・作業記録が残る</t>
   </si>
   <si>
     <t>再起動の前後で見比べる</t>
@@ -322,10 +316,6 @@
   </si>
   <si>
     <t>出どころ</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>grill-me(授業と開発を入れ物にする)/要件定義 問6</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -486,9 +476,6 @@
   </si>
   <si>
     <t>F11 就活</t>
-  </si>
-  <si>
-    <t>就活を入れ物の種類に足し、企業ごとに締切や面接日を管理する</t>
   </si>
   <si>
     <t>要件定義 追加の要望(就活は Google カレンダーや企業からの連絡が見たい)・追加4</t>
@@ -539,9 +526,6 @@
     <t>F15 開発の中身と進み具合</t>
   </si>
   <si>
-    <t>開発の入れ物ごとに、何を作ろうとしているかと、どこまで進んでいるかを出す</t>
-  </si>
-  <si>
     <t>要件定義 追加の要望(開発が何を作ろうとしていて、どこまで進んでいるかがわかる機能)・追加18</t>
   </si>
   <si>
@@ -586,14 +570,6 @@
   </si>
   <si>
     <t>Google は決めたことだけ</t>
-  </si>
-  <si>
-    <t>・登録したリポジトリのコミットを読む
-・1つのリポジトリに複数のアプリがある場合(lab)は、変更されたフォルダで入れ物に振り分ける
-・同じコミットを二重に取り込まない
-・アプリを起動したときと、10分ごと(Claude の案)に読む
-・コミットの時刻に、同じ入れ物の手の記録(F4)が動いていれば、その記録にコミットの内容をくっつける。なければ「その時刻に何をしたか」の点として並べ、作業時間の集計には入れない</t>
-    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>入れ物ごと・種類ごと・全体の進み具合を、ゲージで表示する</t>
@@ -681,18 +657,6 @@
     <t>要件定義 点検の差4・Google カレンダーのような機能を足したい・追加35〜40</t>
   </si>
   <si>
-    <t>済:どのメールを「大学からの連絡」とみなすか → 差出人が大学のアドレスのもの。授業・奨学金・試合のチケットを分けて見せる
-済:3種類に当てはまらない大学のメールをどうするか → 「その他」としてたたんで出す
-済:「学内連絡:」の一斉配信をどこまで拾うか → 3種類以外は全部「その他」に入る
-済:奨学金・試合のチケットの連絡をどこに出すか → それぞれ大学の入れ物にする
-済:授業への振り分け方 → 科目名で自動、外れたら選び直し、選び直しを覚える
-済:タスクの候補を、確認なしで登録するか → 自動で登録し、印をつけ、1回で消せる
-済:いつ読むか、Outlook が起動していないときの扱い → 起動時と10分ごと。閉じていれば裏で立ち上げる
-済(点検で追加):「その他」のメールから自動で入ったタスクの入れ物 → 未分類に入れて印をつける
-済(点検で追加):取り込んだ連絡をどこで見るか → 「連絡」の画面。トップは2段目に件数だけ</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>・入れ物の種類「就活」で、企業ごとに入れ物を1つ作る(エントリーしたときに自分で作る)
 ・ES の締切は、その企業の入れ物のタスクになる。面接日など日時が決まったものは、その企業の入れ物のスケジュール(F19)になる
 ・企業からの連絡(個人の Gmail)を取り込む。読み方は Google の公式の連携(API)。最初に一度、Google の画面で許可する。許可の鍵は PC の中にだけ置き、公開リポジトリに入れない
@@ -741,21 +705,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>大学の授業・就活の企業・開発プロジェクトを「入れ物」として登録・編集・削除する</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>今日・今週やることを、大学・就活・開発を混ぜて締切順に並べる</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・「何を作ろうとしているか」は、そのアプリの README があれば自動で読み、一番上の見出しのすぐ下の段落(空行まで)を出す。100文字(Claude の案)を超えたら、100文字で切って「…」をつける
-・README がないときや、その段落がないときは、自分で一言書ける。自分で書いた説明があれば、そちらを優先する
-・「どこまで進んでいるか」は、アプリの中に docs/spec-excel-status.md があれば、spec-excel の工程(要件定義〜テスト)のどこにいるかを出す。なければ、自分で選んだ状態(アイデア/作成中/動いている/休止)を出す
-・どちらの場合も、F6 の進み具合(完了したタスクの数 ÷ 全部の数)も並べて出す</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>済:「どこまで進んでいるか」を何で表すか → spec-excel の工程があればそれ、なければ自分で選んだ状態。F6 の割合も並べる
 済(点検で追加):README のどこを説明として出すか → 一番上の見出しのすぐ下の段落。100文字を超えたら切る</t>
     <phoneticPr fontId="8"/>
@@ -766,45 +715,6 @@
   </si>
   <si>
     <t>大学・就活・アルバイトと開発の一元管理</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・PC の Outlook アプリ(クラシック版)を読み取り専用で読む(モーニングブリーフと同じ方法)
-・アプリの起動時と10分ごと(Claude の案)に読む。Outlook が起動していなければ、裏で立ち上げて読む
-・読めなかったとき(サインイン切れなど)は推測で埋めず、画面に「大学のメールを読めませんでした」と出す
-・差出人が大学のアドレスのメールだけを対象にする。大学のアドレスの形(@ から後ろ)は PC の中の data/ の設定に置き、公開リポジトリの資料には書かない
-・その中から「授業」「奨学金」「試合のチケット」の連絡を分けて見せる
-・3種類に当てはまらない大学のメール(「学内連絡:」の一斉配信も含む)は、「その他」としてまとめ、3種類より下にたたんだ状態で置く
-・授業の連絡は、件名や本文に時間割の科目名が入っているかで、その授業の入れ物に振り分ける
-・振り分けを間違えたものや「その他」に入ったものは、自分で入れ物を選び直せる。選び直した結果を覚え、次から同じ差出人・同じ件名なら、その入れ物に入れる
-・「奨学金」「試合のチケット」は大学の入れ物として自動で作り、授業と同じように扱う
-・締切が書いてあるメールは、確認なしで自動でタスクにし、「メールから自動で入った」印をつける。間違っていたら1回の操作で消せ、消したものは次に読んだときに復活しない
-・「その他」のメールから自動で入ったタスクは、「未分類」の入れ物に入れ、「入れ物を選んで」の印をつける(F2)
-・学習サイトから大学のアドレスで届く通知メールも読む。本文にあるサイトへのリンクを画面に出し、自分でクリックして開ける。アプリがサイトを開くことはしない(X6)
-・休講・補講の連絡は、その授業の入れ物のスケジュール(F19)にする
-・取り込んだ連絡は「連絡」の画面で、授業・奨学金・試合のチケット・企業・アルバイト・その他に分けて見る。トップには2段目に「新しい連絡 ○件」と件数だけ出し、押すと「連絡」の画面が開く。開いたら件数は0に戻る(「見た」は workbench の中だけで覚え、メールの既読には触らない)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・タスクは必ず1つの入れ物に入る
-・締切(日付)をつけられる。締切のないタスクも登録できる
-・開発のタスクは、ふだんは締切を空のままにする。面接前のデモなど、必要なときだけつけられる
-・締切には時刻も入れられる(入れなくてもよい)。時刻のあるタスクは、同じ日の中で時刻順に並ぶ
-・毎週の繰り返しを作れる(例:毎週火曜 9:00まで)。1つ完了すると、次の週の分が自動で出る
-・完了にできる。合図を見つけて自動で完了になる場合は F18
-・入れ物が決まらないタスク(「その他」のメールから入ったもの、F17 の1行入力で読み取れなかったもの)は「未分類」の入れ物に入り、「入れ物を選んで」の印がつく。印から1クリックで入れ物を選べる
-・(Should:F16 を作ったとき)「着手日」(この日から始める)をつけられる
-・面接・補講など日時が決まったもの(始まりと終わりの時刻があるもの)は、タスクではなくスケジュール(F19)として持つ</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>済:締切を過ぎたタスクをどこに出すか → 一番上に「期限切れ」として出す
-済:締切が同じときの並び順 → 時刻順 → 大学・就活が先 → 登録が古い順(F11 で就活を足したときに直した)
-済(点検で追加):「一目でわかる印」とは何か → 入れ物名のラベル、色は大学・開発・就活の3色(F11 で就活を足したときに直した)
-済(点検で追加):2段目に何を出すか → 9つに決めた
-・1行入力の欄(F17)と、着手日で「今日」に上がったタスク(F16)の、トップでの置き場所と並び順
-・「今週」の範囲(何曜日から何曜日までか。F17 の「金」の読み方もこれに合わせる)
-→ 基本設計で決める</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -864,7 +774,142 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>・書き込むもの:タスクの締切(大学・就活・締切をつけた開発)、面接・面談、休講・補講、奨学金の手続きなど、締切か日時があるもの
+    <t>・一番上に、全体の進み具合のゲージを細く1本出す。そのすぐ下に、「トップに出す」を選んだ入れ物のゲージを出す(F6)
+・その下は役割ごとに3段に分ける。1段目:記録中の作業(F4)。2段目:お知らせ(あるときだけ出す)。3段目:「期限切れ」
+・2段目に出すものは次の9つ:①作業記録の再開の確認(F4)②PC の電源が切れていた間の通知(F8)③学期の終わりの米印(F10)④読めなかった・つながらなかった(F9・F10・F11・F12・F19)⑤読み込み中(非機能要件)⑥カレンダーに書かなかった予定(F13)⑦新しい連絡の件数(F9・F11・F20)⑧「終わっていそう」なタスクの件数(F18)⑨未分類の件数(F2)
+・「期限切れ」には、締切を過ぎたタスクを色を変えてまとめる。完了にするか締切を変えるまで残る
+・その下に、今日の時間(F10・F12)を出す
+・その下に「今日」と「今週」に分けて、締切の近い順に並べる
+・締切のないタスクは、その下に「締切なし」としてまとめて出す
+・同じ締切の日の中は、①時刻があるものは時刻順、時刻なしはその日の最後 ②同じなら「先に並べる」設定の種類を先(初めは大学・就活) ③さらに同じなら登録が古い順。「締切なし」の中は登録が古い順
+・各タスクに入れ物の名前のラベル(例:「卒論」「fx-practice」)をつけ、ラベルの色を種類ごとの色で分ける(F1)
+・「未分類」のタスクのラベルは灰色にする(F1)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・締切の前日に知らせる
+・手つかずのタスクを知らせる。締切のあるタスクは、締切の3日前(Claude の案)になっても作業記録が1つもないとき。締切のないタスクは、登録してから3日間(Claude の案)、作業記録も完了もないとき(「手つかずの通知を出す」をオフにした種類には出さない。初めは開発だけオフ。F1)
+・「手つかず」はタスクを選んだ作業記録だけで判断する。入れ物だけを選んだ記録は数えない。通知が来たら、その記録にタスクを選び直せば止まる
+・同じ作業記録が2時間(Claude の案)続いたら知らせる(切り替え忘れを防ぐため)
+・画面を閉じていても通知する。PC を起動したら裏の部分が自動で立ち上がる
+・PC の電源が切れていた間の通知は、次に画面を開いたときにまとめて見せる
+・(Should:F16 を作ったとき)着手日をつけたタスクは、着手日の翌日になっても作業記録が1つもないとき知らせる。締切の3日前の通知もそのまま残す</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>入れ物の種類(初めは大学・就活・開発。自分で足せる)と、その中の入れ物(授業・企業・アプリなど)を登録・編集・削除する</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>今日・今週やることを、種類を混ぜて締切順に並べる</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>「就活」の種類で企業ごとに入れ物を作り、締切や面接日を管理する</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・入れ物の種類は、初めは「大学」「就活」「開発」の3つ。種類は自分で足す・名前と色を変える・消すことができる。中に入れ物がある種類は消せない
+・種類ごとに2つの設定を持つ:①同じ締切のとき先に並べるか(初めは大学・就活がオン)②締切のないタスクに手つかずの通知を出すか(初めは開発だけオフ)
+・F9・F10 が自動で作る入れ物は「大学」の種類に、F11 の企業は「就活」の種類に入る。名前を変えても同じ種類として扱う
+・タスクと作業記録は、どれか1つの入れ物に入る
+・入れ物は消さずに「終了」にしてしまう。終了にすると一覧とトップ画面から見えなくなり、中身は残る。あとで戻せる
+・完全に消せるのは、中身が空の入れ物だけ
+・学期が終わった授業も「終了」にして片付ける
+・種類とは別に、特別な入れ物「未分類」が1つだけある。入れ物が決まらないタスクの一時的な置き場所(F2)。ラベルは灰色。進み具合は全体のゲージには数えるが、種類ごとのゲージには入れない。締切のないタスクの手つかずの通知(F8)は、ほかと同じく登録から3日で出す
+・初めからある「大学」「就活」「開発」の3つは消せない(名前と色は変えられる)。メールや時間割から自動で作る入れ物の行き先になるため
+・灰色は「未分類」だけの色にし、種類の色には選べない
+・「中に入れ物がある種類は消せない」の入れ物には、「終了」にした入れ物も含む。種類を消したいときは、中の入れ物をほかの種類に移す。入れ物の種類はあとから変えられる
+・自分で「アルバイト」などの種類を作るのは自由。F20 のアルバイトの面接は、種類があってもなくても、入れ物なしのスケジュールとして動く</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:入れ物を消したとき、中のタスクと作業記録をどうするか → 消さずに終了にする
+済:学期が終わった授業をどう片付けるか → 終了にする
+済(点検で追加):「未分類」はどの種類か → 3種類の外の特別な入れ物。ラベルは灰色、全体のゲージにだけ数える
+済(追加55):種類を自分でカスタマイズできるか → 足す・名前と色を変える・消すことができる。種類ごとに「先に並べるか」「締切なしに手つかずの通知を出すか」の2つの設定を持つ
+済(点検で追加):初めの3種類を消せるか → 消せない(名前と色は変えられる)
+済(点検で追加):灰色を種類に選べるか → 選べない(未分類だけの色)
+済(点検で追加):終了した入れ物が残る種類を消せるか → 消せない。入れ物をほかの種類に移せる
+済(点検で追加):自分で作ったアルバイトの種類と F20 → 種類は作れる。F20 は入れ物なしのまま</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>grill-me(授業と開発を入れ物にする)/要件定義 問6・追加55・56(種類のカスタマイズ)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・タスクは必ず1つの入れ物に入る
+・締切(日付)をつけられる。締切のないタスクも登録できる
+・開発のタスク(初めは「開発」の種類)は、ふだんは締切を空のままにする。面接前のデモなど、必要なときだけつけられる
+・締切には時刻も入れられる(入れなくてもよい)。時刻のあるタスクは、同じ日の中で時刻順に並ぶ
+・毎週の繰り返しを作れる(例:毎週火曜 9:00まで)。1つ完了すると、次の週の分が自動で出る
+・完了にできる。合図を見つけて自動で完了になる場合は F18
+・入れ物が決まらないタスク(「その他」のメールから入ったもの、F17 の1行入力で読み取れなかったもの)は「未分類」の入れ物に入り、「入れ物を選んで」の印がつく。印から1クリックで入れ物を選べる
+・(Should:F16 を作ったとき)「着手日」(この日から始める)をつけられる
+・面接・補講など日時が決まったもの(始まりと終わりの時刻があるもの)は、タスクではなくスケジュール(F19)として持つ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>git のコミット履歴から、リポジトリを登録した入れ物の作業記録を自動で取り込む</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・登録したリポジトリのコミットを読む
+・1つのリポジトリに複数のアプリがある場合(lab)は、変更されたフォルダで入れ物に振り分ける
+・同じコミットを二重に取り込まない
+・アプリを起動したときと、10分ごと(Claude の案)に読む
+・コミットの時刻に、同じ入れ物の手の記録(F4)が動いていれば、その記録にコミットの内容をくっつける。なければ「その時刻に何をしたか」の点として並べ、作業時間の集計には入れない
+・リポジトリは入れ物に登録する。登録できる入れ物の種類は問わない(初めは「開発」で使う想定)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>リポジトリを登録した入れ物ごとに、何を作ろうとしているかと、どこまで進んでいるかを出す</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・「何を作ろうとしているか」は、そのアプリの README があれば自動で読み、一番上の見出しのすぐ下の段落(空行まで)を出す。100文字(Claude の案)を超えたら、100文字で切って「…」をつける
+・README がないときや、その段落がないときは、自分で一言書ける。自分で書いた説明があれば、そちらを優先する
+・「どこまで進んでいるか」は、アプリの中に docs/spec-excel-status.md があれば、spec-excel の工程(要件定義〜テスト)のどこにいるかを出す。なければ、自分で選んだ状態(アイデア/作成中/動いている/休止)を出す
+・どちらの場合も、F6 の進み具合(完了したタスクの数 ÷ 全部の数)も並べて出す
+・この表示は、F7 でリポジトリを登録した入れ物に出る(種類は問わない)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:締切を過ぎたタスクをどこに出すか → 一番上に「期限切れ」として出す
+済:締切が同じときの並び順 → 時刻順 → 「先に並べる」設定の種類が先(初めは大学・就活)→ 登録が古い順
+済(点検で追加):「一目でわかる印」とは何か → 入れ物名のラベル、色は種類ごとの色(F1。未分類は灰色)
+済(点検で追加):2段目に何を出すか → 9つに決めた
+・1行入力の欄(F17)と、着手日で「今日」に上がったタスク(F16)の、トップでの置き場所と並び順
+・「今週」の範囲(何曜日から何曜日までか。F17 の「金」の読み方もこれに合わせる)
+→ 基本設計で決める</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:タスクが0件の入れ物をどう表示するか → 「タスクなし」と文字で出す
+済:どの画面に出すか → トップは今日・今週にタスクがある入れ物+自分で選んだ入れ物、一覧画面は全部
+済:全体のゲージを何で出すか → 種類ごと(初めは大学・就活・開発)と全体
+済:種類ごと・全体で何を数えるか → 「終了」にしていない入れ物のタスクだけ
+済:全体と種類ごとのゲージをどこに出すか → トップの一番上に全体を細く1本、押すと小窓で種類ごと
+済(点検で追加):入れ物ごとのゲージをトップのどこに出すか → 選んだ入れ物は全体のすぐ下にいつも、今日・今週の入れ物は小窓の中(図で比べた)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・完了したタスクの数 ÷ 全部のタスクの数
+・タスクが0件の入れ物は、数字やバーを出さずに「タスクなし」と出す
+・トップ画面では、「トップに出す」を選んだ入れ物のゲージを、全体のゲージのすぐ下にいつも出す。今日・今週にタスクがある入れ物のゲージは、全体のゲージを押して開く小窓の中に、全体と種類ごとのゲージに続けて並べる
+・入れ物ごとに「トップに出す」を自分で選べる。選んだ入れ物は、タスクがなくてもトップに出る
+・入れ物の一覧画面には、全部の入れ物の進み具合を出す
+・進み具合はゲージ(横に伸びるバー)と「○% 完了」で出す
+・入れ物ごとのゲージに加えて、種類ごと(初めは大学・就活・開発)と全体のゲージを出す
+・種類ごと・全体で数えるのは、「終了」にしていない入れ物のタスクだけ
+・トップ画面の一番上に、全体のゲージを細く1本だけ出す。押すと小さな窓が開き、全体と種類ごとのゲージが見える(小窓の細かい動きは UI 試作で決める)
+・「未分類」のタスクは、全体のゲージにだけ数え、種類ごとのゲージには入れない(F1)
+・タスクが0件の種類のゲージも、入れ物と同じく「タスクなし」と出す</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・書き込むもの:タスクの締切(種類を問わず、締切のあるもの)、面接・面談、休講・補講、奨学金の手続きなど、締切か日時があるもの
 ・「その他」のメールから自動で入ったものは書き込まない
 ・面接など日時の決まったものは、時刻つきの予定にする。締切は全部終日の予定にし、時刻は名前に書く(例:「締切 23:59 第10回レポート」)
 ・書けなかった予定は、workbench の中に「書けなかった予定」として一時的に残す。Google に接続できなかったときは、つながったら自動でもう一度書く。重なる予定があって書かなかったときは、2段目のお知らせに「重なる予定があるため書いていません」と出し、「それでも書く」「書かない」を選べる。書けたら、または「書かない」を選んだら、一時的な分は消す
@@ -886,13 +931,43 @@
 ・未分類から入れ物を選び直したタスクを、カレンダーに書くか
 → 基本設計で決める
 済(点検で追加):Google に書けなかった予定 → workbench に一時的に残し、つながったら書き直す。重なりは2段目で選ぶ
-済(点検で追加):締切の予定がタスクと2回出る件、Google 側で動かしたとき → 画面には1回だけ。Google で動かしたらタスクの締切も合わせる</t>
+済(点検で追加):締切の予定がタスクと2回出る件、Google 側で動かしたとき → 画面には1回だけ。Google で動かしたらタスクの締切も合わせる
+済(点検で追加):自分で足した種類のタスクの締切も書くか → 書く(種類を問わない)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・PC の Outlook アプリ(クラシック版)を読み取り専用で読む(モーニングブリーフと同じ方法)
+・アプリの起動時と10分ごと(Claude の案)に読む。Outlook が起動していなければ、裏で立ち上げて読む
+・読めなかったとき(サインイン切れなど)は推測で埋めず、画面に「大学のメールを読めませんでした」と出す
+・差出人が大学のアドレスのメールだけを対象にする。大学のアドレスの形(@ から後ろ)は PC の中の data/ の設定に置き、公開リポジトリの資料には書かない
+・その中から「授業」「奨学金」「試合のチケット」の連絡を分けて見せる
+・3つの分類に当てはまらない大学のメール(「学内連絡:」の一斉配信も含む)は、「その他」としてまとめ、3つの分類より下にたたんだ状態で置く
+・授業の連絡は、件名や本文に時間割の科目名が入っているかで、その授業の入れ物に振り分ける
+・振り分けを間違えたものや「その他」に入ったものは、自分で入れ物を選び直せる。選び直した結果を覚え、次から同じ差出人・同じ件名なら、その入れ物に入れる
+・「奨学金」「試合のチケット」は大学の入れ物として自動で作り、授業と同じように扱う
+・締切が書いてあるメールは、確認なしで自動でタスクにし、「メールから自動で入った」印をつける。間違っていたら1回の操作で消せ、消したものは次に読んだときに復活しない
+・「その他」のメールから自動で入ったタスクは、「未分類」の入れ物に入れ、「入れ物を選んで」の印をつける(F2)
+・学習サイトから大学のアドレスで届く通知メールも読む。本文にあるサイトへのリンクを画面に出し、自分でクリックして開ける。アプリがサイトを開くことはしない(X6)
+・休講・補講の連絡は、その授業の入れ物のスケジュール(F19)にする
+・取り込んだ連絡は「連絡」の画面で、授業・奨学金・試合のチケット・企業・アルバイト・その他に分けて見る。トップには2段目に「新しい連絡 ○件」と件数だけ出し、押すと「連絡」の画面が開く。開いたら件数は0に戻る(「見た」は workbench の中だけで覚え、メールの既読には触らない)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:どのメールを「大学からの連絡」とみなすか → 差出人が大学のアドレスのもの。授業・奨学金・試合のチケットを分けて見せる
+済:3つの分類に当てはまらない大学のメールをどうするか → 「その他」としてたたんで出す
+済:「学内連絡:」の一斉配信をどこまで拾うか → 3つの分類以外は全部「その他」に入る
+済:奨学金・試合のチケットの連絡をどこに出すか → それぞれ大学の入れ物にする
+済:授業への振り分け方 → 科目名で自動、外れたら選び直し、選び直しを覚える
+済:タスクの候補を、確認なしで登録するか → 自動で登録し、印をつけ、1回で消せる
+済:いつ読むか、Outlook が起動していないときの扱い → 起動時と10分ごと。閉じていれば裏で立ち上げる
+済(点検で追加):「その他」のメールから自動で入ったタスクの入れ物 → 未分類に入れて印をつける
+済(点検で追加):取り込んだ連絡をどこで見るか → 「連絡」の画面。トップは2段目に件数だけ</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>・予定の本体は Google カレンダー(個人のアカウントのメインのカレンダー)に置く。workbench の中に別の写しは持たない。ただし、Google に書けなかった予定だけは一時的に預かる(F13)
 ・workbench で予定を足す・直す・消すと、その場で Google カレンダーにも反映する
-・Google カレンダーで足した・直した予定(スマホからも)は、画面を開いたときと10分ごと(Claude の案)に読んで出す
+・Google カレンダーで足した・直した予定(スマホからも)は、アプリの起動時と10分ごと(Claude の案)に読んで出す
 ・時間割の授業(F10)とタスクの締切も、同じ画面にまとめて出す
 ・面接・面談・補講・休講など日時が決まったものは、スケジュールとして持つ。完了はなく、進み具合のゲージにも数えない
 ・スケジュールは入れ物に入れられる(企業の面接はその企業の入れ物など)。入れ物なしでも持てる(アルバイトの面接 F20、Google カレンダーで足した予定など)
@@ -906,66 +981,7 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>済:タスクが0件の入れ物をどう表示するか → 「タスクなし」と文字で出す
-済:どの画面に出すか → トップは今日・今週にタスクがある入れ物+自分で選んだ入れ物、一覧画面は全部
-済:全体のゲージを何で出すか → 種類ごと(大学・就活・開発)と全体
-済:種類ごと・全体で何を数えるか → 「終了」にしていない入れ物のタスクだけ
-済:全体と種類ごとのゲージをどこに出すか → トップの一番上に全体を細く1本、押すと小窓で種類ごと
-済(点検で追加):入れ物ごとのゲージをトップのどこに出すか → 選んだ入れ物は全体のすぐ下にいつも、今日・今週の入れ物は小窓の中(図で比べた)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・入れ物の種類は、初めは「大学」「就活」「開発」の3つ。種類は自分で足す・名前と色を変える・消すことができる。中に入れ物がある種類は消せない
-・種類ごとに2つの設定を持つ:①同じ締切のとき先に並べるか(初めは大学・就活がオン)②締切のないタスクに手つかずの通知を出すか(初めは開発だけオフ)
-・F9・F10 が自動で作る入れ物は「大学」の種類に、F11 の企業は「就活」の種類に入る。名前を変えても同じ種類として扱う
-・タスクと作業記録は、どれか1つの入れ物に入る
-・入れ物は消さずに「終了」にしてしまう。終了にすると一覧とトップ画面から見えなくなり、中身は残る。あとで戻せる
-・完全に消せるのは、中身が空の入れ物だけ
-・学期が終わった授業も「終了」にして片付ける
-・種類とは別に、特別な入れ物「未分類」が1つだけある。入れ物が決まらないタスクの一時的な置き場所(F2)。ラベルは灰色。進み具合は全体のゲージには数えるが、種類ごとのゲージには入れない。締切のないタスクの手つかずの通知(F8)は、ほかと同じく登録から3日で出す</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・一番上に、全体の進み具合のゲージを細く1本出す。そのすぐ下に、「トップに出す」を選んだ入れ物のゲージを出す(F6)
-・その下は役割ごとに3段に分ける。1段目:記録中の作業(F4)。2段目:お知らせ(あるときだけ出す)。3段目:「期限切れ」
-・2段目に出すものは次の9つ:①作業記録の再開の確認(F4)②PC の電源が切れていた間の通知(F8)③学期の終わりの米印(F10)④読めなかった・つながらなかった(F9・F10・F11・F12・F19)⑤読み込み中(非機能要件)⑥カレンダーに書かなかった予定(F13)⑦新しい連絡の件数(F9・F11・F20)⑧「終わっていそう」なタスクの件数(F18)⑨未分類の件数(F2)
-・「期限切れ」には、締切を過ぎたタスクを色を変えてまとめる。完了にするか締切を変えるまで残る
-・その下に、今日の時間(F10・F12)を出す
-・その下に「今日」と「今週」に分けて、締切の近い順に並べる
-・締切のないタスクは、その下に「締切なし」としてまとめて出す
-・同じ締切の日の中は、①時刻があるものは時刻順、時刻なしはその日の最後 ②同じなら「先に並べる」設定の種類を先(初めは大学・就活) ③さらに同じなら登録が古い順。「締切なし」の中は登録が古い順
-・各タスクに入れ物の名前のラベル(例:「卒論」「fx-practice」)をつけ、ラベルの色を種類ごとの色で分ける(F1)
-・「未分類」のタスクのラベルは灰色にする(F1)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・完了したタスクの数 ÷ 全部のタスクの数
-・タスクが0件の入れ物は、数字やバーを出さずに「タスクなし」と出す
-・トップ画面では、「トップに出す」を選んだ入れ物のゲージを、全体のゲージのすぐ下にいつも出す。今日・今週にタスクがある入れ物のゲージは、全体のゲージを押して開く小窓の中に、全体と種類ごとのゲージに続けて並べる
-・入れ物ごとに「トップに出す」を自分で選べる。選んだ入れ物は、タスクがなくてもトップに出る
-・入れ物の一覧画面には、全部の入れ物の進み具合を出す
-・進み具合はゲージ(横に伸びるバー)と「○% 完了」で出す
-・入れ物ごとのゲージに加えて、種類ごと(初めは大学・就活・開発)と全体のゲージを出す
-・種類ごと・全体で数えるのは、「終了」にしていない入れ物のタスクだけ
-・トップ画面の一番上に、全体のゲージを細く1本だけ出す。押すと小さな窓が開き、全体と種類ごとのゲージが見える(小窓の細かい動きは UI 試作で決める)
-・「未分類」のタスクは、全体のゲージにだけ数え、種類ごとのゲージには入れない(F1)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・締切の前日に知らせる
-・手つかずのタスクを知らせる。締切のあるタスクは、締切の3日前(Claude の案)になっても作業記録が1つもないとき。締切のないタスクは、登録してから3日間(Claude の案)、作業記録も完了もないとき(「手つかずの通知を出す」をオフにした種類には出さない。初めは開発だけオフ。F1)
-・「手つかず」はタスクを選んだ作業記録だけで判断する。入れ物だけを選んだ記録は数えない。通知が来たら、その記録にタスクを選び直せば止まる
-・同じ作業記録が2時間(Claude の案)続いたら知らせる(切り替え忘れを防ぐため)
-・画面を閉じていても通知する。PC を起動したら裏の部分が自動で立ち上がる
-・PC の電源が切れていた間の通知は、次に画面を開いたときにまとめて見せる
-・(Should:F16 を作ったとき)着手日をつけたタスクは、着手日の翌日になっても作業記録が1つもないとき知らせる。締切の3日前の通知もそのまま残す</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>済:入れ物を消したとき、中のタスクと作業記録をどうするか → 消さずに終了にする
-済:学期が終わった授業をどう片付けるか → 終了にする
-済(点検で追加):「未分類」はどの種類か → 3種類の外の特別な入れ物。ラベルは灰色、全体のゲージにだけ数える
-済(追加55):種類を自分でカスタマイズできるか → 足す・名前と色を変える・消すことができる。種類ごとに「先に並べるか」「締切なしに手つかずの通知を出すか」の2つの設定を持つ</t>
+    <t>アプリや PC を再起動しても、入れ物・タスク・作業記録・種類とその設定・トップに出す選択・バイト先の一覧・振り分けの覚え・一時的に預かった「書けなかった予定」が残る</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1576,7 +1592,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="F8" s="26"/>
       <c r="G8" s="26"/>
@@ -1602,7 +1618,7 @@
         <v>6</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="16.5">
@@ -1685,7 +1701,7 @@
     </row>
     <row r="2" spans="1:9" ht="148.5">
       <c r="A2" s="28" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="16.5">
@@ -2001,7 +2017,7 @@
     </row>
     <row r="2" spans="1:3" ht="66">
       <c r="A2" s="28" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="16.5">
@@ -2023,10 +2039,10 @@
         <v>23</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="54">
@@ -2034,7 +2050,7 @@
         <v>37</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="54">
@@ -2042,7 +2058,7 @@
         <v>39</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="81">
@@ -2084,7 +2100,7 @@
     </row>
     <row r="2" spans="1:7" ht="66">
       <c r="A2" s="28" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="16.5">
@@ -2112,10 +2128,10 @@
         <v>29</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="297">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="409.5">
       <c r="A6" s="8" t="s">
         <v>39</v>
       </c>
@@ -2123,19 +2139,19 @@
         <v>43</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>214</v>
+        <v>199</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>202</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>96</v>
+      <c r="F6" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="280.5">
@@ -2147,16 +2163,16 @@
         <v>46</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>44</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="363">
@@ -2165,19 +2181,19 @@
         <v>47</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>215</v>
+        <v>200</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>197</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>44</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="115.5">
@@ -2189,16 +2205,16 @@
         <v>49</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>44</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="82.5">
@@ -2210,331 +2226,331 @@
         <v>51</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>44</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="330">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="363">
       <c r="A11" s="8"/>
       <c r="B11" s="8" t="s">
         <v>52</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>216</v>
+        <v>156</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>212</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>44</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="132">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="165">
       <c r="A12" s="8"/>
       <c r="B12" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>54</v>
+      <c r="C12" s="19" t="s">
+        <v>206</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>161</v>
+        <v>207</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>44</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="297">
       <c r="A13" s="8"/>
       <c r="B13" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>217</v>
+      <c r="D13" s="19" t="s">
+        <v>198</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>44</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="409.5">
       <c r="A14" s="8"/>
       <c r="B14" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>44</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>182</v>
+        <v>216</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="214.5">
       <c r="A15" s="8"/>
       <c r="B15" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>44</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="409.5">
       <c r="A16" s="19"/>
       <c r="B16" s="19" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>136</v>
+        <v>201</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="E16" s="19" t="s">
         <v>44</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="214.5">
       <c r="A17" s="19"/>
       <c r="B17" s="19" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="E17" s="19" t="s">
         <v>44</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="G17" s="25" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="409.5">
       <c r="A18" s="19"/>
       <c r="B18" s="19" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E18" s="19" t="s">
         <v>44</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="G18" s="25" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="214.5">
       <c r="A19" s="19"/>
       <c r="B19" s="19" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E19" s="19" t="s">
         <v>44</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="198">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="231">
       <c r="A20" s="19"/>
       <c r="B20" s="19" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>150</v>
+        <v>208</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="E20" s="19" t="s">
         <v>44</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="G20" s="25" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="94.5">
       <c r="A21" s="21"/>
       <c r="B21" s="21" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="121.5">
       <c r="A22" s="20"/>
       <c r="B22" s="20" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D22" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="E22" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="E22" s="20" t="s">
-        <v>176</v>
-      </c>
       <c r="F22" s="20" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="G22" s="20" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="283.5">
       <c r="A23" s="20"/>
       <c r="B23" s="20" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="409.5">
       <c r="A24" s="20"/>
       <c r="B24" s="20" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="E24" s="20" t="s">
         <v>44</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="G24" s="20" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="121.5">
       <c r="A25" s="20"/>
       <c r="B25" s="20" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -2559,7 +2575,7 @@
     </row>
     <row r="2" spans="1:1" ht="99">
       <c r="A2" s="28" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="16.5">
@@ -2600,7 +2616,7 @@
     </row>
     <row r="2" spans="1:4" ht="66">
       <c r="A2" s="28" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.5">
@@ -2624,310 +2640,310 @@
     </row>
     <row r="6" spans="1:4" ht="49.5">
       <c r="A6" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>58</v>
-      </c>
       <c r="C6" s="19" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16.5">
       <c r="A7" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="C7" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="D7" s="8" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="49.5">
+      <c r="A8" s="8" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="16.5">
-      <c r="A8" s="8" t="s">
+      <c r="B8" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="33">
       <c r="A9" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16.5">
       <c r="A10" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="D10" s="8" t="s">
         <v>69</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="33">
       <c r="A11" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="33">
       <c r="A12" s="19" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="16.5">
       <c r="A13" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" s="19" t="s">
         <v>122</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="33">
       <c r="A14" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D14" s="19" t="s">
         <v>122</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="27">
       <c r="A15" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D15" s="21" t="s">
         <v>122</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>129</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="20" t="s">
         <v>122</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="54">
       <c r="A17" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="D17" s="20" t="s">
         <v>122</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="27">
       <c r="A18" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B18" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>80</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>85</v>
-      </c>
       <c r="D19" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="54">
       <c r="A22" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="27">
       <c r="A23" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="40.5">
       <c r="A25" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="27">
       <c r="A26" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="D26" s="20" t="s">
         <v>114</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="C26" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="54">
       <c r="A27" s="20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>

--- a/docs/requirements-v0.1.xlsx
+++ b/docs/requirements-v0.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Workspace\02_開発\workbench\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{506DD2F1-98FF-4276-AB10-2B7CA9DD0FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DCA7E33-21A4-4C8E-BFC4-1B5DB018206B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -46,9 +46,6 @@
     <t>workbench(作業台)</t>
   </si>
   <si>
-    <t>ver.0.1</t>
-  </si>
-  <si>
     <t>利用者承認</t>
   </si>
   <si>
@@ -283,9 +280,6 @@
   </si>
   <si>
     <t>C1 費用</t>
-  </si>
-  <si>
-    <t>費用は0円。有料のサービスや API は使わない</t>
   </si>
   <si>
     <t>C2 体制</t>
@@ -727,12 +721,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>済:どのカレンダーを読むか → 個人のアカウントのメインのカレンダーだけ
-・Google カレンダーをいつ読むか(案:起動時と10分ごと。F19 と同じ)
-→ 基本設計で決める</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>済:何を読み取るか → 締切と入れ物の両方
 済:読み取れなかったとき → すぐ入れて、未分類と印であとから直す(図で比べた)
 ・読み取る日付の書き方の範囲(「金」「10/25」「明日」のほかに何を読むか)
@@ -757,33 +745,6 @@
   </si>
   <si>
     <t>Gmail は読むだけ(送信・削除・既読化をしない)。Google カレンダーで、自動で書き換え・削除するのは目印のある予定だけ。手で直せるのは、自分が作った予定と、トグルで許した招待された予定だけ。許可の鍵は公開リポジトリに入れない</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>Gmail に読む以外の操作がないこと、自動の処理が目印のない予定を変えないこと、トグルを入れていない招待された予定を直せないことを確かめる</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・F10 の今日の授業と同じ「今日の時間」の列に、今日の予定を混ぜて時刻順に並べる
-・空き時間は書かない
-・読むのは個人の Google アカウントのメインのカレンダーだけ
-・読み方は F11 と同じ Google の公式の連携(API)。読めなかったときは、推測で埋めず「Google に接続できませんでした」と出す
-・アルバイトの予定は、入れ物を作らず、ここに予定として出す。入れ方は F14 のシフト表の写真か、Google カレンダーへの直接入力
-・今日より先の予定は、F19 のスケジュールの画面で見る
-・workbench が書いた締切の予定は、F12 の「今日の時間」と F19 のスケジュールの画面では、タスクとして1回だけ出す(予定としては出さない)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・一番上に、全体の進み具合のゲージを細く1本出す。そのすぐ下に、「トップに出す」を選んだ入れ物のゲージを出す(F6)
-・その下は役割ごとに3段に分ける。1段目:記録中の作業(F4)。2段目:お知らせ(あるときだけ出す)。3段目:「期限切れ」
-・2段目に出すものは次の9つ:①作業記録の再開の確認(F4)②PC の電源が切れていた間の通知(F8)③学期の終わりの米印(F10)④読めなかった・つながらなかった(F9・F10・F11・F12・F19)⑤読み込み中(非機能要件)⑥カレンダーに書かなかった予定(F13)⑦新しい連絡の件数(F9・F11・F20)⑧「終わっていそう」なタスクの件数(F18)⑨未分類の件数(F2)
-・「期限切れ」には、締切を過ぎたタスクを色を変えてまとめる。完了にするか締切を変えるまで残る
-・その下に、今日の時間(F10・F12)を出す
-・その下に「今日」と「今週」に分けて、締切の近い順に並べる
-・締切のないタスクは、その下に「締切なし」としてまとめて出す
-・同じ締切の日の中は、①時刻があるものは時刻順、時刻なしはその日の最後 ②同じなら「先に並べる」設定の種類を先(初めは大学・就活) ③さらに同じなら登録が古い順。「締切なし」の中は登録が古い順
-・各タスクに入れ物の名前のラベル(例:「卒論」「fx-practice」)をつけ、ラベルの色を種類ごとの色で分ける(F1)
-・「未分類」のタスクのラベルは灰色にする(F1)</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -824,17 +785,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>済:入れ物を消したとき、中のタスクと作業記録をどうするか → 消さずに終了にする
-済:学期が終わった授業をどう片付けるか → 終了にする
-済(点検で追加):「未分類」はどの種類か → 3種類の外の特別な入れ物。ラベルは灰色、全体のゲージにだけ数える
-済(追加55):種類を自分でカスタマイズできるか → 足す・名前と色を変える・消すことができる。種類ごとに「先に並べるか」「締切なしに手つかずの通知を出すか」の2つの設定を持つ
-済(点検で追加):初めの3種類を消せるか → 消せない(名前と色は変えられる)
-済(点検で追加):灰色を種類に選べるか → 選べない(未分類だけの色)
-済(点検で追加):終了した入れ物が残る種類を消せるか → 消せない。入れ物をほかの種類に移せる
-済(点検で追加):自分で作ったアルバイトの種類と F20 → 種類は作れる。F20 は入れ物なしのまま</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>grill-me(授業と開発を入れ物にする)/要件定義 問6・追加55・56(種類のカスタマイズ)</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -855,15 +805,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>・登録したリポジトリのコミットを読む
-・1つのリポジトリに複数のアプリがある場合(lab)は、変更されたフォルダで入れ物に振り分ける
-・同じコミットを二重に取り込まない
-・アプリを起動したときと、10分ごと(Claude の案)に読む
-・コミットの時刻に、同じ入れ物の手の記録(F4)が動いていれば、その記録にコミットの内容をくっつける。なければ「その時刻に何をしたか」の点として並べ、作業時間の集計には入れない
-・リポジトリは入れ物に登録する。登録できる入れ物の種類は問わない(初めは「開発」で使う想定)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>リポジトリを登録した入れ物ごとに、何を作ろうとしているかと、どこまで進んでいるかを出す</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -883,56 +824,6 @@
 ・1行入力の欄(F17)と、着手日で「今日」に上がったタスク(F16)の、トップでの置き場所と並び順
 ・「今週」の範囲(何曜日から何曜日までか。F17 の「金」の読み方もこれに合わせる)
 → 基本設計で決める</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>済:タスクが0件の入れ物をどう表示するか → 「タスクなし」と文字で出す
-済:どの画面に出すか → トップは今日・今週にタスクがある入れ物+自分で選んだ入れ物、一覧画面は全部
-済:全体のゲージを何で出すか → 種類ごと(初めは大学・就活・開発)と全体
-済:種類ごと・全体で何を数えるか → 「終了」にしていない入れ物のタスクだけ
-済:全体と種類ごとのゲージをどこに出すか → トップの一番上に全体を細く1本、押すと小窓で種類ごと
-済(点検で追加):入れ物ごとのゲージをトップのどこに出すか → 選んだ入れ物は全体のすぐ下にいつも、今日・今週の入れ物は小窓の中(図で比べた)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・完了したタスクの数 ÷ 全部のタスクの数
-・タスクが0件の入れ物は、数字やバーを出さずに「タスクなし」と出す
-・トップ画面では、「トップに出す」を選んだ入れ物のゲージを、全体のゲージのすぐ下にいつも出す。今日・今週にタスクがある入れ物のゲージは、全体のゲージを押して開く小窓の中に、全体と種類ごとのゲージに続けて並べる
-・入れ物ごとに「トップに出す」を自分で選べる。選んだ入れ物は、タスクがなくてもトップに出る
-・入れ物の一覧画面には、全部の入れ物の進み具合を出す
-・進み具合はゲージ(横に伸びるバー)と「○% 完了」で出す
-・入れ物ごとのゲージに加えて、種類ごと(初めは大学・就活・開発)と全体のゲージを出す
-・種類ごと・全体で数えるのは、「終了」にしていない入れ物のタスクだけ
-・トップ画面の一番上に、全体のゲージを細く1本だけ出す。押すと小さな窓が開き、全体と種類ごとのゲージが見える(小窓の細かい動きは UI 試作で決める)
-・「未分類」のタスクは、全体のゲージにだけ数え、種類ごとのゲージには入れない(F1)
-・タスクが0件の種類のゲージも、入れ物と同じく「タスクなし」と出す</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・書き込むもの:タスクの締切(種類を問わず、締切のあるもの)、面接・面談、休講・補講、奨学金の手続きなど、締切か日時があるもの
-・「その他」のメールから自動で入ったものは書き込まない
-・面接など日時の決まったものは、時刻つきの予定にする。締切は全部終日の予定にし、時刻は名前に書く(例:「締切 23:59 第10回レポート」)
-・書けなかった予定は、workbench の中に「書けなかった予定」として一時的に残す。Google に接続できなかったときは、つながったら自動でもう一度書く。重なる予定があって書かなかったときは、2段目のお知らせに「重なる予定があるため書いていません」と出し、「それでも書く」「書かない」を選べる。書けたら、または「書かない」を選んだら、一時的な分は消す
-・書き込み先は、F12 と同じ個人のアカウントのメインのカレンダー
-・タスクやメールから自動で書いた予定には目印をつける。F19 の画面で手で足した予定には目印をつけない(スマホから足した予定と同じ扱い)。締切や日時が変わったり、タスクを消したりしたときに、自動で書き換え・削除するのは目印のある予定だけ
-・自分の手で直すときは、F19 のスケジュールの画面から、自分が作った予定を全部直せる。人から招待された予定は、予定ごとのトグルで許したものだけ直せる
-・タスクを完了にしたら、予定は消さずに名前の頭に「済」をつける(例:「済 第10回レポート」)。期限が過ぎて未完了のものは、そのまま残す
-・同じ予定がすでにカレンダーにあれば書き込まない。日時のある予定は、同じ日に時間帯が重なれば名前が違っても同じとみなす。時間帯のない締切は、同じ日に同じ名前なら同じとみなす
-・モーニングブリーフ(gmail-secretary)側の自動登録は止める(二重登録を防ぐため)。止めるのは、F13 が動くようになってから
-・目印のある締切の予定を Google 側(スマホなど)で動かしたら、workbench のタスクの締切もそれに合わせる</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>済:締切や日時が変わったり、タスクを消したりしたとき、カレンダーの予定も直すか → 直す(workbench が書いた予定だけ)
-済:タスクを完了にしたとき、期限が過ぎたときの予定の扱い → 消さずに残し、完了したら「済」をつける
-済:同じ予定がすでにカレンダーにあるときの扱い → 時間帯が重なれば書かない(締切は同じ日・同じ名前で比べる)
-済:締切を時刻つきの予定にするか、終日の予定にするか → 締切は終日、時刻は名前に書く
-済(F19 で変更):自分の手で直せる予定 → 自分が作った予定は全部。招待された予定は、予定ごとのトグルで許したものだけ
-・未分類から入れ物を選び直したタスクを、カレンダーに書くか
-→ 基本設計で決める
-済(点検で追加):Google に書けなかった予定 → workbench に一時的に残し、つながったら書き直す。重なりは2段目で選ぶ
-済(点検で追加):締切の予定がタスクと2回出る件、Google 側で動かしたとき → 画面には1回だけ。Google で動かしたらタスクの締切も合わせる
-済(点検で追加):自分で足した種類のタスクの締切も書くか → 書く(種類を問わない)</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -965,6 +856,30 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
+    <t>・一番上に、全体の進み具合のゲージを細く1本出す。そのすぐ下に、「トップに出す」を選んだ入れ物のゲージを出す(F6)
+・その下は役割ごとに3段に分ける。1段目:記録中の作業(F4)。2段目:お知らせ(あるときだけ出す)。3段目:「期限切れ」
+・2段目に出すものは次の9つ:①作業記録の再開の確認(F4)②PC の電源が切れていた間の通知(F8)③学期の終わりの米印(F10)④読めなかった・つながらなかった(F7・F9・F10・F11・F12・F19)⑤読み込み中(非機能要件)⑥カレンダーに書かなかった予定(F13)⑦新しい連絡の件数(F9・F11・F20)⑧「終わっていそう」なタスクの件数(F18)⑨未分類の件数(F2)
+・「期限切れ」には、締切を過ぎたタスクを色を変えてまとめる。完了にするか締切を変えるまで残る
+・その下に、今日の時間(F10・F12)を出す。今日の時間には、授業・面接など時刻の決まった予定だけを出し、タスクの締切は出さない(今日が締切のタスクは「今日」の欄にだけ出す)
+・その下に「今日」と「今週」に分けて、締切の近い順に並べる
+・締切のないタスクは、その下に「締切なし」としてまとめて出す
+・同じ締切の日の中は、①時刻があるものは時刻順、時刻なしはその日の最後 ②同じなら「先に並べる」設定の種類を先(初めは大学・就活) ③さらに同じなら登録が古い順。「締切なし」の中は登録が古い順
+・各タスクに入れ物の名前のラベル(例:「卒論」「fx-practice」)をつけ、ラベルの色を種類ごとの色で分ける(F1)
+・「未分類」のタスクのラベルは灰色にする(F1)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・F10 の今日の授業と同じ「今日の時間」の列に、今日の予定を混ぜて時刻順に並べる
+・空き時間は書かない
+・読むのは個人の Google アカウントのメインのカレンダーだけ
+・読み方は F11 と同じ Google の公式の連携(API)。読めなかったときは、推測で埋めず「Google に接続できませんでした」と出す
+・アルバイトの予定は、入れ物を作らず、ここに予定として出す。入れ方は F14 のシフト表の写真か、Google カレンダーへの直接入力
+・今日より先の予定は、F19 のスケジュールの画面で見る
+・workbench が書いた締切の予定は、「今日の時間」には出さない。今日が締切のタスクは、トップの「今日」の欄にだけ出す(F3)
+・アプリの起動時と10分ごと(Claude の案)に読む(F19 と同じ)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
     <t>・予定の本体は Google カレンダー(個人のアカウントのメインのカレンダー)に置く。workbench の中に別の写しは持たない。ただし、Google に書けなかった予定だけは一時的に預かる(F13)
 ・workbench で予定を足す・直す・消すと、その場で Google カレンダーにも反映する
 ・Google カレンダーで足した・直した予定(スマホからも)は、アプリの起動時と10分ごと(Claude の案)に読んで出す
@@ -977,11 +892,107 @@
 ・予定を消す前には確認を出す
 ・Google に接続できないときは、足す・直すことができない。「Google に接続できませんでした」と出す
 ・画面で手で足した予定には、workbench の目印をつけない(F13)
-・workbench が書いた締切の予定は、F12 の「今日の時間」と F19 のスケジュールの画面では、タスクとして1回だけ出す(予定としては出さない)。Google 側で動かしたら、タスクの締切も合わせる(F13)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>アプリや PC を再起動しても、入れ物・タスク・作業記録・種類とその設定・トップに出す選択・バイト先の一覧・振り分けの覚え・一時的に預かった「書けなかった予定」が残る</t>
+・workbench が書いた締切の予定は、スケジュールの画面では、タスクとして1回だけ出す(予定としては出さない)。Google 側で動かしたら、タスクの締切も合わせる(F13)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・書き込むもの:タスクの締切(種類を問わず、締切のあるもの)、面接・面談、休講・補講、奨学金の手続きなど、締切か日時があるもの
+・「その他」のメールから自動で入ったものは書き込まない。1行入力(F17)などで「未分類」に入った締切つきのタスクは書き込む
+・面接など日時の決まったものは、時刻つきの予定にする。締切は全部終日の予定にし、時刻は名前に書く(例:「締切 23:59 第10回レポート」)
+・書けなかった予定は、workbench の中に「書けなかった予定」として一時的に残す。Google に接続できなかったときは、つながったら自動でもう一度書く。重なる予定があって書かなかったときは、2段目のお知らせに「重なる予定があるため書いていません」と出し、「それでも書く」「書かない」を選べる。書けたら、または「書かない」を選んだら、一時的な分は消す
+・書き込み先は、F12 と同じ個人のアカウントのメインのカレンダー
+・タスクやメールから自動で書いた予定には目印をつける。F19 の画面で手で足した予定には目印をつけない(スマホから足した予定と同じ扱い)。締切や日時が変わったり、タスクを消したりしたときに、自動で書き換え・削除するのは目印のある予定だけ
+・自分の手で直すときは、F19 のスケジュールの画面から、自分が作った予定を全部直せる。人から招待された予定は、予定ごとのトグルで許したものだけ直せる
+・タスクを完了にしたら、予定は消さずに名前の頭に「済」をつける(例:「済 第10回レポート」)。期限が過ぎて未完了のものは、そのまま残す
+・同じ予定がすでにカレンダーにあれば書き込まない。日時のある予定は、同じ日に時間帯が重なれば名前が違っても同じとみなす。時間帯のない締切は、同じ日に同じ名前なら同じとみなす
+・モーニングブリーフ(gmail-secretary)側の自動登録は止める(二重登録を防ぐため)。止めるのは、F13 が動くようになってから
+・目印のある締切の予定を Google 側(スマホなど)で動かしたら、workbench のタスクの締切もそれに合わせる</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:締切や日時が変わったり、タスクを消したりしたとき、カレンダーの予定も直すか → 直す(workbench が書いた予定だけ)
+済:タスクを完了にしたとき、期限が過ぎたときの予定の扱い → 消さずに残し、完了したら「済」をつける
+済:同じ予定がすでにカレンダーにあるときの扱い → 時間帯が重なれば書かない(締切は同じ日・同じ名前で比べる)
+済:締切を時刻つきの予定にするか、終日の予定にするか → 締切は終日、時刻は名前に書く
+済(F19 で変更):自分の手で直せる予定 → 自分が作った予定は全部。招待された予定は、予定ごとのトグルで許したものだけ
+・未分類から入れ物を選び直したタスクを、カレンダーに書くか
+→ 基本設計で決める
+済(点検で追加):Google に書けなかった予定 → workbench に一時的に残し、つながったら書き直す。重なりは2段目で選ぶ
+済(点検で追加):締切の予定がタスクと2回出る件、Google 側で動かしたとき → 画面には1回だけ。Google で動かしたらタスクの締切も合わせる
+済(点検で追加):自分で足した種類のタスクの締切も書くか → 書く(種類を問わない)
+済(点検で追加):1行入力などで未分類に入った締切つきのタスク → 書き込む
+・目印のある締切の予定を Google 側で消した・名前を変えたときの、タスクの扱い
+→ 基本設計で決める</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:入れ物を消したとき、中のタスクと作業記録をどうするか → 消さずに終了にする
+済:学期が終わった授業をどう片付けるか → 終了にする
+済(点検で追加):「未分類」はどの種類か → 3種類の外の特別な入れ物。ラベルは灰色、全体のゲージにだけ数える
+済(追加55):種類を自分でカスタマイズできるか → 足す・名前と色を変える・消すことができる。種類ごとに「先に並べるか」「締切なしに手つかずの通知を出すか」の2つの設定を持つ
+済(点検で追加):初めの3種類を消せるか → 消せない(名前と色は変えられる)
+済(点検で追加):灰色を種類に選べるか → 選べない(未分類だけの色)
+済(点検で追加):終了した入れ物が残る種類を消せるか → 消せない。入れ物をほかの種類に移せる
+済(点検で追加):自分で作ったアルバイトの種類と F20 → 種類は作れる。F20 は入れ物なしのまま
+・自動で作った入れ物(授業・企業)をほかの種類に移したときの扱い(次に時間割を読んだときにもう一度作るか、メールを振り分け続けるか)
+・自分で足した種類の2つの設定の、初めの値
+→ 基本設計で決める</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:どのカレンダーを読むか → 個人のアカウントのメインのカレンダーだけ
+済(点検で追加):いつ読むか → 起動時と10分ごと(F19 と同じ)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・完了したタスクの数 ÷ 全部のタスクの数
+・タスクが0件の入れ物は、数字やバーを出さずに「タスクなし」と出す
+・トップ画面では、「トップに出す」を選んだ入れ物のゲージを、全体のゲージのすぐ下にいつも出す。今日・今週にタスクがある入れ物のゲージは、全体のゲージを押して開く小窓の中に、全体と種類ごとのゲージに続けて並べる
+・入れ物ごとに「トップに出す」を自分で選べる。選んだ入れ物は、タスクがなくてもトップに出る
+・入れ物の一覧画面には、全部の入れ物の進み具合を出す
+・進み具合はゲージ(横に伸びるバー)と「○% 完了」で出す
+・入れ物ごとのゲージに加えて、種類ごと(初めは大学・就活・開発)と全体のゲージを出す
+・種類ごと・全体で数えるのは、「終了」にしていない入れ物のタスクだけ
+・トップ画面の一番上に、全体のゲージを細く1本だけ出す。押すと小さな窓が開き、全体と種類ごとのゲージが見える
+・「未分類」のタスクは、全体のゲージにだけ数え、種類ごとのゲージには入れない(F1)
+・タスクが0件の種類のゲージも、入れ物と同じく「タスクなし」と出す</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:タスクが0件の入れ物をどう表示するか → 「タスクなし」と文字で出す
+済:どの画面に出すか → トップは今日・今週にタスクがある入れ物+自分で選んだ入れ物、一覧画面は全部
+済:全体のゲージを何で出すか → 種類ごと(初めは大学・就活・開発)と全体
+済:種類ごと・全体で何を数えるか → 「終了」にしていない入れ物のタスクだけ
+済:全体と種類ごとのゲージをどこに出すか → トップの一番上に全体を細く1本、押すと小窓で種類ごと
+済(点検で追加):入れ物ごとのゲージをトップのどこに出すか → 選んだ入れ物は全体のすぐ下にいつも、今日・今週の入れ物は小窓の中(図で比べた)
+・全体のゲージの小窓の細かい動き(開き方・閉じ方)
+→ UI 試作で決める</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・登録したリポジトリのコミットを読む
+・1つのリポジトリに複数のアプリがある場合(lab)は、変更されたフォルダで入れ物に振り分ける
+・同じコミットを二重に取り込まない
+・アプリを起動したときと、10分ごと(Claude の案)に読む
+・コミットの時刻に、同じ入れ物の手の記録(F4)が動いていれば、その記録にコミットの内容をくっつける。なければ「その時刻に何をしたか」の点として並べ、作業時間の集計には入れない
+・リポジトリは入れ物に登録する。登録できる入れ物の種類は問わない(初めは「開発」で使う想定)
+・読めなかったとき(リポジトリが見つからないなど)は推測で埋めず、画面に「git の履歴を読めませんでした」と出す</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>アプリや PC を再起動しても、data/ に置く設定と記録は全部残る(入れ物・タスク・作業記録・種類とその設定・トップに出す選択・リポジトリの登録・企業とバイト先のアドレス・シフト表での自分の名前・自分で書いた一言と選んだ状態・振り分けの覚え・消したものの記録・連絡の「見た」・「自動」の印・招待された予定のトグル・一時的に預かった「書けなかった予定」)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>新しく払うお金は0円。有料のサービスや API を新しく契約しない(今の Claude Code の契約は含めない。F14・F18 はその範囲で動かす)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>Gmail に読む以外の操作がないこと、自動の処理が目印のない予定を変えないこと、トグルを入れていない招待された予定を直せないこと、リポジトリに鍵のファイルや鍵らしい文字列がないことを確かめる</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ver.0.1</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1183,7 +1194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1232,6 +1243,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1252,6 +1266,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1591,14 +1608,14 @@
       <c r="C8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="27" t="s">
-        <v>188</v>
-      </c>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
+      <c r="E8" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
     </row>
     <row r="10" spans="1:10" ht="19.5">
       <c r="C10" s="2" t="s">
@@ -1614,43 +1631,43 @@
       <c r="J10" s="14"/>
     </row>
     <row r="13" spans="1:10" ht="37.5">
-      <c r="F13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G13" s="22" t="s">
-        <v>131</v>
+      <c r="F13" s="22" t="s">
+        <v>218</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="16.5">
       <c r="E15" s="12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="12"/>
       <c r="H15" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I15" s="12"/>
       <c r="J15" s="12"/>
     </row>
     <row r="16" spans="1:10" ht="16.5">
       <c r="E16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="H16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="17" spans="5:10" ht="45.95" customHeight="1">
@@ -1696,39 +1713,39 @@
   <sheetData>
     <row r="1" spans="1:9" ht="24">
       <c r="A1" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="148.5">
-      <c r="A2" s="28" t="s">
-        <v>193</v>
+      <c r="A2" s="29" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="16.5">
       <c r="A3" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="C5" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="D5" s="16" t="s">
         <v>16</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>17</v>
       </c>
       <c r="E5" s="18"/>
       <c r="F5" s="16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G5" s="18"/>
       <c r="H5" s="16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I5" s="18"/>
     </row>
@@ -1737,22 +1754,22 @@
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
       <c r="D6" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="16.5">
@@ -1760,13 +1777,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>20</v>
-      </c>
       <c r="D7" s="4"/>
-      <c r="E7" s="23">
+      <c r="E7" s="24">
         <v>46310</v>
       </c>
       <c r="F7" s="4"/>
@@ -1778,10 +1795,10 @@
       <c r="A8" s="4">
         <v>2</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="8"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="19"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
+      <c r="E8" s="24"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
@@ -2012,61 +2029,61 @@
   <sheetData>
     <row r="1" spans="1:3" ht="24">
       <c r="A1" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="66">
-      <c r="A2" s="28" t="s">
-        <v>193</v>
+      <c r="A2" s="29" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="16.5">
       <c r="A3" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="36" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C5" s="8"/>
     </row>
     <row r="6" spans="1:3" ht="36" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="54">
       <c r="A7" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="54">
       <c r="A8" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="81">
       <c r="A9" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>41</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -2095,462 +2112,462 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24">
       <c r="A1" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="66">
-      <c r="A2" s="28" t="s">
-        <v>193</v>
+      <c r="A2" s="29" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="16.5">
       <c r="A3" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="16.5">
       <c r="A5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>29</v>
-      </c>
       <c r="G5" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="409.5">
       <c r="A6" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>202</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>44</v>
-      </c>
       <c r="F6" s="19" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="280.5">
       <c r="A7" s="8"/>
       <c r="B7" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>46</v>
-      </c>
       <c r="D7" s="19" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="363">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="396">
       <c r="A8" s="8"/>
       <c r="B8" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="115.5">
       <c r="A9" s="8"/>
       <c r="B9" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>49</v>
-      </c>
       <c r="D9" s="19" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="82.5">
       <c r="A10" s="8"/>
       <c r="B10" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>51</v>
-      </c>
       <c r="D10" s="19" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="363">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="346.5">
       <c r="A11" s="8"/>
       <c r="B11" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>212</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="165">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="198">
       <c r="A12" s="8"/>
       <c r="B12" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="297">
       <c r="A13" s="8"/>
       <c r="B13" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>55</v>
-      </c>
       <c r="D13" s="19" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="409.5">
       <c r="A14" s="8"/>
       <c r="B14" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="214.5">
       <c r="A15" s="8"/>
       <c r="B15" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>77</v>
-      </c>
       <c r="D15" s="19" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="409.5">
       <c r="A16" s="19"/>
       <c r="B16" s="19" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="G16" s="24" t="s">
-        <v>133</v>
+        <v>175</v>
+      </c>
+      <c r="G16" s="25" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="214.5">
       <c r="A17" s="19"/>
       <c r="B17" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="G17" s="26" t="s">
         <v>134</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="F17" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="G17" s="25" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="409.5">
       <c r="A18" s="19"/>
       <c r="B18" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="G18" s="26" t="s">
         <v>137</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="G18" s="25" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="214.5">
       <c r="A19" s="19"/>
       <c r="B19" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="G19" s="26" t="s">
         <v>140</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="F19" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="G19" s="25" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="231">
       <c r="A20" s="19"/>
       <c r="B20" s="19" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="G20" s="25" t="s">
-        <v>146</v>
+        <v>184</v>
+      </c>
+      <c r="G20" s="26" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="94.5">
       <c r="A21" s="21"/>
       <c r="B21" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="D21" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="C21" s="21" t="s">
+      <c r="E21" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="F21" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="D21" s="21" t="s">
+      <c r="G21" s="20" t="s">
         <v>159</v>
-      </c>
-      <c r="E21" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="F21" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="G21" s="20" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="121.5">
       <c r="A22" s="20"/>
       <c r="B22" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="D22" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="E22" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="G22" s="20" t="s">
         <v>163</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="F22" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="G22" s="20" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="283.5">
       <c r="A23" s="20"/>
       <c r="B23" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="D23" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="C23" s="20" t="s">
+      <c r="E23" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="G23" s="20" t="s">
         <v>167</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="F23" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="G23" s="20" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="409.5">
       <c r="A24" s="20"/>
       <c r="B24" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="G24" s="20" t="s">
         <v>173</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="E24" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="F24" s="20" t="s">
-        <v>174</v>
-      </c>
-      <c r="G24" s="20" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="121.5">
       <c r="A25" s="20"/>
       <c r="B25" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="D25" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="C25" s="20" t="s">
+      <c r="E25" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="F25" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="D25" s="20" t="s">
+      <c r="G25" s="20" t="s">
         <v>182</v>
-      </c>
-      <c r="E25" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="F25" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="G25" s="20" t="s">
-        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -2570,22 +2587,22 @@
   <sheetData>
     <row r="1" spans="1:1" ht="24">
       <c r="A1" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="99">
-      <c r="A2" s="28" t="s">
-        <v>193</v>
+      <c r="A2" s="29" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="16.5">
       <c r="A3" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="16.5">
       <c r="A5" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -2611,339 +2628,339 @@
   <sheetData>
     <row r="1" spans="1:4" ht="24">
       <c r="A1" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="66">
-      <c r="A2" s="28" t="s">
-        <v>193</v>
+      <c r="A2" s="29" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.5">
       <c r="A3" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16.5">
       <c r="A5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>35</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="49.5">
       <c r="A6" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>57</v>
-      </c>
       <c r="C6" s="19" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16.5">
       <c r="A7" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="C7" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="D7" s="8" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="99">
+      <c r="A8" s="8" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="49.5">
-      <c r="A8" s="8" t="s">
+      <c r="B8" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>62</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="33">
       <c r="A9" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>64</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16.5">
       <c r="A10" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="C10" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="D10" s="8" t="s">
         <v>68</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="33">
       <c r="A11" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>71</v>
-      </c>
       <c r="C11" s="19" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="33">
       <c r="A12" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="16.5">
       <c r="A13" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="C13" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="D13" s="19" t="s">
         <v>120</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="33">
       <c r="A14" s="19" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="27">
       <c r="A15" s="21" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="20" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="54">
       <c r="A17" s="20" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="27">
       <c r="A18" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B18" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="D18" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D18" s="11" t="s">
+    </row>
+    <row r="19" spans="1:4" ht="27">
+      <c r="A19" s="11" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="11" t="s">
+      <c r="B19" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="B19" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>83</v>
+      <c r="C19" s="20" t="s">
+        <v>216</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="54">
       <c r="A22" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="27">
       <c r="A23" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="40.5">
       <c r="A25" s="20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="27">
       <c r="A26" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="B26" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="B26" s="20" t="s">
-        <v>113</v>
-      </c>
       <c r="C26" s="20" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="54">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="67.5">
       <c r="A27" s="20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
